--- a/generated_data/bank_statement_union_bank.xlsx
+++ b/generated_data/bank_statement_union_bank.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,22 +496,20 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>01-05-2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609019237/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605019455/CR</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n">
-        <v>3636.55</v>
-      </c>
+      <c r="F2" s="3" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>13,636.55 Cr</t>
+          <t>8,999.94 Cr</t>
         </is>
       </c>
     </row>
@@ -521,22 +519,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>01-05-2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609023305/CR</t>
+          <t>UPIAB/539631629714/CR/TAIESWA/PPIW/6302476334.wal</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n">
-        <v>4496.71</v>
+        <v>368.88</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>18,133.26 Cr</t>
+          <t>9,368.82 Cr</t>
         </is>
       </c>
     </row>
@@ -546,22 +544,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>02-05-2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/800823341214/CR/PITCHIKA/CNRB/ umanag9712@ax</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605023207/CR</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n">
-        <v>2169.46</v>
+        <v>438.89</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>20,302.72 Cr</t>
+          <t>9,807.71 Cr</t>
         </is>
       </c>
     </row>
@@ -571,22 +569,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>02-05-2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/110099887766/DR/OLA CABS</t>
+          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="3" t="n">
-        <v>268.94</v>
-      </c>
-      <c r="F5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n">
+        <v>801.3099999999999</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,033.78 Cr</t>
+          <t>10,609.02 Cr</t>
         </is>
       </c>
     </row>
@@ -596,22 +594,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>03-05-2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609042093/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605036812/CR</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n">
-        <v>2247.28</v>
+        <v>4248.47</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22,281.06 Cr</t>
+          <t>14,857.49 Cr</t>
         </is>
       </c>
     </row>
@@ -621,22 +619,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>05-05-2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609053685/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605052379/CR</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n">
-        <v>2317.1</v>
+        <v>3691.9</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,598.16 Cr</t>
+          <t>18,549.39 Cr</t>
         </is>
       </c>
     </row>
@@ -646,22 +644,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>06-09-2026</t>
+          <t>06-05-2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609062389/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605067265/CR</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n">
-        <v>2439</v>
+        <v>1141.07</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>27,037.16 Cr</t>
+          <t>19,690.46 Cr</t>
         </is>
       </c>
     </row>
@@ -671,22 +669,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>06-09-2026</t>
+          <t>07-05-2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/665544332211/DR/AMAZON INDIA</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605076100/CR</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="3" t="n">
-        <v>1448.55</v>
-      </c>
-      <c r="F9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n">
+        <v>1580.98</v>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,588.61 Cr</t>
+          <t>21,271.44 Cr</t>
         </is>
       </c>
     </row>
@@ -696,22 +694,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>08-05-2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609076328/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605081706/CR</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n">
-        <v>802.84</v>
+        <v>1309.3</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>26,391.45 Cr</t>
+          <t>22,580.74 Cr</t>
         </is>
       </c>
     </row>
@@ -721,22 +719,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>08-05-2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/322671730620/CR/PITCHIKA/SBIN/ 8919861154@ax</t>
+          <t>UPIAB/020074062699/CR/THIRUVEE/UBIN/9391652831-2@a</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n">
-        <v>1930.56</v>
+        <v>124.53</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,322.01 Cr</t>
+          <t>22,705.27 Cr</t>
         </is>
       </c>
     </row>
@@ -746,22 +744,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609081244/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605095035/CR</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n">
-        <v>2445.15</v>
+        <v>5937.13</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>30,767.16 Cr</t>
+          <t>28,642.40 Cr</t>
         </is>
       </c>
     </row>
@@ -771,22 +769,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>11-05-2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609098010/CR</t>
+          <t>UPIAB/443322110099/CR/PROMO DISCOUNT CREDIT</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n">
-        <v>4123.44</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,890.60 Cr</t>
+          <t>28,721.14 Cr</t>
         </is>
       </c>
     </row>
@@ -796,22 +794,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>12-05-2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/026544681447/DR/SHANTIP/YESB/ Q707874078@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605126192/CR</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="3" t="n">
-        <v>364.28</v>
-      </c>
-      <c r="F14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n">
+        <v>7131.43</v>
+      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>34,526.32 Cr</t>
+          <t>35,852.57 Cr</t>
         </is>
       </c>
     </row>
@@ -821,22 +819,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>13-05-2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>BANK SMS ALERTS &amp; ANNUAL MAINT CHARGES</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605138736/CR</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="3" t="n">
-        <v>92.34999999999999</v>
-      </c>
-      <c r="F15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n">
+        <v>1771.58</v>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34,433.97 Cr</t>
+          <t>37,624.15 Cr</t>
         </is>
       </c>
     </row>
@@ -846,22 +844,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>10-09-2026</t>
+          <t>13-05-2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609106021/CR</t>
+          <t>UPIAR/204208208508/DR/Zomato87/AIRP/Zomato8759546.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n">
-        <v>2792.79</v>
-      </c>
+      <c r="E16" s="3" t="n">
+        <v>179.74</v>
+      </c>
+      <c r="F16" s="3" t="n"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>37,226.76 Cr</t>
+          <t>37,444.41 Cr</t>
         </is>
       </c>
     </row>
@@ -871,22 +869,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>14-05-2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609115230/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605144211/CR</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n">
-        <v>922.8</v>
+        <v>2730.17</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>38,149.56 Cr</t>
+          <t>40,174.58 Cr</t>
         </is>
       </c>
     </row>
@@ -896,22 +894,22 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12-09-2026</t>
+          <t>14-05-2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609126886/CR</t>
+          <t>UPIAR/701074556047/DR/73374590/PUNB/7337459005@pty</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n">
-        <v>4121.38</v>
-      </c>
+      <c r="E18" s="3" t="n">
+        <v>101.34</v>
+      </c>
+      <c r="F18" s="3" t="n"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>42,270.94 Cr</t>
+          <t>40,073.24 Cr</t>
         </is>
       </c>
     </row>
@@ -921,22 +919,22 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12-09-2026</t>
+          <t>15-05-2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/140515780706/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605152367/CR</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="3" t="n">
-        <v>187.91</v>
-      </c>
-      <c r="F19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n">
+        <v>1575.76</v>
+      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>42,083.03 Cr</t>
+          <t>41,649.00 Cr</t>
         </is>
       </c>
     </row>
@@ -946,22 +944,22 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>12-09-2026</t>
+          <t>15-05-2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/455944913251/DR/KEMSARAP/SBIN/ 8977604821@yb</t>
+          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="3" t="n">
-        <v>212.16</v>
+        <v>11223.4</v>
       </c>
       <c r="F20" s="3" t="n"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>41,870.87 Cr</t>
+          <t>30,425.60 Cr</t>
         </is>
       </c>
     </row>
@@ -971,22 +969,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>13-09-2026</t>
+          <t>16-05-2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609132900/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605164710/CR</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n">
-        <v>243.07</v>
+        <v>3990.25</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>42,113.94 Cr</t>
+          <t>34,415.85 Cr</t>
         </is>
       </c>
     </row>
@@ -996,22 +994,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>13-09-2026</t>
+          <t>16-05-2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/812938102938/DR/PETROL PUMP/HPCL/hpcl@icici</t>
+          <t>OFFICE PANTRY &amp; FRESH REFRESHMENTS</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="3" t="n">
-        <v>774.59</v>
+        <v>1584.14</v>
       </c>
       <c r="F22" s="3" t="n"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>41,339.35 Cr</t>
+          <t>32,831.71 Cr</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1019,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>14-09-2026</t>
+          <t>17-05-2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609144939/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605178273/CR</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n">
-        <v>1266.14</v>
+        <v>1273.33</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>42,605.49 Cr</t>
+          <t>34,105.04 Cr</t>
         </is>
       </c>
     </row>
@@ -1046,22 +1044,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>18-05-2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609151789/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605189899/CR</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n">
-        <v>3049.01</v>
+        <v>1226.16</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>45,654.50 Cr</t>
+          <t>35,331.20 Cr</t>
         </is>
       </c>
     </row>
@@ -1071,22 +1069,22 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>18-05-2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609166719/CR</t>
+          <t>UPIAB/322671730620/CR/PITCHIKA/SBIN/ 8919861154@ax</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n">
-        <v>3539.06</v>
+        <v>4367.77</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>49,193.56 Cr</t>
+          <t>39,698.97 Cr</t>
         </is>
       </c>
     </row>
@@ -1096,22 +1094,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>19-05-2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609176485/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605197998/CR</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="n">
-        <v>6801.41</v>
+        <v>3120.03</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>55,994.97 Cr</t>
+          <t>42,819.00 Cr</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1119,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>20-05-2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609187785/CR</t>
+          <t>UPIAB/789123891023/CR/CUSTOMER REFUND REVERSAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="n">
-        <v>3597.5</v>
+        <v>401.15</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>59,592.47 Cr</t>
+          <t>43,220.15 Cr</t>
         </is>
       </c>
     </row>
@@ -1146,22 +1144,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>21-05-2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/123854061954/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605214877/CR</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="3" t="n">
-        <v>266.91</v>
-      </c>
-      <c r="F28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n">
+        <v>4677.05</v>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>59,325.56 Cr</t>
+          <t>47,897.20 Cr</t>
         </is>
       </c>
     </row>
@@ -1171,22 +1169,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>19-09-2026</t>
+          <t>21-05-2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609199425/CR</t>
+          <t>SERVICE CHARGE / MINIMUM BALANCE FEE</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n">
-        <v>2167.4</v>
-      </c>
+      <c r="E29" s="3" t="n">
+        <v>385.41</v>
+      </c>
+      <c r="F29" s="3" t="n"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>61,492.96 Cr</t>
+          <t>47,511.79 Cr</t>
         </is>
       </c>
     </row>
@@ -1196,22 +1194,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>20-09-2026</t>
+          <t>21-05-2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609207527/CR</t>
+          <t>UPIAR/554433221100/DR/FLIPKART ONLINE</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n">
-        <v>3197.76</v>
-      </c>
+      <c r="E30" s="3" t="n">
+        <v>2547.07</v>
+      </c>
+      <c r="F30" s="3" t="n"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>64,690.72 Cr</t>
+          <t>44,964.72 Cr</t>
         </is>
       </c>
     </row>
@@ -1221,22 +1219,22 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>22-05-2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609215081/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605227895/CR</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n">
-        <v>1981.85</v>
+        <v>563.87</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>66,672.57 Cr</t>
+          <t>45,528.59 Cr</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1244,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>22-05-2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/998877665544/DR/PAYTM QR VENDOR</t>
+          <t>WAREHOUSE STAFF WAGES &amp; PACKING CREW</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="3" t="n">
-        <v>72.2</v>
+        <v>26007.63</v>
       </c>
       <c r="F32" s="3" t="n"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>66,600.37 Cr</t>
+          <t>19,520.96 Cr</t>
         </is>
       </c>
     </row>
@@ -1271,22 +1269,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>23-05-2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>PACKAGING SUPPLIES / ECO CORRUGATED BOXES</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605233589/CR</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
-      <c r="E33" s="3" t="n">
-        <v>10136.89</v>
-      </c>
-      <c r="F33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n">
+        <v>1834.21</v>
+      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>56,463.48 Cr</t>
+          <t>21,355.17 Cr</t>
         </is>
       </c>
     </row>
@@ -1296,22 +1294,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>24-05-2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609221181/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605246400/CR</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n">
-        <v>1412.75</v>
+        <v>2316.07</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>57,876.23 Cr</t>
+          <t>23,671.24 Cr</t>
         </is>
       </c>
     </row>
@@ -1321,22 +1319,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>25-05-2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609233081/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605254539/CR</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n">
-        <v>697.15</v>
+        <v>178.48</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>58,573.38 Cr</t>
+          <t>23,849.72 Cr</t>
         </is>
       </c>
     </row>
@@ -1346,22 +1344,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>26-05-2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>EMPLOYEE FIELD COMMUTE &amp; TRAVEL REIMBURSEMENT</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605269626/CR</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="3" t="n">
-        <v>3968.31</v>
-      </c>
-      <c r="F36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="n">
+        <v>1008.82</v>
+      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>54,605.07 Cr</t>
+          <t>24,858.54 Cr</t>
         </is>
       </c>
     </row>
@@ -1371,122 +1369,22 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>27-05-2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609241811/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605277050/CR</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="3" t="n"/>
       <c r="F37" s="3" t="n">
-        <v>2465.65</v>
+        <v>149.78</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>57,070.72 Cr</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>25-09-2026</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609257127/CR</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n">
-        <v>2524.19</v>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>59,594.91 Cr</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>25-09-2026</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>COMMERCIAL WAREHOUSE RENT / KORAMANGALA HUB</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr"/>
-      <c r="E39" s="3" t="n">
-        <v>49251.75</v>
-      </c>
-      <c r="F39" s="3" t="n"/>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>10,343.16 Cr</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>26-09-2026</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609267231/CR</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="3" t="n"/>
-      <c r="F40" s="3" t="n">
-        <v>1121.6</v>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>11,464.76 Cr</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>27-09-2026</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202609272822/CR</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n">
-        <v>1548.19</v>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>13,012.95 Cr</t>
+          <t>25,008.32 Cr</t>
         </is>
       </c>
     </row>

--- a/generated_data/bank_statement_union_bank.xlsx
+++ b/generated_data/bank_statement_union_bank.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,15 +501,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605019455/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605013162/CR</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
+      <c r="F2" s="3" t="n">
+        <v>10816.01</v>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>8,999.94 Cr</t>
+          <t>20,816.01 Cr</t>
         </is>
       </c>
     </row>
@@ -524,17 +526,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/539631629714/CR/TAIESWA/PPIW/6302476334.wal</t>
+          <t>UPIAB/112938102938/CR/WHOLESALE MILK DEPOSIT</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n">
-        <v>368.88</v>
+        <v>4307.46</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>9,368.82 Cr</t>
+          <t>25,123.47 Cr</t>
         </is>
       </c>
     </row>
@@ -544,22 +546,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>02-05-2026</t>
+          <t>01-05-2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605023207/CR</t>
+          <t>SERVICE CHARGE / MINIMUM BALANCE FEE</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n">
-        <v>438.89</v>
-      </c>
+      <c r="E4" s="3" t="n">
+        <v>466.42</v>
+      </c>
+      <c r="F4" s="3" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,807.71 Cr</t>
+          <t>24,657.05 Cr</t>
         </is>
       </c>
     </row>
@@ -574,17 +576,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605024216/CR</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n">
-        <v>801.3099999999999</v>
+        <v>12025.72</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,609.02 Cr</t>
+          <t>36,682.77 Cr</t>
         </is>
       </c>
     </row>
@@ -599,17 +601,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605036812/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605032800/CR</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n">
-        <v>4248.47</v>
+        <v>13395.87</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14,857.49 Cr</t>
+          <t>50,078.64 Cr</t>
         </is>
       </c>
     </row>
@@ -619,22 +621,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05-05-2026</t>
+          <t>03-05-2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605052379/CR</t>
+          <t>BESCOM POWER UTILITY / BANGALORE WAREHOUSE</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n">
-        <v>3691.9</v>
-      </c>
+      <c r="E7" s="3" t="n">
+        <v>16770.07</v>
+      </c>
+      <c r="F7" s="3" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,549.39 Cr</t>
+          <t>33,308.57 Cr</t>
         </is>
       </c>
     </row>
@@ -644,22 +646,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>06-05-2026</t>
+          <t>04-05-2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605067265/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605041826/CR</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n">
-        <v>1141.07</v>
+        <v>4490.83</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>19,690.46 Cr</t>
+          <t>37,799.40 Cr</t>
         </is>
       </c>
     </row>
@@ -669,22 +671,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>07-05-2026</t>
+          <t>04-05-2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605076100/CR</t>
+          <t>DELIVERY FLEET FUEL &amp; DIESEL RECHARGE</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n">
-        <v>1580.98</v>
-      </c>
+      <c r="E9" s="3" t="n">
+        <v>8083.46</v>
+      </c>
+      <c r="F9" s="3" t="n"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,271.44 Cr</t>
+          <t>29,715.94 Cr</t>
         </is>
       </c>
     </row>
@@ -694,22 +696,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>08-05-2026</t>
+          <t>04-05-2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605081706/CR</t>
+          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n">
-        <v>1309.3</v>
+        <v>720.24</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>22,580.74 Cr</t>
+          <t>30,436.18 Cr</t>
         </is>
       </c>
     </row>
@@ -719,22 +721,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>08-05-2026</t>
+          <t>05-05-2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/020074062699/CR/THIRUVEE/UBIN/9391652831-2@a</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605054269/CR</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n">
-        <v>124.53</v>
+        <v>10255.65</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,705.27 Cr</t>
+          <t>40,691.83 Cr</t>
         </is>
       </c>
     </row>
@@ -744,22 +746,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>05-05-2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605095035/CR</t>
+          <t>UPIAR/124934775512/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n">
-        <v>5937.13</v>
-      </c>
+      <c r="E12" s="3" t="n">
+        <v>497.88</v>
+      </c>
+      <c r="F12" s="3" t="n"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28,642.40 Cr</t>
+          <t>40,193.95 Cr</t>
         </is>
       </c>
     </row>
@@ -769,22 +771,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>11-05-2026</t>
+          <t>05-05-2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/443322110099/CR/PROMO DISCOUNT CREDIT</t>
+          <t>UPIAB/789123891023/CR/CUSTOMER REFUND REVERSAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n">
-        <v>78.73999999999999</v>
+        <v>564.48</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,721.14 Cr</t>
+          <t>40,758.43 Cr</t>
         </is>
       </c>
     </row>
@@ -794,22 +796,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12-05-2026</t>
+          <t>06-05-2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605126192/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605064476/CR</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n">
-        <v>7131.43</v>
+        <v>10372.41</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>35,852.57 Cr</t>
+          <t>51,130.84 Cr</t>
         </is>
       </c>
     </row>
@@ -819,22 +821,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>13-05-2026</t>
+          <t>06-05-2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605138736/CR</t>
+          <t>INVENTORY AUDITOR &amp; CA LEGAL RETAINER</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n">
-        <v>1771.58</v>
-      </c>
+      <c r="E15" s="3" t="n">
+        <v>11140.38</v>
+      </c>
+      <c r="F15" s="3" t="n"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37,624.15 Cr</t>
+          <t>39,990.46 Cr</t>
         </is>
       </c>
     </row>
@@ -844,22 +846,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13-05-2026</t>
+          <t>06-05-2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/204208208508/DR/Zomato87/AIRP/Zomato8759546.</t>
+          <t>SERVICE CHARGE / MINIMUM BALANCE FEE</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="3" t="n">
-        <v>179.74</v>
+        <v>413.41</v>
       </c>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>37,444.41 Cr</t>
+          <t>39,577.05 Cr</t>
         </is>
       </c>
     </row>
@@ -869,22 +871,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>14-05-2026</t>
+          <t>06-05-2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605144211/CR</t>
+          <t>INVENTORY AUDITOR &amp; CA LEGAL RETAINER</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n">
-        <v>2730.17</v>
-      </c>
+      <c r="E17" s="3" t="n">
+        <v>17799.43</v>
+      </c>
+      <c r="F17" s="3" t="n"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>40,174.58 Cr</t>
+          <t>21,777.62 Cr</t>
         </is>
       </c>
     </row>
@@ -894,22 +896,22 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>14-05-2026</t>
+          <t>06-05-2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/701074556047/DR/73374590/PUNB/7337459005@pty</t>
+          <t>NEFT/OUTWARD/HDFC/FARMERS COOP SUPPLY</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="3" t="n">
-        <v>101.34</v>
+        <v>17987.92</v>
       </c>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>40,073.24 Cr</t>
+          <t>3,789.70 Cr</t>
         </is>
       </c>
     </row>
@@ -919,22 +921,22 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>15-05-2026</t>
+          <t>06-05-2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605152367/CR</t>
+          <t>UPIAR/026544681447/DR/SHANTIP/YESB/ Q707874078@yb</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n">
-        <v>1575.76</v>
-      </c>
+      <c r="E19" s="3" t="n">
+        <v>469.4</v>
+      </c>
+      <c r="F19" s="3" t="n"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>41,649.00 Cr</t>
+          <t>3,320.30 Cr</t>
         </is>
       </c>
     </row>
@@ -944,22 +946,22 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>15-05-2026</t>
+          <t>07-05-2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605075384/CR</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="3" t="n">
-        <v>11223.4</v>
-      </c>
-      <c r="F20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n">
+        <v>12685.01</v>
+      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>30,425.60 Cr</t>
+          <t>16,005.31 Cr</t>
         </is>
       </c>
     </row>
@@ -969,22 +971,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16-05-2026</t>
+          <t>07-05-2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605164710/CR</t>
+          <t>SWIGGY INSTAMART FLEET REIMBURSEMENT</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n">
-        <v>3990.25</v>
-      </c>
+      <c r="E21" s="3" t="n">
+        <v>608.86</v>
+      </c>
+      <c r="F21" s="3" t="n"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34,415.85 Cr</t>
+          <t>15,396.45 Cr</t>
         </is>
       </c>
     </row>
@@ -994,22 +996,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>16-05-2026</t>
+          <t>08-05-2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>OFFICE PANTRY &amp; FRESH REFRESHMENTS</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605088700/CR</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="3" t="n">
-        <v>1584.14</v>
-      </c>
-      <c r="F22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n">
+        <v>10408.6</v>
+      </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>32,831.71 Cr</t>
+          <t>25,805.05 Cr</t>
         </is>
       </c>
     </row>
@@ -1019,22 +1021,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>17-05-2026</t>
+          <t>08-05-2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605178273/CR</t>
+          <t>UPIAB/776655443322/CR/CASHBACK REWARD</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n">
-        <v>1273.33</v>
+        <v>39.63</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>34,105.04 Cr</t>
+          <t>25,844.68 Cr</t>
         </is>
       </c>
     </row>
@@ -1044,22 +1046,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>18-05-2026</t>
+          <t>08-05-2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605189899/CR</t>
+          <t>BESCOM POWER UTILITY / BANGALORE WAREHOUSE</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n">
-        <v>1226.16</v>
-      </c>
+      <c r="E24" s="3" t="n">
+        <v>12505.11</v>
+      </c>
+      <c r="F24" s="3" t="n"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>35,331.20 Cr</t>
+          <t>13,339.57 Cr</t>
         </is>
       </c>
     </row>
@@ -1069,22 +1071,22 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>18-05-2026</t>
+          <t>08-05-2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/322671730620/CR/PITCHIKA/SBIN/ 8919861154@ax</t>
+          <t>UPIAR/235911221570/DR/LHEMANT/HDFC/hemanth0508@yb</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n">
-        <v>4367.77</v>
-      </c>
+      <c r="E25" s="3" t="n">
+        <v>82.56</v>
+      </c>
+      <c r="F25" s="3" t="n"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>39,698.97 Cr</t>
+          <t>13,257.01 Cr</t>
         </is>
       </c>
     </row>
@@ -1094,22 +1096,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>19-05-2026</t>
+          <t>08-05-2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605197998/CR</t>
+          <t>INVENTORY AUDITOR &amp; CA LEGAL RETAINER</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n">
-        <v>3120.03</v>
-      </c>
+      <c r="E26" s="3" t="n">
+        <v>15776.97</v>
+      </c>
+      <c r="F26" s="3" t="n"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>42,819.00 Cr</t>
+          <t>-2,519.96 Cr</t>
         </is>
       </c>
     </row>
@@ -1119,22 +1121,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>20-05-2026</t>
+          <t>08-05-2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/789123891023/CR/CUSTOMER REFUND REVERSAL</t>
+          <t>NEFT/OUTWARD/UTI MUTUAL FUND SIP</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n">
-        <v>401.15</v>
-      </c>
+      <c r="E27" s="3" t="n">
+        <v>9725.700000000001</v>
+      </c>
+      <c r="F27" s="3" t="n"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>43,220.15 Cr</t>
+          <t>-12,245.66 Cr</t>
         </is>
       </c>
     </row>
@@ -1144,22 +1146,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>21-05-2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605214877/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605098828/CR</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="n">
-        <v>4677.05</v>
+        <v>8984.120000000001</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>47,897.20 Cr</t>
+          <t>-3,261.54 Cr</t>
         </is>
       </c>
     </row>
@@ -1169,22 +1171,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>21-05-2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>SERVICE CHARGE / MINIMUM BALANCE FEE</t>
+          <t>ATM CASH WITHDRAWAL / KORAMANGALA BRANCH</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="3" t="n">
-        <v>385.41</v>
+        <v>8343.690000000001</v>
       </c>
       <c r="F29" s="3" t="n"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>47,511.79 Cr</t>
+          <t>-11,605.23 Cr</t>
         </is>
       </c>
     </row>
@@ -1194,22 +1196,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>21-05-2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/554433221100/DR/FLIPKART ONLINE</t>
+          <t>UPIAR/685013228668/DR/LHEMANT/HDFC/hemanth0508@yb</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="3" t="n">
-        <v>2547.07</v>
+        <v>53.94</v>
       </c>
       <c r="F30" s="3" t="n"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>44,964.72 Cr</t>
+          <t>-11,659.17 Cr</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1221,22 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>22-05-2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605227895/CR</t>
+          <t>UPIAB/322671730620/CR/PITCHIKA/SBIN/ 8919861154@ax</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n">
-        <v>563.87</v>
+        <v>883.21</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>45,528.59 Cr</t>
+          <t>-10,775.96 Cr</t>
         </is>
       </c>
     </row>
@@ -1244,22 +1246,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22-05-2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE STAFF WAGES &amp; PACKING CREW</t>
+          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="3" t="n">
-        <v>26007.63</v>
+        <v>10247.9</v>
       </c>
       <c r="F32" s="3" t="n"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>19,520.96 Cr</t>
+          <t>-21,023.86 Cr</t>
         </is>
       </c>
     </row>
@@ -1269,22 +1271,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>23-05-2026</t>
+          <t>10-05-2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605233589/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605101746/CR</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="n">
-        <v>1834.21</v>
+        <v>10132.16</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>21,355.17 Cr</t>
+          <t>-10,891.70 Cr</t>
         </is>
       </c>
     </row>
@@ -1294,22 +1296,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>24-05-2026</t>
+          <t>10-05-2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605246400/CR</t>
+          <t>AIRTEL CORPORATE BROADBAND &amp; FIBER</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n">
-        <v>2316.07</v>
-      </c>
+      <c r="E34" s="3" t="n">
+        <v>2084.39</v>
+      </c>
+      <c r="F34" s="3" t="n"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>23,671.24 Cr</t>
+          <t>-12,976.09 Cr</t>
         </is>
       </c>
     </row>
@@ -1319,22 +1321,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25-05-2026</t>
+          <t>10-05-2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605254539/CR</t>
+          <t>UPIAR/717134959917/DR/AoapAmr/AIRP/AoapAmrita.pay</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n">
-        <v>178.48</v>
-      </c>
+      <c r="E35" s="3" t="n">
+        <v>2449.44</v>
+      </c>
+      <c r="F35" s="3" t="n"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>23,849.72 Cr</t>
+          <t>-15,425.53 Cr</t>
         </is>
       </c>
     </row>
@@ -1344,22 +1346,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>26-05-2026</t>
+          <t>11-05-2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605269626/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605116013/CR</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="n">
-        <v>1008.82</v>
+        <v>9437.379999999999</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>24,858.54 Cr</t>
+          <t>-5,988.15 Cr</t>
         </is>
       </c>
     </row>
@@ -1369,22 +1371,3795 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
+          <t>11-05-2026</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/685013228668/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="3" t="n">
+        <v>103.31</v>
+      </c>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>-6,091.46 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>12-05-2026</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605128885/CR</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="3" t="n">
+        <v>10654.09</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>4,562.63 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>12-05-2026</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/301984712093/DR/SWIGGY/HDFC/swiggy@hdfc</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
+      <c r="E39" s="3" t="n">
+        <v>345.25</v>
+      </c>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>4,217.38 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>12-05-2026</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>GST ADVANCE TAX DEPOSIT / GOVT OF INDIA</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="3" t="n">
+        <v>16991.3</v>
+      </c>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>-12,773.92 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>12-05-2026</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/235911221570/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="3" t="n">
+        <v>96.94</v>
+      </c>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>-12,870.86 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>13-05-2026</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605131026/CR</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3" t="n">
+        <v>7104.65</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>-5,766.21 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>13-05-2026</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/443322110099/CR/PROMO DISCOUNT CREDIT</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n">
+        <v>207.94</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>-5,558.27 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>14-05-2026</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605146410/CR</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="n">
+        <v>6736.3</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1,178.03 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>14-05-2026</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/204208208508/DR/Zomato87/AIRP/Zomato8759546.</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="3" t="n">
+        <v>215.32</v>
+      </c>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>962.71 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>14-05-2026</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>DELIVERY ELECTRIC VAN MAINTENANCE &amp; AMC</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="3" t="n">
+        <v>5183.8</v>
+      </c>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>-4,221.09 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>14-05-2026</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/322671730620/CR/PITCHIKA/SBIN/ 8919861154@ax</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="n">
+        <v>4103</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>-118.09 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>14-05-2026</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>AWS CLOUD SERVER HOSTING &amp; INFRASTRUCTURE</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="3" t="n">
+        <v>6870.34</v>
+      </c>
+      <c r="F48" s="3" t="n"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>-6,988.43 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>15-05-2026</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605158640/CR</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="3" t="n"/>
+      <c r="F49" s="3" t="n">
+        <v>10253.64</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>3,265.21 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>15-05-2026</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/758331734676/DR/EKNATHB/YESB/ Q440089343@yb</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="3" t="n">
+        <v>176.05</v>
+      </c>
+      <c r="F50" s="3" t="n"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>3,089.16 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>15-05-2026</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/908129381023/DR/BILLDESK/SBIN/billdesk@sbi</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="3" t="n">
+        <v>1103.79</v>
+      </c>
+      <c r="F51" s="3" t="n"/>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>1,985.37 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>15-05-2026</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/373995020793/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="3" t="n">
+        <v>2729.32</v>
+      </c>
+      <c r="F52" s="3" t="n"/>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>-743.95 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>16-05-2026</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605164499/CR</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n">
+        <v>10174.15</v>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>9,430.20 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>16-05-2026</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>BESCOM POWER UTILITY / BANGALORE WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="3" t="n">
+        <v>10774.02</v>
+      </c>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>-1,343.82 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>17-05-2026</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605173578/CR</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="n">
+        <v>3805.31</v>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>2,461.49 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>17-05-2026</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/887766554433/DR/BHARATPE MERCHANT</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="3" t="n">
+        <v>55.34</v>
+      </c>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>2,406.15 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>18-05-2026</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605181258/CR</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n">
+        <v>8387.68</v>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>10,793.83 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>18-05-2026</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>DELIVERY ELECTRIC VAN MAINTENANCE &amp; AMC</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="3" t="n">
+        <v>4766.73</v>
+      </c>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>6,027.10 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>19-05-2026</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605193787/CR</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n">
+        <v>9439.620000000001</v>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>15,466.72 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>19-05-2026</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/332211009988/DR/BOOKMYSHOW TICKET</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="3" t="n">
+        <v>866.45</v>
+      </c>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>14,600.27 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>19-05-2026</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/026544681447/DR/SHANTIP/YESB/ Q707874078@yb</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="3" t="n">
+        <v>742.36</v>
+      </c>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>13,857.91 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>19-05-2026</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>PACKAGING SUPPLIES / ECO CORRUGATED BOXES</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="3" t="n">
+        <v>15415.62</v>
+      </c>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>-1,557.71 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>20-05-2026</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605202820/CR</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr"/>
+      <c r="E63" s="3" t="n"/>
+      <c r="F63" s="3" t="n">
+        <v>9245.799999999999</v>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>7,688.09 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>20-05-2026</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>COMMERCIAL WAREHOUSE RENT / KORAMANGALA HUB</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="3" t="n">
+        <v>45885.05</v>
+      </c>
+      <c r="F64" s="3" t="n"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>-38,196.96 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>20-05-2026</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>WATER TANKER &amp; SANITATION CHARGES</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="3" t="n">
+        <v>3485.92</v>
+      </c>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>-41,682.88 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>21-05-2026</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605211677/CR</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="n">
+        <v>7109.9</v>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>-34,572.98 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>21-05-2026</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr"/>
+      <c r="E67" s="3" t="n"/>
+      <c r="F67" s="3" t="n">
+        <v>1047.86</v>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>-33,525.12 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>22-05-2026</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605226697/CR</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="n">
+        <v>11263</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>-22,262.12 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>22-05-2026</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/221100998877/DR/UBER RIDE</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="3" t="n">
+        <v>418.86</v>
+      </c>
+      <c r="F69" s="3" t="n"/>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>-22,680.98 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>22-05-2026</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/301984712093/DR/SWIGGY/HDFC/swiggy@hdfc</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="3" t="n">
+        <v>193.98</v>
+      </c>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>-22,874.96 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>23-05-2026</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605234899/CR</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n">
+        <v>11475.61</v>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>-11,399.35 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>24-05-2026</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605249678/CR</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n">
+        <v>7504.29</v>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>-3,895.06 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>24-05-2026</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>PRINTING BARCODE LABELS &amp; BILLING ROLLS</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr"/>
+      <c r="E73" s="3" t="n">
+        <v>1536.43</v>
+      </c>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>-5,431.49 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>24-05-2026</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/512938102938/CR/SUPPLIER CREDIT NOTE</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="3" t="n">
+        <v>4734.16</v>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>-697.33 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>24-05-2026</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>EMPLOYEE FIELD COMMUTE &amp; TRAVEL REIMBURSEMENT</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
+      <c r="E75" s="3" t="n">
+        <v>6588.48</v>
+      </c>
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>-7,285.81 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>24-05-2026</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/665544332211/DR/AMAZON INDIA</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="3" t="n">
+        <v>1829.21</v>
+      </c>
+      <c r="F76" s="3" t="n"/>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>-9,115.02 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>25-05-2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605259390/CR</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="3" t="n"/>
+      <c r="F77" s="3" t="n">
+        <v>9667.59</v>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>552.57 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>25-05-2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>SWIGGY INSTAMART FLEET REIMBURSEMENT</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="3" t="n">
+        <v>1115.26</v>
+      </c>
+      <c r="F78" s="3" t="n"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>-562.69 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>25-05-2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>PACKAGING SUPPLIES / ECO CORRUGATED BOXES</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" s="3" t="n">
+        <v>12411.45</v>
+      </c>
+      <c r="F79" s="3" t="n"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>-12,974.14 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>25-05-2026</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>POINT OF SALE (POS) HARDWARE RENTAL</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
+      <c r="E80" s="3" t="n">
+        <v>2566.97</v>
+      </c>
+      <c r="F80" s="3" t="n"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>-15,541.11 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>25-05-2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/172136536211/DR/ZOMATO L/YESB/zomato-order@p</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr"/>
+      <c r="E81" s="3" t="n">
+        <v>579.47</v>
+      </c>
+      <c r="F81" s="3" t="n"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>-16,120.58 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>26-05-2026</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605262378/CR</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="3" t="n"/>
+      <c r="F82" s="3" t="n">
+        <v>7075.66</v>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>-9,044.92 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>26-05-2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>LIC PREMIUM AUTO DEBIT CLEARING</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
+      <c r="E83" s="3" t="n">
+        <v>4023.86</v>
+      </c>
+      <c r="F83" s="3" t="n"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>-13,068.78 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>26-05-2026</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/539631629714/CR/TAIESWA/PPIW/6302476334.wal</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
+      <c r="E84" s="3" t="n"/>
+      <c r="F84" s="3" t="n">
+        <v>203.49</v>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>-12,865.29 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>27-05-2026</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605277050/CR</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr"/>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n">
-        <v>149.78</v>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>25,008.32 Cr</t>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605271436/CR</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr"/>
+      <c r="E85" s="3" t="n"/>
+      <c r="F85" s="3" t="n">
+        <v>6030.7</v>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-6,834.59 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>27-05-2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/712626244599/CR/PICHIKA/BARB/ 8985068499@ax</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr"/>
+      <c r="E86" s="3" t="n"/>
+      <c r="F86" s="3" t="n">
+        <v>869.67</v>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>-5,964.92 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>27-05-2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/212938102938/DR/BLINKIT/KOTAK/blinkit@kotak</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
+      <c r="E87" s="3" t="n">
+        <v>515.48</v>
+      </c>
+      <c r="F87" s="3" t="n"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>-6,480.40 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>27-05-2026</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>ATM CASH WITHDRAWAL / KORAMANGALA BRANCH</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="3" t="n">
+        <v>3646.86</v>
+      </c>
+      <c r="F88" s="3" t="n"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>-10,127.26 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>28-05-2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605284691/CR</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr"/>
+      <c r="E89" s="3" t="n"/>
+      <c r="F89" s="3" t="n"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>-17,272.66 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>28-05-2026</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/112938102938/CR/WHOLESALE MILK DEPOSIT</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
+      <c r="E90" s="3" t="n"/>
+      <c r="F90" s="3" t="n">
+        <v>11835.14</v>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>-5,437.52 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>29-05-2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605293961/CR</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr"/>
+      <c r="E91" s="3" t="n"/>
+      <c r="F91" s="3" t="n">
+        <v>12342.81</v>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>6,905.29 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>30-05-2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605306717/CR</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr"/>
+      <c r="E92" s="3" t="n"/>
+      <c r="F92" s="3" t="n">
+        <v>7677.71</v>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>14,583.00 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>30-05-2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/009988776655/CR/DIVIDEND PAYOUT</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr"/>
+      <c r="E93" s="3" t="n"/>
+      <c r="F93" s="3" t="n">
+        <v>1763.01</v>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>16,346.01 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>31-05-2026</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605314233/CR</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr"/>
+      <c r="E94" s="3" t="n"/>
+      <c r="F94" s="3" t="n">
+        <v>11447.92</v>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>27,793.93 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>31-05-2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/701074556047/DR/73374590/PUNB/7337459005@pty</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr"/>
+      <c r="E95" s="3" t="n">
+        <v>179.13</v>
+      </c>
+      <c r="F95" s="3" t="n"/>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>27,614.80 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>01-06-2026</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606013320/CR</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr"/>
+      <c r="E96" s="3" t="n"/>
+      <c r="F96" s="3" t="n">
+        <v>11778.21</v>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>39,393.01 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>01-06-2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/077728365159/DR/NAMBURI /YESB/ Q501702001@yb</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr"/>
+      <c r="E97" s="3" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="F97" s="3" t="n"/>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>39,382.63 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>01-06-2026</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/443322110099/CR/PROMO DISCOUNT CREDIT</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr"/>
+      <c r="E98" s="3" t="n"/>
+      <c r="F98" s="3" t="n">
+        <v>263.63</v>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>39,646.26 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>01-06-2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/140288398543/DR/73374590/PUNB/7337459005@pty</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr"/>
+      <c r="E99" s="3" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="F99" s="3" t="n"/>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>39,551.44 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>02-06-2026</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606022356/CR</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr"/>
+      <c r="E100" s="3" t="n"/>
+      <c r="F100" s="3" t="n">
+        <v>4567.2</v>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>44,118.64 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>03-06-2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606035152/CR</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr"/>
+      <c r="E101" s="3" t="n"/>
+      <c r="F101" s="3" t="n">
+        <v>4580.6</v>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>48,699.24 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>03-06-2026</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>BBMP MUNICIPAL TRADE LICENSE &amp; PROPERTY TAX</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
+      <c r="E102" s="3" t="n">
+        <v>6089.05</v>
+      </c>
+      <c r="F102" s="3" t="n"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>42,610.19 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>03-06-2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/908129381023/DR/BILLDESK/SBIN/billdesk@sbi</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr"/>
+      <c r="E103" s="3" t="n">
+        <v>695.26</v>
+      </c>
+      <c r="F103" s="3" t="n"/>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>41,914.93 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>03-06-2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>INVENTORY AUDITOR &amp; CA LEGAL RETAINER</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr"/>
+      <c r="E104" s="3" t="n">
+        <v>14081.25</v>
+      </c>
+      <c r="F104" s="3" t="n"/>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>27,833.68 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>04-06-2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606044731/CR</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr"/>
+      <c r="E105" s="3" t="n"/>
+      <c r="F105" s="3" t="n">
+        <v>14185.04</v>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>42,018.72 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>04-06-2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/332211009988/DR/BOOKMYSHOW TICKET</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr"/>
+      <c r="E106" s="3" t="n">
+        <v>858.11</v>
+      </c>
+      <c r="F106" s="3" t="n"/>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>41,160.61 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>05-06-2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606057301/CR</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr"/>
+      <c r="E107" s="3" t="n"/>
+      <c r="F107" s="3" t="n">
+        <v>14405.03</v>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>55,565.64 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>05-06-2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>SWIGGY INSTAMART FLEET REIMBURSEMENT</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr"/>
+      <c r="E108" s="3" t="n">
+        <v>1652.01</v>
+      </c>
+      <c r="F108" s="3" t="n"/>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>53,913.63 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>05-06-2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/235911221570/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr"/>
+      <c r="E109" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="F109" s="3" t="n"/>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>53,825.63 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>06-06-2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606065313/CR</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr"/>
+      <c r="E110" s="3" t="n"/>
+      <c r="F110" s="3" t="n">
+        <v>4072.21</v>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>57,897.84 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>06-06-2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/140288398543/DR/73374590/PUNB/7337459005@pty</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr"/>
+      <c r="E111" s="3" t="n">
+        <v>64.16</v>
+      </c>
+      <c r="F111" s="3" t="n"/>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>57,833.68 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07-06-2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606076667/CR</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr"/>
+      <c r="E112" s="3" t="n"/>
+      <c r="F112" s="3" t="n">
+        <v>15703.64</v>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>73,537.32 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07-06-2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/789123891023/CR/CUSTOMER REFUND REVERSAL</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr"/>
+      <c r="E113" s="3" t="n"/>
+      <c r="F113" s="3" t="n">
+        <v>704.9</v>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>74,242.22 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>08-06-2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606083068/CR</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr"/>
+      <c r="E114" s="3" t="n"/>
+      <c r="F114" s="3" t="n">
+        <v>7571.62</v>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>81,813.84 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>08-06-2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>PRINTING BARCODE LABELS &amp; BILLING ROLLS</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr"/>
+      <c r="E115" s="3" t="n">
+        <v>3269.19</v>
+      </c>
+      <c r="F115" s="3" t="n"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>78,544.65 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>08-06-2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr"/>
+      <c r="E116" s="3" t="n"/>
+      <c r="F116" s="3" t="n">
+        <v>1219.68</v>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>79,764.33 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>08-06-2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/143302589531/DR/Zomato87/AIRP/Zomato8759546.</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr"/>
+      <c r="E117" s="3" t="n">
+        <v>188.92</v>
+      </c>
+      <c r="F117" s="3" t="n"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>79,575.41 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>09-06-2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606091208/CR</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr"/>
+      <c r="E118" s="3" t="n"/>
+      <c r="F118" s="3" t="n">
+        <v>9183.440000000001</v>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>88,758.85 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>09-06-2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/619283019283/DR/D-MART/HDFC/dmart@hdfc</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr"/>
+      <c r="E119" s="3" t="n">
+        <v>3763.51</v>
+      </c>
+      <c r="F119" s="3" t="n"/>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>84,995.34 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>09-06-2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/140515780706/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr"/>
+      <c r="E120" s="3" t="n">
+        <v>359.02</v>
+      </c>
+      <c r="F120" s="3" t="n"/>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>84,636.32 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606103270/CR</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr"/>
+      <c r="E121" s="3" t="n"/>
+      <c r="F121" s="3" t="n">
+        <v>9350.799999999999</v>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>93,987.12 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/619283019283/DR/D-MART/HDFC/dmart@hdfc</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr"/>
+      <c r="E122" s="3" t="n">
+        <v>3297.51</v>
+      </c>
+      <c r="F122" s="3" t="n"/>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>90,689.61 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE STAFF WAGES &amp; PACKING CREW</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr"/>
+      <c r="E123" s="3" t="n">
+        <v>32555.85</v>
+      </c>
+      <c r="F123" s="3" t="n"/>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>58,133.76 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>GST ADVANCE TAX DEPOSIT / GOVT OF INDIA</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr"/>
+      <c r="E124" s="3" t="n">
+        <v>18989.77</v>
+      </c>
+      <c r="F124" s="3" t="n"/>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>39,143.99 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>11-06-2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606114093/CR</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr"/>
+      <c r="E125" s="3" t="n"/>
+      <c r="F125" s="3" t="n">
+        <v>5177.96</v>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>44,321.95 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>11-06-2026</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/998877665544/DR/PAYTM QR VENDOR</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr"/>
+      <c r="E126" s="3" t="n">
+        <v>53.23</v>
+      </c>
+      <c r="F126" s="3" t="n"/>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>44,268.72 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>12-06-2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606123080/CR</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr"/>
+      <c r="E127" s="3" t="n"/>
+      <c r="F127" s="3" t="n">
+        <v>9653.57</v>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>53,922.29 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>12-06-2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/443322110099/CR/PROMO DISCOUNT CREDIT</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr"/>
+      <c r="E128" s="3" t="n"/>
+      <c r="F128" s="3" t="n">
+        <v>76.15000000000001</v>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>53,998.44 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>12-06-2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>DELIVERY ELECTRIC VAN MAINTENANCE &amp; AMC</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr"/>
+      <c r="E129" s="3" t="n">
+        <v>3726.97</v>
+      </c>
+      <c r="F129" s="3" t="n"/>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>50,271.47 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>12-06-2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/512938102938/CR/SUPPLIER CREDIT NOTE</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr"/>
+      <c r="E130" s="3" t="n"/>
+      <c r="F130" s="3" t="n">
+        <v>5855.7</v>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>56,127.17 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>12-06-2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>GOOGLE WORKSPACE &amp; SLACK CLOUD SUITE</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr"/>
+      <c r="E131" s="3" t="n">
+        <v>5895.97</v>
+      </c>
+      <c r="F131" s="3" t="n"/>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>50,231.20 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>12-06-2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr"/>
+      <c r="E132" s="3" t="n">
+        <v>6872.99</v>
+      </c>
+      <c r="F132" s="3" t="n"/>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>43,358.21 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>12-06-2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/143302589531/DR/Zomato87/AIRP/Zomato8759546.</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr"/>
+      <c r="E133" s="3" t="n">
+        <v>151.47</v>
+      </c>
+      <c r="F133" s="3" t="n"/>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>43,206.74 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>12-06-2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE CHARGE / MINIMUM BALANCE FEE</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr"/>
+      <c r="E134" s="3" t="n">
+        <v>213.31</v>
+      </c>
+      <c r="F134" s="3" t="n"/>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>42,993.43 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>13-06-2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606136788/CR</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr"/>
+      <c r="E135" s="3" t="n"/>
+      <c r="F135" s="3" t="n">
+        <v>11772.98</v>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>54,766.41 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>13-06-2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/982301928371/CR/LOCAL VENDOR/ICIC/vendor@icici</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr"/>
+      <c r="E136" s="3" t="n"/>
+      <c r="F136" s="3" t="n">
+        <v>4253.34</v>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>59,019.75 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>13-06-2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/758331734676/DR/EKNATHB/YESB/ Q440089343@yb</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr"/>
+      <c r="E137" s="3" t="n">
+        <v>103.48</v>
+      </c>
+      <c r="F137" s="3" t="n"/>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>58,916.27 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>13-06-2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>POINT OF SALE (POS) HARDWARE RENTAL</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr"/>
+      <c r="E138" s="3" t="n">
+        <v>2463.21</v>
+      </c>
+      <c r="F138" s="3" t="n"/>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>56,453.06 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>13-06-2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>DELIVERY FLEET FUEL &amp; DIESEL RECHARGE</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr"/>
+      <c r="E139" s="3" t="n">
+        <v>5684.57</v>
+      </c>
+      <c r="F139" s="3" t="n"/>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>50,768.49 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>14-06-2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606147646/CR</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr"/>
+      <c r="E140" s="3" t="n"/>
+      <c r="F140" s="3" t="n">
+        <v>7020.13</v>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>57,788.62 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>14-06-2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE CHARGE / MINIMUM BALANCE FEE</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr"/>
+      <c r="E141" s="3" t="n">
+        <v>246.16</v>
+      </c>
+      <c r="F141" s="3" t="n"/>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>57,542.46 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>14-06-2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/455944913251/DR/KEMSARAP/SBIN/ 8977604821@yb</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr"/>
+      <c r="E142" s="3" t="n">
+        <v>212.94</v>
+      </c>
+      <c r="F142" s="3" t="n"/>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>57,329.52 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>14-06-2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/140288398543/DR/73374590/PUNB/7337459005@pty</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr"/>
+      <c r="E143" s="3" t="n">
+        <v>135.36</v>
+      </c>
+      <c r="F143" s="3" t="n"/>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>57,194.16 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>14-06-2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/857830578859/DR/GAURAV S/YESB/ Q815875629@yb</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr"/>
+      <c r="E144" s="3" t="n">
+        <v>254.51</v>
+      </c>
+      <c r="F144" s="3" t="n"/>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>56,939.65 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606153064/CR</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr"/>
+      <c r="E145" s="3" t="n"/>
+      <c r="F145" s="3" t="n">
+        <v>8682.1</v>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>65,621.75 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/278079065373/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr"/>
+      <c r="E146" s="3" t="n">
+        <v>565.22</v>
+      </c>
+      <c r="F146" s="3" t="n"/>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>65,056.53 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>16-06-2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606161887/CR</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr"/>
+      <c r="E147" s="3" t="n"/>
+      <c r="F147" s="3" t="n">
+        <v>6031.9</v>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>71,088.43 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>16-06-2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>BESCOM POWER UTILITY / BANGALORE WAREHOUSE</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr"/>
+      <c r="E148" s="3" t="n">
+        <v>11700.54</v>
+      </c>
+      <c r="F148" s="3" t="n"/>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>59,387.89 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>17-06-2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606172802/CR</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr"/>
+      <c r="E149" s="3" t="n"/>
+      <c r="F149" s="3" t="n">
+        <v>9780.049999999999</v>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>69,167.94 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>17-06-2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/776655443322/CR/CASHBACK REWARD</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr"/>
+      <c r="E150" s="3" t="n"/>
+      <c r="F150" s="3" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>69,187.10 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>17-06-2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/026544681447/DR/SHANTIP/YESB/ Q707874078@yb</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr"/>
+      <c r="E151" s="3" t="n">
+        <v>402.4</v>
+      </c>
+      <c r="F151" s="3" t="n"/>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>68,784.70 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>18-06-2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606186459/CR</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr"/>
+      <c r="E152" s="3" t="n"/>
+      <c r="F152" s="3" t="n">
+        <v>11678.21</v>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>80,462.91 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>18-06-2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/701074556047/DR/73374590/PUNB/7337459005@pty</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr"/>
+      <c r="E153" s="3" t="n">
+        <v>200.33</v>
+      </c>
+      <c r="F153" s="3" t="n"/>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>80,262.58 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>19-06-2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606199705/CR</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr"/>
+      <c r="E154" s="3" t="n"/>
+      <c r="F154" s="3" t="n">
+        <v>7785.64</v>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>88,048.22 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>19-06-2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/857830578859/DR/GAURAV S/YESB/ Q815875629@yb</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr"/>
+      <c r="E155" s="3" t="n">
+        <v>198.66</v>
+      </c>
+      <c r="F155" s="3" t="n"/>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>87,849.56 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>19-06-2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/278079065373/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr"/>
+      <c r="E156" s="3" t="n">
+        <v>524.3</v>
+      </c>
+      <c r="F156" s="3" t="n"/>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>87,325.26 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>20-06-2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606204313/CR</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr"/>
+      <c r="E157" s="3" t="n"/>
+      <c r="F157" s="3" t="n">
+        <v>11335.82</v>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>98,661.08 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>20-06-2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>DELIVERY ELECTRIC VAN MAINTENANCE &amp; AMC</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr"/>
+      <c r="E158" s="3" t="n">
+        <v>3052.23</v>
+      </c>
+      <c r="F158" s="3" t="n"/>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>95,608.85 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>20-06-2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/221100998877/DR/UBER RIDE</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr"/>
+      <c r="E159" s="3" t="n">
+        <v>323.58</v>
+      </c>
+      <c r="F159" s="3" t="n"/>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>95,285.27 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>21-06-2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606219852/CR</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr"/>
+      <c r="E160" s="3" t="n"/>
+      <c r="F160" s="3" t="n">
+        <v>10793.98</v>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>106,079.25 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>21-06-2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/539631629714/CR/TAIESWA/PPIW/6302476334.wal</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr"/>
+      <c r="E161" s="3" t="n"/>
+      <c r="F161" s="3" t="n">
+        <v>207.88</v>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>106,287.13 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>21-06-2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>COMMERCIAL WAREHOUSE RENT / KORAMANGALA HUB</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr"/>
+      <c r="E162" s="3" t="n">
+        <v>36853.91</v>
+      </c>
+      <c r="F162" s="3" t="n"/>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>69,433.22 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>21-06-2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>DELIVERY ELECTRIC VAN MAINTENANCE &amp; AMC</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr"/>
+      <c r="E163" s="3" t="n">
+        <v>3216.26</v>
+      </c>
+      <c r="F163" s="3" t="n"/>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>66,216.96 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>21-06-2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/637338636405/CR/PITCHIKA/SBIN/ 8919861154@yb</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr"/>
+      <c r="E164" s="3" t="n"/>
+      <c r="F164" s="3" t="n">
+        <v>3734.28</v>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>69,951.24 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>21-06-2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/312938102938/DR/ZEPTO/YESB/zepto@yb</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr"/>
+      <c r="E165" s="3" t="n">
+        <v>617.0599999999999</v>
+      </c>
+      <c r="F165" s="3" t="n"/>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>69,334.18 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606221676/CR</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr"/>
+      <c r="E166" s="3" t="n"/>
+      <c r="F166" s="3" t="n">
+        <v>689.92</v>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>70,024.10 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/539631629714/CR/TAIESWA/PPIW/6302476334.wal</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr"/>
+      <c r="E167" s="3" t="n"/>
+      <c r="F167" s="3" t="n">
+        <v>363.48</v>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>70,387.58 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>GST ADVANCE TAX DEPOSIT / GOVT OF INDIA</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr"/>
+      <c r="E168" s="3" t="n">
+        <v>16806.34</v>
+      </c>
+      <c r="F168" s="3" t="n"/>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>53,581.24 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/412938102938/DR/BIGBASKET/ICIC/bb@icici</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr"/>
+      <c r="E169" s="3" t="n">
+        <v>1565.6</v>
+      </c>
+      <c r="F169" s="3" t="n"/>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>52,015.64 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr"/>
+      <c r="E170" s="3" t="n"/>
+      <c r="F170" s="3" t="n">
+        <v>1336.66</v>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>53,352.30 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>23-06-2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606232774/CR</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr"/>
+      <c r="E171" s="3" t="n"/>
+      <c r="F171" s="3" t="n">
+        <v>10325</v>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>63,677.30 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>23-06-2026</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/800823341214/CR/PITCHIKA/CNRB/ umanag9712@ax</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr"/>
+      <c r="E172" s="3" t="n"/>
+      <c r="F172" s="3" t="n">
+        <v>4523.15</v>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>68,200.45 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>23-06-2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>NEFT/INWARD/CITI/GROCERY WHOLESALE REBATE</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr"/>
+      <c r="E173" s="3" t="n"/>
+      <c r="F173" s="3" t="n">
+        <v>7913.1</v>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>76,113.55 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>23-06-2026</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/800823341214/CR/PITCHIKA/CNRB/ umanag9712@ax</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr"/>
+      <c r="E174" s="3" t="n"/>
+      <c r="F174" s="3" t="n">
+        <v>4445.4</v>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>80,558.95 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>23-06-2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/278079065373/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr"/>
+      <c r="E175" s="3" t="n">
+        <v>453.95</v>
+      </c>
+      <c r="F175" s="3" t="n"/>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>80,105.00 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606244888/CR</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr"/>
+      <c r="E176" s="3" t="n"/>
+      <c r="F176" s="3" t="n">
+        <v>15267.23</v>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>95,372.23 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/124934775512/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr"/>
+      <c r="E177" s="3" t="n">
+        <v>500.11</v>
+      </c>
+      <c r="F177" s="3" t="n"/>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>94,872.12 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>NEFT/OUTWARD/UTI MUTUAL FUND SIP</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr"/>
+      <c r="E178" s="3" t="n">
+        <v>4864.39</v>
+      </c>
+      <c r="F178" s="3" t="n"/>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>90,007.73 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606251372/CR</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr"/>
+      <c r="E179" s="3" t="n"/>
+      <c r="F179" s="3" t="n">
+        <v>7398.4</v>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>97,406.13 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>INVENTORY AUDITOR &amp; CA LEGAL RETAINER</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr"/>
+      <c r="E180" s="3" t="n">
+        <v>14217.34</v>
+      </c>
+      <c r="F180" s="3" t="n"/>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>83,188.79 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/140515780706/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr"/>
+      <c r="E181" s="3" t="n">
+        <v>90.97</v>
+      </c>
+      <c r="F181" s="3" t="n"/>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>83,097.82 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>26-06-2026</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606266668/CR</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr"/>
+      <c r="E182" s="3" t="n"/>
+      <c r="F182" s="3" t="n">
+        <v>8108.59</v>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>91,206.41 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>26-06-2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/124934775512/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr"/>
+      <c r="E183" s="3" t="n">
+        <v>492.09</v>
+      </c>
+      <c r="F183" s="3" t="n"/>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>90,714.32 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>26-06-2026</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/140515780706/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr"/>
+      <c r="E184" s="3" t="n">
+        <v>330.74</v>
+      </c>
+      <c r="F184" s="3" t="n"/>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>90,383.58 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>27-06-2026</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606278681/CR</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr"/>
+      <c r="E185" s="3" t="n"/>
+      <c r="F185" s="3" t="n">
+        <v>1915.86</v>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>92,299.44 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>27-06-2026</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/322671730620/CR/PITCHIKA/SBIN/ 8919861154@ax</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr"/>
+      <c r="E186" s="3" t="n"/>
+      <c r="F186" s="3" t="n">
+        <v>3514.36</v>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>95,813.80 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>27-06-2026</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>FIRE SAFETY INSPECTION &amp; EQUIPMENT REFILL</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr"/>
+      <c r="E187" s="3" t="n">
+        <v>4165.51</v>
+      </c>
+      <c r="F187" s="3" t="n"/>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>91,648.29 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>27-06-2026</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/172136536211/DR/ZOMATO L/YESB/zomato-order@p</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr"/>
+      <c r="E188" s="3" t="n">
+        <v>174.24</v>
+      </c>
+      <c r="F188" s="3" t="n"/>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>91,474.05 Cr</t>
         </is>
       </c>
     </row>

--- a/generated_data/bank_statement_union_bank.xlsx
+++ b/generated_data/bank_statement_union_bank.xlsx
@@ -501,17 +501,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605013162/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605018255/CR</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n">
-        <v>10816.01</v>
+        <v>12452.79</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>20,816.01 Cr</t>
+          <t>22,452.79 Cr</t>
         </is>
       </c>
     </row>
@@ -526,17 +526,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/112938102938/CR/WHOLESALE MILK DEPOSIT</t>
+          <t>UPIAB/271988123471/CR/THIRUVEE/UBIN/9391652831-2@a</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n">
-        <v>4307.46</v>
+        <v>588.63</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>25,123.47 Cr</t>
+          <t>23,041.42 Cr</t>
         </is>
       </c>
     </row>
@@ -551,17 +551,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SERVICE CHARGE / MINIMUM BALANCE FEE</t>
+          <t>UPIAR/685013228668/DR/LHEMANT/HDFC/hemanth0508@yb</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="3" t="n">
-        <v>466.42</v>
+        <v>86.39</v>
       </c>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,657.05 Cr</t>
+          <t>22,955.03 Cr</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>02-05-2026</t>
+          <t>01-05-2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605024216/CR</t>
+          <t>UPIAR/717134959917/DR/AoapAmr/AIRP/AoapAmrita.pay</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n">
-        <v>12025.72</v>
-      </c>
+      <c r="E5" s="3" t="n">
+        <v>4146.82</v>
+      </c>
+      <c r="F5" s="3" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,682.77 Cr</t>
+          <t>18,808.21 Cr</t>
         </is>
       </c>
     </row>
@@ -596,22 +596,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>03-05-2026</t>
+          <t>02-05-2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605032800/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605028468/CR</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n">
-        <v>13395.87</v>
+        <v>9710.4</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>50,078.64 Cr</t>
+          <t>28,518.61 Cr</t>
         </is>
       </c>
     </row>
@@ -621,22 +621,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>03-05-2026</t>
+          <t>02-05-2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>BESCOM POWER UTILITY / BANGALORE WAREHOUSE</t>
+          <t>IMPS/INWARD/SBIN/DISTRIBUTOR SETTLEMENT</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="3" t="n">
-        <v>16770.07</v>
-      </c>
-      <c r="F7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n">
+        <v>24202.31</v>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,308.57 Cr</t>
+          <t>52,720.92 Cr</t>
         </is>
       </c>
     </row>
@@ -646,22 +646,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04-05-2026</t>
+          <t>02-05-2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605041826/CR</t>
+          <t>UPIAR/373995020793/DR/LHEMANT/HDFC/hemanth0508@yb</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n">
-        <v>4490.83</v>
-      </c>
+      <c r="E8" s="3" t="n">
+        <v>1794.33</v>
+      </c>
+      <c r="F8" s="3" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>37,799.40 Cr</t>
+          <t>50,926.59 Cr</t>
         </is>
       </c>
     </row>
@@ -671,22 +671,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04-05-2026</t>
+          <t>02-05-2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DELIVERY FLEET FUEL &amp; DIESEL RECHARGE</t>
+          <t>UPIAR/172136536211/DR/ZOMATO L/YESB/zomato-order@p</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="3" t="n">
-        <v>8083.46</v>
+        <v>292.4</v>
       </c>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,715.94 Cr</t>
+          <t>50,634.19 Cr</t>
         </is>
       </c>
     </row>
@@ -696,22 +696,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>04-05-2026</t>
+          <t>02-05-2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
+          <t>UPIAR/347067657684/DR/KAJALVI/YESB/paytm.s1w3jr9@</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n">
-        <v>720.24</v>
-      </c>
+      <c r="E10" s="3" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="F10" s="3" t="n"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>30,436.18 Cr</t>
+          <t>50,606.89 Cr</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>05-05-2026</t>
+          <t>03-05-2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605054269/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605035098/CR</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n">
-        <v>10255.65</v>
+        <v>5962.59</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,691.83 Cr</t>
+          <t>56,569.48 Cr</t>
         </is>
       </c>
     </row>
@@ -746,22 +746,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>05-05-2026</t>
+          <t>03-05-2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/124934775512/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+          <t>PACKAGING SUPPLIES / ECO CORRUGATED BOXES</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="3" t="n">
-        <v>497.88</v>
+        <v>19389.03</v>
       </c>
       <c r="F12" s="3" t="n"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>40,193.95 Cr</t>
+          <t>37,180.45 Cr</t>
         </is>
       </c>
     </row>
@@ -771,22 +771,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>05-05-2026</t>
+          <t>04-05-2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/789123891023/CR/CUSTOMER REFUND REVERSAL</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605041954/CR</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n">
-        <v>564.48</v>
+        <v>13287.64</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>40,758.43 Cr</t>
+          <t>50,468.09 Cr</t>
         </is>
       </c>
     </row>
@@ -796,22 +796,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>06-05-2026</t>
+          <t>04-05-2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605064476/CR</t>
+          <t>UPIAR/719421374678/DR/NEWKRSN/YESB/paytmqr6a0ixr@</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n">
-        <v>10372.41</v>
-      </c>
+      <c r="E14" s="3" t="n">
+        <v>108.61</v>
+      </c>
+      <c r="F14" s="3" t="n"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>51,130.84 Cr</t>
+          <t>50,359.48 Cr</t>
         </is>
       </c>
     </row>
@@ -821,22 +821,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>06-05-2026</t>
+          <t>05-05-2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>INVENTORY AUDITOR &amp; CA LEGAL RETAINER</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605057169/CR</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="3" t="n">
-        <v>11140.38</v>
-      </c>
-      <c r="F15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n">
+        <v>7208.68</v>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>39,990.46 Cr</t>
+          <t>57,568.16 Cr</t>
         </is>
       </c>
     </row>
@@ -846,22 +846,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>06-05-2026</t>
+          <t>05-05-2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>SERVICE CHARGE / MINIMUM BALANCE FEE</t>
+          <t>NEFT/OUTWARD/UTI MUTUAL FUND SIP</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="3" t="n">
-        <v>413.41</v>
+        <v>6383.3</v>
       </c>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>39,577.05 Cr</t>
+          <t>51,184.86 Cr</t>
         </is>
       </c>
     </row>
@@ -876,17 +876,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>INVENTORY AUDITOR &amp; CA LEGAL RETAINER</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605068982/CR</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="3" t="n">
-        <v>17799.43</v>
-      </c>
-      <c r="F17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n">
+        <v>7932.09</v>
+      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,777.62 Cr</t>
+          <t>59,116.95 Cr</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>NEFT/OUTWARD/HDFC/FARMERS COOP SUPPLY</t>
+          <t>NEFT/OUTWARD/UTI MUTUAL FUND SIP</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="3" t="n">
-        <v>17987.92</v>
+        <v>8540.549999999999</v>
       </c>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,789.70 Cr</t>
+          <t>50,576.40 Cr</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/026544681447/DR/SHANTIP/YESB/ Q707874078@yb</t>
+          <t>UPIAR/998877665544/DR/PAYTM QR VENDOR</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="3" t="n">
-        <v>469.4</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="F19" s="3" t="n"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,320.30 Cr</t>
+          <t>50,509.89 Cr</t>
         </is>
       </c>
     </row>
@@ -946,22 +946,22 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>07-05-2026</t>
+          <t>06-05-2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605075384/CR</t>
+          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n">
-        <v>12685.01</v>
-      </c>
+      <c r="E20" s="3" t="n">
+        <v>7734.65</v>
+      </c>
+      <c r="F20" s="3" t="n"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>16,005.31 Cr</t>
+          <t>42,775.24 Cr</t>
         </is>
       </c>
     </row>
@@ -971,22 +971,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>07-05-2026</t>
+          <t>06-05-2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>SWIGGY INSTAMART FLEET REIMBURSEMENT</t>
+          <t>IMPS/OUTWARD/612984019283/RAW INGREDIENTS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="3" t="n">
-        <v>608.86</v>
+        <v>23537.82</v>
       </c>
       <c r="F21" s="3" t="n"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,396.45 Cr</t>
+          <t>19,237.42 Cr</t>
         </is>
       </c>
     </row>
@@ -996,22 +996,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08-05-2026</t>
+          <t>07-05-2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605088700/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605074413/CR</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n">
-        <v>10408.6</v>
+        <v>12175.38</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>25,805.05 Cr</t>
+          <t>31,412.80 Cr</t>
         </is>
       </c>
     </row>
@@ -1026,17 +1026,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/776655443322/CR/CASHBACK REWARD</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605086180/CR</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n">
-        <v>39.63</v>
+        <v>12375.57</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>25,844.68 Cr</t>
+          <t>43,788.37 Cr</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>BESCOM POWER UTILITY / BANGALORE WAREHOUSE</t>
+          <t>NEFT/OUTWARD/UTI MUTUAL FUND SIP</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="3" t="n">
-        <v>12505.11</v>
+        <v>5952.13</v>
       </c>
       <c r="F24" s="3" t="n"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13,339.57 Cr</t>
+          <t>37,836.24 Cr</t>
         </is>
       </c>
     </row>
@@ -1071,22 +1071,22 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>08-05-2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/235911221570/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605095735/CR</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
-      <c r="E25" s="3" t="n">
-        <v>82.56</v>
-      </c>
-      <c r="F25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n">
+        <v>5040.3</v>
+      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>13,257.01 Cr</t>
+          <t>42,876.54 Cr</t>
         </is>
       </c>
     </row>
@@ -1096,22 +1096,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08-05-2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>INVENTORY AUDITOR &amp; CA LEGAL RETAINER</t>
+          <t>UPIAB/800823341214/CR/PITCHIKA/CNRB/ umanag9712@ax</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="3" t="n">
-        <v>15776.97</v>
-      </c>
-      <c r="F26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n">
+        <v>2216.11</v>
+      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-2,519.96 Cr</t>
+          <t>45,092.65 Cr</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08-05-2026</t>
+          <t>10-05-2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>NEFT/OUTWARD/UTI MUTUAL FUND SIP</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605104553/CR</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
-      <c r="E27" s="3" t="n">
-        <v>9725.700000000001</v>
-      </c>
-      <c r="F27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n">
+        <v>7888.35</v>
+      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-12,245.66 Cr</t>
+          <t>52,981.00 Cr</t>
         </is>
       </c>
     </row>
@@ -1146,22 +1146,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>11-05-2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605098828/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605112946/CR</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="n">
-        <v>8984.120000000001</v>
+        <v>12573.94</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-3,261.54 Cr</t>
+          <t>65,554.94 Cr</t>
         </is>
       </c>
     </row>
@@ -1171,22 +1171,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>11-05-2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>ATM CASH WITHDRAWAL / KORAMANGALA BRANCH</t>
+          <t>UPIAR/719421374678/DR/NEWKRSN/YESB/paytmqr6a0ixr@</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="3" t="n">
-        <v>8343.690000000001</v>
+        <v>212.1</v>
       </c>
       <c r="F29" s="3" t="n"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-11,605.23 Cr</t>
+          <t>65,342.84 Cr</t>
         </is>
       </c>
     </row>
@@ -1196,22 +1196,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>11-05-2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/685013228668/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="3" t="n">
-        <v>53.94</v>
-      </c>
-      <c r="F30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n">
+        <v>658.0599999999999</v>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-11,659.17 Cr</t>
+          <t>66,000.90 Cr</t>
         </is>
       </c>
     </row>
@@ -1221,22 +1221,22 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>12-05-2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/322671730620/CR/PITCHIKA/SBIN/ 8919861154@ax</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605126218/CR</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n">
-        <v>883.21</v>
+        <v>7986.2</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-10,775.96 Cr</t>
+          <t>73,987.10 Cr</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>12-05-2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
+          <t>UPIAR/077728365159/DR/NAMBURI /YESB/ Q501702001@yb</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="3" t="n">
-        <v>10247.9</v>
+        <v>62.94</v>
       </c>
       <c r="F32" s="3" t="n"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-21,023.86 Cr</t>
+          <t>73,924.16 Cr</t>
         </is>
       </c>
     </row>
@@ -1271,22 +1271,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10-05-2026</t>
+          <t>12-05-2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605101746/CR</t>
+          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="n">
-        <v>10132.16</v>
+        <v>1111.27</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-10,891.70 Cr</t>
+          <t>75,035.43 Cr</t>
         </is>
       </c>
     </row>
@@ -1296,22 +1296,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>10-05-2026</t>
+          <t>12-05-2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>AIRTEL CORPORATE BROADBAND &amp; FIBER</t>
+          <t>UPIAR/412938102938/DR/BIGBASKET/ICIC/bb@icici</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="3" t="n">
-        <v>2084.39</v>
+        <v>763.9299999999999</v>
       </c>
       <c r="F34" s="3" t="n"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-12,976.09 Cr</t>
+          <t>74,271.50 Cr</t>
         </is>
       </c>
     </row>
@@ -1321,22 +1321,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>10-05-2026</t>
+          <t>13-05-2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/717134959917/DR/AoapAmr/AIRP/AoapAmrita.pay</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605133440/CR</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
-      <c r="E35" s="3" t="n">
-        <v>2449.44</v>
-      </c>
-      <c r="F35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n">
+        <v>11571.21</v>
+      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-15,425.53 Cr</t>
+          <t>85,842.71 Cr</t>
         </is>
       </c>
     </row>
@@ -1346,22 +1346,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>11-05-2026</t>
+          <t>13-05-2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605116013/CR</t>
+          <t>UPIAR/110099887766/DR/OLA CABS</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n">
-        <v>9437.379999999999</v>
-      </c>
+      <c r="E36" s="3" t="n">
+        <v>268.7</v>
+      </c>
+      <c r="F36" s="3" t="n"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-5,988.15 Cr</t>
+          <t>85,574.01 Cr</t>
         </is>
       </c>
     </row>
@@ -1371,22 +1371,22 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>11-05-2026</t>
+          <t>13-05-2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/685013228668/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+          <t>UPIAR/719421374678/DR/NEWKRSN/YESB/paytmqr6a0ixr@</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="3" t="n">
-        <v>103.31</v>
+        <v>289.32</v>
       </c>
       <c r="F37" s="3" t="n"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,091.46 Cr</t>
+          <t>85,284.69 Cr</t>
         </is>
       </c>
     </row>
@@ -1396,22 +1396,22 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>12-05-2026</t>
+          <t>13-05-2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605128885/CR</t>
+          <t>UPIAR/998877665544/DR/PAYTM QR VENDOR</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n">
-        <v>10654.09</v>
-      </c>
+      <c r="E38" s="3" t="n">
+        <v>95.16</v>
+      </c>
+      <c r="F38" s="3" t="n"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>4,562.63 Cr</t>
+          <t>85,189.53 Cr</t>
         </is>
       </c>
     </row>
@@ -1421,22 +1421,22 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>12-05-2026</t>
+          <t>13-05-2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/301984712093/DR/SWIGGY/HDFC/swiggy@hdfc</t>
+          <t>UPIAR/143302589531/DR/Zomato87/AIRP/Zomato8759546.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="3" t="n">
-        <v>345.25</v>
+        <v>339.38</v>
       </c>
       <c r="F39" s="3" t="n"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>4,217.38 Cr</t>
+          <t>84,850.15 Cr</t>
         </is>
       </c>
     </row>
@@ -1446,22 +1446,22 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>12-05-2026</t>
+          <t>13-05-2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>GST ADVANCE TAX DEPOSIT / GOVT OF INDIA</t>
+          <t>UPIAB/712626244599/CR/PICHIKA/BARB/ 8985068499@ax</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="3" t="n">
-        <v>16991.3</v>
-      </c>
-      <c r="F40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n">
+        <v>1131.63</v>
+      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>-12,773.92 Cr</t>
+          <t>85,981.78 Cr</t>
         </is>
       </c>
     </row>
@@ -1471,22 +1471,22 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>12-05-2026</t>
+          <t>13-05-2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/235911221570/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+          <t>GOOGLE WORKSPACE &amp; SLACK CLOUD SUITE</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="3" t="n">
-        <v>96.94</v>
+        <v>4659.12</v>
       </c>
       <c r="F41" s="3" t="n"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-12,870.86 Cr</t>
+          <t>81,322.66 Cr</t>
         </is>
       </c>
     </row>
@@ -1496,22 +1496,22 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>13-05-2026</t>
+          <t>14-05-2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605131026/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605144249/CR</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="3" t="n"/>
       <c r="F42" s="3" t="n">
-        <v>7104.65</v>
+        <v>5884.03</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>-5,766.21 Cr</t>
+          <t>87,206.69 Cr</t>
         </is>
       </c>
     </row>
@@ -1521,22 +1521,22 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>13-05-2026</t>
+          <t>14-05-2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/443322110099/CR/PROMO DISCOUNT CREDIT</t>
+          <t>UPIAR/140515780706/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="3" t="n"/>
-      <c r="F43" s="3" t="n">
-        <v>207.94</v>
-      </c>
+      <c r="E43" s="3" t="n">
+        <v>163.12</v>
+      </c>
+      <c r="F43" s="3" t="n"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-5,558.27 Cr</t>
+          <t>87,043.57 Cr</t>
         </is>
       </c>
     </row>
@@ -1551,17 +1551,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605146410/CR</t>
+          <t>UPIAB/637338636405/CR/PITCHIKA/SBIN/ 8919861154@yb</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n">
-        <v>6736.3</v>
+        <v>1612.82</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1,178.03 Cr</t>
+          <t>88,656.39 Cr</t>
         </is>
       </c>
     </row>
@@ -1576,17 +1576,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/204208208508/DR/Zomato87/AIRP/Zomato8759546.</t>
+          <t>NEFT/INWARD/CITI/GROCERY WHOLESALE REBATE</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
-      <c r="E45" s="3" t="n">
-        <v>215.32</v>
-      </c>
-      <c r="F45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="n">
+        <v>11642.52</v>
+      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>962.71 Cr</t>
+          <t>100,298.91 Cr</t>
         </is>
       </c>
     </row>
@@ -1596,22 +1596,22 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>14-05-2026</t>
+          <t>15-05-2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>DELIVERY ELECTRIC VAN MAINTENANCE &amp; AMC</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605153990/CR</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="3" t="n">
-        <v>5183.8</v>
-      </c>
-      <c r="F46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n">
+        <v>8909.33</v>
+      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>-4,221.09 Cr</t>
+          <t>109,208.24 Cr</t>
         </is>
       </c>
     </row>
@@ -1621,22 +1621,22 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>14-05-2026</t>
+          <t>15-05-2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/322671730620/CR/PITCHIKA/SBIN/ 8919861154@ax</t>
+          <t>UPIAR/235911221570/DR/LHEMANT/HDFC/hemanth0508@yb</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
-      <c r="E47" s="3" t="n"/>
-      <c r="F47" s="3" t="n">
-        <v>4103</v>
-      </c>
+      <c r="E47" s="3" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="F47" s="3" t="n"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-118.09 Cr</t>
+          <t>109,159.18 Cr</t>
         </is>
       </c>
     </row>
@@ -1646,22 +1646,22 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14-05-2026</t>
+          <t>15-05-2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>AWS CLOUD SERVER HOSTING &amp; INFRASTRUCTURE</t>
+          <t>UPIAR/908931590719/DR/Mr Raju/YESB/ Q249677790@yb</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="3" t="n">
-        <v>6870.34</v>
+        <v>92.89</v>
       </c>
       <c r="F48" s="3" t="n"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>-6,988.43 Cr</t>
+          <t>109,066.29 Cr</t>
         </is>
       </c>
     </row>
@@ -1671,22 +1671,22 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>15-05-2026</t>
+          <t>16-05-2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605158640/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605163232/CR</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="3" t="n"/>
       <c r="F49" s="3" t="n">
-        <v>10253.64</v>
+        <v>6637.27</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>3,265.21 Cr</t>
+          <t>115,703.56 Cr</t>
         </is>
       </c>
     </row>
@@ -1696,22 +1696,22 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>15-05-2026</t>
+          <t>16-05-2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/758331734676/DR/EKNATHB/YESB/ Q440089343@yb</t>
+          <t>BBMP MUNICIPAL TRADE LICENSE &amp; PROPERTY TAX</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="3" t="n">
-        <v>176.05</v>
+        <v>6499.52</v>
       </c>
       <c r="F50" s="3" t="n"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>3,089.16 Cr</t>
+          <t>109,204.04 Cr</t>
         </is>
       </c>
     </row>
@@ -1721,22 +1721,22 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>15-05-2026</t>
+          <t>16-05-2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/908129381023/DR/BILLDESK/SBIN/billdesk@sbi</t>
+          <t>DELIVERY ELECTRIC VAN MAINTENANCE &amp; AMC</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="3" t="n">
-        <v>1103.79</v>
+        <v>2616.96</v>
       </c>
       <c r="F51" s="3" t="n"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1,985.37 Cr</t>
+          <t>106,587.08 Cr</t>
         </is>
       </c>
     </row>
@@ -1746,22 +1746,22 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>15-05-2026</t>
+          <t>17-05-2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/373995020793/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605171296/CR</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="3" t="n">
-        <v>2729.32</v>
-      </c>
-      <c r="F52" s="3" t="n"/>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="3" t="n">
+        <v>15151.11</v>
+      </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>-743.95 Cr</t>
+          <t>121,738.19 Cr</t>
         </is>
       </c>
     </row>
@@ -1771,22 +1771,22 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16-05-2026</t>
+          <t>17-05-2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605164499/CR</t>
+          <t>UPIAR/758331734676/DR/EKNATHB/YESB/ Q440089343@yb</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
-      <c r="E53" s="3" t="n"/>
-      <c r="F53" s="3" t="n">
-        <v>10174.15</v>
-      </c>
+      <c r="E53" s="3" t="n">
+        <v>227.8</v>
+      </c>
+      <c r="F53" s="3" t="n"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>9,430.20 Cr</t>
+          <t>121,510.39 Cr</t>
         </is>
       </c>
     </row>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>16-05-2026</t>
+          <t>17-05-2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>BESCOM POWER UTILITY / BANGALORE WAREHOUSE</t>
+          <t>UPIAR/857830578859/DR/GAURAV S/YESB/ Q815875629@yb</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="3" t="n">
-        <v>10774.02</v>
+        <v>305.36</v>
       </c>
       <c r="F54" s="3" t="n"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>-1,343.82 Cr</t>
+          <t>121,205.03 Cr</t>
         </is>
       </c>
     </row>
@@ -1826,17 +1826,17 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605173578/CR</t>
+          <t>COMMERCIAL WAREHOUSE RENT / KORAMANGALA HUB</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
-      <c r="E55" s="3" t="n"/>
-      <c r="F55" s="3" t="n">
-        <v>3805.31</v>
-      </c>
+      <c r="E55" s="3" t="n">
+        <v>39599.34</v>
+      </c>
+      <c r="F55" s="3" t="n"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>2,461.49 Cr</t>
+          <t>81,605.69 Cr</t>
         </is>
       </c>
     </row>
@@ -1851,17 +1851,17 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/887766554433/DR/BHARATPE MERCHANT</t>
+          <t>UPIAR/123854061954/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="3" t="n">
-        <v>55.34</v>
+        <v>203.34</v>
       </c>
       <c r="F56" s="3" t="n"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>2,406.15 Cr</t>
+          <t>81,402.35 Cr</t>
         </is>
       </c>
     </row>
@@ -1876,17 +1876,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605181258/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605187235/CR</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="3" t="n"/>
       <c r="F57" s="3" t="n">
-        <v>8387.68</v>
+        <v>5186.93</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>10,793.83 Cr</t>
+          <t>86,589.28 Cr</t>
         </is>
       </c>
     </row>
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>DELIVERY ELECTRIC VAN MAINTENANCE &amp; AMC</t>
+          <t>JNS-PMSBY-25-26-00289608474-301-631272322</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="3" t="n">
-        <v>4766.73</v>
+        <v>20</v>
       </c>
       <c r="F58" s="3" t="n"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>6,027.10 Cr</t>
+          <t>86,569.28 Cr</t>
         </is>
       </c>
     </row>
@@ -1926,17 +1926,17 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605193787/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605198712/CR</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="3" t="n"/>
       <c r="F59" s="3" t="n">
-        <v>9439.620000000001</v>
+        <v>6975.51</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>15,466.72 Cr</t>
+          <t>93,544.79 Cr</t>
         </is>
       </c>
     </row>
@@ -1951,17 +1951,17 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/332211009988/DR/BOOKMYSHOW TICKET</t>
+          <t>UPIAR/110099887766/DR/OLA CABS</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="3" t="n">
-        <v>866.45</v>
+        <v>621.14</v>
       </c>
       <c r="F60" s="3" t="n"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>14,600.27 Cr</t>
+          <t>92,923.65 Cr</t>
         </is>
       </c>
     </row>
@@ -1971,22 +1971,22 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19-05-2026</t>
+          <t>20-05-2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/026544681447/DR/SHANTIP/YESB/ Q707874078@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605205423/CR</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
-      <c r="E61" s="3" t="n">
-        <v>742.36</v>
-      </c>
-      <c r="F61" s="3" t="n"/>
+      <c r="E61" s="3" t="n"/>
+      <c r="F61" s="3" t="n">
+        <v>4983.29</v>
+      </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>13,857.91 Cr</t>
+          <t>97,906.94 Cr</t>
         </is>
       </c>
     </row>
@@ -1996,22 +1996,22 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>19-05-2026</t>
+          <t>20-05-2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>PACKAGING SUPPLIES / ECO CORRUGATED BOXES</t>
+          <t>NEFT/INWARD/CITI/GROCERY WHOLESALE REBATE</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
-      <c r="E62" s="3" t="n">
-        <v>15415.62</v>
-      </c>
-      <c r="F62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n">
+        <v>18687.69</v>
+      </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>-1,557.71 Cr</t>
+          <t>116,594.63 Cr</t>
         </is>
       </c>
     </row>
@@ -2026,17 +2026,17 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605202820/CR</t>
+          <t>OFFICE PANTRY &amp; FRESH REFRESHMENTS</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
-      <c r="E63" s="3" t="n"/>
-      <c r="F63" s="3" t="n">
-        <v>9245.799999999999</v>
-      </c>
+      <c r="E63" s="3" t="n">
+        <v>960.17</v>
+      </c>
+      <c r="F63" s="3" t="n"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>7,688.09 Cr</t>
+          <t>115,634.46 Cr</t>
         </is>
       </c>
     </row>
@@ -2046,22 +2046,22 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>20-05-2026</t>
+          <t>21-05-2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COMMERCIAL WAREHOUSE RENT / KORAMANGALA HUB</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605216690/CR</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="3" t="n">
-        <v>45885.05</v>
-      </c>
-      <c r="F64" s="3" t="n"/>
+      <c r="E64" s="3" t="n"/>
+      <c r="F64" s="3" t="n">
+        <v>6636.1</v>
+      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>-38,196.96 Cr</t>
+          <t>122,270.56 Cr</t>
         </is>
       </c>
     </row>
@@ -2071,22 +2071,22 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>20-05-2026</t>
+          <t>21-05-2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>WATER TANKER &amp; SANITATION CHARGES</t>
+          <t>SWIGGY INSTAMART FLEET REIMBURSEMENT</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
       <c r="E65" s="3" t="n">
-        <v>3485.92</v>
+        <v>1702.6</v>
       </c>
       <c r="F65" s="3" t="n"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-41,682.88 Cr</t>
+          <t>120,567.96 Cr</t>
         </is>
       </c>
     </row>
@@ -2101,17 +2101,17 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605211677/CR</t>
+          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="3" t="n"/>
-      <c r="F66" s="3" t="n">
-        <v>7109.9</v>
-      </c>
+      <c r="E66" s="3" t="n">
+        <v>11060.37</v>
+      </c>
+      <c r="F66" s="3" t="n"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>-34,572.98 Cr</t>
+          <t>109,507.59 Cr</t>
         </is>
       </c>
     </row>
@@ -2121,22 +2121,22 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>21-05-2026</t>
+          <t>22-05-2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605227673/CR</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="3" t="n"/>
       <c r="F67" s="3" t="n">
-        <v>1047.86</v>
+        <v>14365.55</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-33,525.12 Cr</t>
+          <t>123,873.14 Cr</t>
         </is>
       </c>
     </row>
@@ -2146,22 +2146,22 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>22-05-2026</t>
+          <t>23-05-2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605226697/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605233394/CR</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="3" t="n"/>
       <c r="F68" s="3" t="n">
-        <v>11263</v>
+        <v>11099.5</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>-22,262.12 Cr</t>
+          <t>134,972.64 Cr</t>
         </is>
       </c>
     </row>
@@ -2171,22 +2171,22 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>22-05-2026</t>
+          <t>23-05-2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/221100998877/DR/UBER RIDE</t>
+          <t>UPIAR/301984712093/DR/SWIGGY/HDFC/swiggy@hdfc</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
       <c r="E69" s="3" t="n">
-        <v>418.86</v>
+        <v>407.09</v>
       </c>
       <c r="F69" s="3" t="n"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-22,680.98 Cr</t>
+          <t>134,565.55 Cr</t>
         </is>
       </c>
     </row>
@@ -2196,22 +2196,22 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22-05-2026</t>
+          <t>23-05-2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/301984712093/DR/SWIGGY/HDFC/swiggy@hdfc</t>
+          <t>UPIAR/455944913251/DR/KEMSARAP/SBIN/ 8977604821@yb</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="3" t="n">
-        <v>193.98</v>
+        <v>120.82</v>
       </c>
       <c r="F70" s="3" t="n"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>-22,874.96 Cr</t>
+          <t>134,444.73 Cr</t>
         </is>
       </c>
     </row>
@@ -2226,17 +2226,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605234899/CR</t>
+          <t>UPIAR/301984712093/DR/SWIGGY/HDFC/swiggy@hdfc</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
-      <c r="E71" s="3" t="n"/>
-      <c r="F71" s="3" t="n">
-        <v>11475.61</v>
-      </c>
+      <c r="E71" s="3" t="n">
+        <v>184.84</v>
+      </c>
+      <c r="F71" s="3" t="n"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-11,399.35 Cr</t>
+          <t>134,259.89 Cr</t>
         </is>
       </c>
     </row>
@@ -2246,22 +2246,22 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>24-05-2026</t>
+          <t>23-05-2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605249678/CR</t>
+          <t>UPIAR/312938102938/DR/ZEPTO/YESB/zepto@yb</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
-      <c r="E72" s="3" t="n"/>
-      <c r="F72" s="3" t="n">
-        <v>7504.29</v>
-      </c>
+      <c r="E72" s="3" t="n">
+        <v>310.96</v>
+      </c>
+      <c r="F72" s="3" t="n"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>-3,895.06 Cr</t>
+          <t>133,948.93 Cr</t>
         </is>
       </c>
     </row>
@@ -2271,22 +2271,22 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>24-05-2026</t>
+          <t>23-05-2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>PRINTING BARCODE LABELS &amp; BILLING ROLLS</t>
+          <t>UPIAB/637338636405/CR/PITCHIKA/SBIN/ 8919861154@yb</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
-      <c r="E73" s="3" t="n">
-        <v>1536.43</v>
-      </c>
-      <c r="F73" s="3" t="n"/>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="n">
+        <v>1485.51</v>
+      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-5,431.49 Cr</t>
+          <t>135,434.44 Cr</t>
         </is>
       </c>
     </row>
@@ -2301,17 +2301,17 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/512938102938/CR/SUPPLIER CREDIT NOTE</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605249014/CR</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="3" t="n"/>
       <c r="F74" s="3" t="n">
-        <v>4734.16</v>
+        <v>9696.25</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>-697.33 Cr</t>
+          <t>145,130.69 Cr</t>
         </is>
       </c>
     </row>
@@ -2326,17 +2326,17 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>EMPLOYEE FIELD COMMUTE &amp; TRAVEL REIMBURSEMENT</t>
+          <t>ATM CASH WITHDRAWAL / KORAMANGALA BRANCH</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" s="3" t="n">
-        <v>6588.48</v>
+        <v>7475.64</v>
       </c>
       <c r="F75" s="3" t="n"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-7,285.81 Cr</t>
+          <t>137,655.05 Cr</t>
         </is>
       </c>
     </row>
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/665544332211/DR/AMAZON INDIA</t>
+          <t>UPIAB/624556864731/CR/PICHIKA/UBIN/pvasuviswanadh</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
-      <c r="E76" s="3" t="n">
-        <v>1829.21</v>
-      </c>
-      <c r="F76" s="3" t="n"/>
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="3" t="n">
+        <v>2844.64</v>
+      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>-9,115.02 Cr</t>
+          <t>140,499.69 Cr</t>
         </is>
       </c>
     </row>
@@ -2371,22 +2371,22 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>25-05-2026</t>
+          <t>24-05-2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605259390/CR</t>
+          <t>NEFT/OUTWARD/HDFC/FARMERS COOP SUPPLY</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
-      <c r="E77" s="3" t="n"/>
-      <c r="F77" s="3" t="n">
-        <v>9667.59</v>
-      </c>
+      <c r="E77" s="3" t="n">
+        <v>21572.11</v>
+      </c>
+      <c r="F77" s="3" t="n"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>552.57 Cr</t>
+          <t>118,927.58 Cr</t>
         </is>
       </c>
     </row>
@@ -2396,22 +2396,22 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>25-05-2026</t>
+          <t>24-05-2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>SWIGGY INSTAMART FLEET REIMBURSEMENT</t>
+          <t>UPIAR/998877665544/DR/PAYTM QR VENDOR</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="3" t="n">
-        <v>1115.26</v>
+        <v>163.58</v>
       </c>
       <c r="F78" s="3" t="n"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>-562.69 Cr</t>
+          <t>118,764.00 Cr</t>
         </is>
       </c>
     </row>
@@ -2426,17 +2426,17 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>PACKAGING SUPPLIES / ECO CORRUGATED BOXES</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605256403/CR</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
-      <c r="E79" s="3" t="n">
-        <v>12411.45</v>
-      </c>
-      <c r="F79" s="3" t="n"/>
+      <c r="E79" s="3" t="n"/>
+      <c r="F79" s="3" t="n">
+        <v>4013.1</v>
+      </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-12,974.14 Cr</t>
+          <t>122,777.10 Cr</t>
         </is>
       </c>
     </row>
@@ -2451,17 +2451,17 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>POINT OF SALE (POS) HARDWARE RENTAL</t>
+          <t>UPIAR/685013228668/DR/LHEMANT/HDFC/hemanth0508@yb</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="3" t="n">
-        <v>2566.97</v>
+        <v>124.3</v>
       </c>
       <c r="F80" s="3" t="n"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>-15,541.11 Cr</t>
+          <t>122,652.80 Cr</t>
         </is>
       </c>
     </row>
@@ -2476,17 +2476,17 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/172136536211/DR/ZOMATO L/YESB/zomato-order@p</t>
+          <t>INVENTORY AUDITOR &amp; CA LEGAL RETAINER</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" s="3" t="n">
-        <v>579.47</v>
+        <v>17355.65</v>
       </c>
       <c r="F81" s="3" t="n"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-16,120.58 Cr</t>
+          <t>105,297.15 Cr</t>
         </is>
       </c>
     </row>
@@ -2501,17 +2501,17 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605262378/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605263702/CR</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="3" t="n"/>
       <c r="F82" s="3" t="n">
-        <v>7075.66</v>
+        <v>5182.12</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>-9,044.92 Cr</t>
+          <t>110,479.27 Cr</t>
         </is>
       </c>
     </row>
@@ -2526,17 +2526,17 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>LIC PREMIUM AUTO DEBIT CLEARING</t>
+          <t>UPIAR/077728365159/DR/NAMBURI /YESB/ Q501702001@yb</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="3" t="n">
-        <v>4023.86</v>
+        <v>60.88</v>
       </c>
       <c r="F83" s="3" t="n"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-13,068.78 Cr</t>
+          <t>110,418.39 Cr</t>
         </is>
       </c>
     </row>
@@ -2551,17 +2551,17 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/539631629714/CR/TAIESWA/PPIW/6302476334.wal</t>
+          <t>POINT OF SALE (POS) HARDWARE RENTAL</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
-      <c r="E84" s="3" t="n"/>
-      <c r="F84" s="3" t="n">
-        <v>203.49</v>
-      </c>
+      <c r="E84" s="3" t="n">
+        <v>2075.18</v>
+      </c>
+      <c r="F84" s="3" t="n"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>-12,865.29 Cr</t>
+          <t>108,343.21 Cr</t>
         </is>
       </c>
     </row>
@@ -2576,17 +2576,17 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605271436/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605277184/CR</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="3" t="n"/>
       <c r="F85" s="3" t="n">
-        <v>6030.7</v>
+        <v>10293.27</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-6,834.59 Cr</t>
+          <t>118,636.48 Cr</t>
         </is>
       </c>
     </row>
@@ -2601,17 +2601,17 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/712626244599/CR/PICHIKA/BARB/ 8985068499@ax</t>
+          <t>GST ADVANCE TAX DEPOSIT / GOVT OF INDIA</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
-      <c r="E86" s="3" t="n"/>
-      <c r="F86" s="3" t="n">
-        <v>869.67</v>
-      </c>
+      <c r="E86" s="3" t="n">
+        <v>20328.28</v>
+      </c>
+      <c r="F86" s="3" t="n"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>-5,964.92 Cr</t>
+          <t>98,308.20 Cr</t>
         </is>
       </c>
     </row>
@@ -2626,17 +2626,17 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/212938102938/DR/BLINKIT/KOTAK/blinkit@kotak</t>
+          <t>UPIAR/172136536211/DR/ZOMATO L/YESB/zomato-order@p</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="3" t="n">
-        <v>515.48</v>
+        <v>480.23</v>
       </c>
       <c r="F87" s="3" t="n"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>-6,480.40 Cr</t>
+          <t>97,827.97 Cr</t>
         </is>
       </c>
     </row>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>27-05-2026</t>
+          <t>28-05-2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>ATM CASH WITHDRAWAL / KORAMANGALA BRANCH</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605281947/CR</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
-      <c r="E88" s="3" t="n">
-        <v>3646.86</v>
-      </c>
-      <c r="F88" s="3" t="n"/>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="n">
+        <v>13182.41</v>
+      </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>-10,127.26 Cr</t>
+          <t>111,010.38 Cr</t>
         </is>
       </c>
     </row>
@@ -2676,15 +2676,17 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605284691/CR</t>
+          <t>SECURITY GUARD SERVICES &amp; CCTV MONITORING</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
-      <c r="E89" s="3" t="n"/>
+      <c r="E89" s="3" t="n">
+        <v>5458.04</v>
+      </c>
       <c r="F89" s="3" t="n"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>-17,272.66 Cr</t>
+          <t>105,552.34 Cr</t>
         </is>
       </c>
     </row>
@@ -2699,17 +2701,17 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/112938102938/CR/WHOLESALE MILK DEPOSIT</t>
+          <t>UPIAR/347067657684/DR/KAJALVI/YESB/paytm.s1w3jr9@</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
-      <c r="E90" s="3" t="n"/>
-      <c r="F90" s="3" t="n">
-        <v>11835.14</v>
-      </c>
+      <c r="E90" s="3" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="F90" s="3" t="n"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>-5,437.52 Cr</t>
+          <t>105,495.25 Cr</t>
         </is>
       </c>
     </row>
@@ -2719,22 +2721,22 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>29-05-2026</t>
+          <t>28-05-2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605293961/CR</t>
+          <t>UPIAB/776655443322/CR/CASHBACK REWARD</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
       <c r="E91" s="3" t="n"/>
       <c r="F91" s="3" t="n">
-        <v>12342.81</v>
+        <v>123.78</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>6,905.29 Cr</t>
+          <t>105,619.03 Cr</t>
         </is>
       </c>
     </row>
@@ -2744,22 +2746,22 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>30-05-2026</t>
+          <t>28-05-2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605306717/CR</t>
+          <t>UPIAB/800823341214/CR/PITCHIKA/CNRB/ umanag9712@ax</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
       <c r="E92" s="3" t="n"/>
       <c r="F92" s="3" t="n">
-        <v>7677.71</v>
+        <v>3417.12</v>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>14,583.00 Cr</t>
+          <t>109,036.15 Cr</t>
         </is>
       </c>
     </row>
@@ -2769,22 +2771,22 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>30-05-2026</t>
+          <t>28-05-2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/009988776655/CR/DIVIDEND PAYOUT</t>
+          <t>IMPS/OUTWARD/612984019283/RAW INGREDIENTS</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
-      <c r="E93" s="3" t="n"/>
-      <c r="F93" s="3" t="n">
-        <v>1763.01</v>
-      </c>
+      <c r="E93" s="3" t="n">
+        <v>15698</v>
+      </c>
+      <c r="F93" s="3" t="n"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>16,346.01 Cr</t>
+          <t>93,338.15 Cr</t>
         </is>
       </c>
     </row>
@@ -2794,22 +2796,22 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>31-05-2026</t>
+          <t>28-05-2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605314233/CR</t>
+          <t>UPIAR/717134959917/DR/AoapAmr/AIRP/AoapAmrita.pay</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
-      <c r="E94" s="3" t="n"/>
-      <c r="F94" s="3" t="n">
-        <v>11447.92</v>
-      </c>
+      <c r="E94" s="3" t="n">
+        <v>3583.42</v>
+      </c>
+      <c r="F94" s="3" t="n"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>27,793.93 Cr</t>
+          <t>89,754.73 Cr</t>
         </is>
       </c>
     </row>
@@ -2819,22 +2821,22 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>31-05-2026</t>
+          <t>29-05-2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/701074556047/DR/73374590/PUNB/7337459005@pty</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605292547/CR</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
-      <c r="E95" s="3" t="n">
-        <v>179.13</v>
-      </c>
-      <c r="F95" s="3" t="n"/>
+      <c r="E95" s="3" t="n"/>
+      <c r="F95" s="3" t="n">
+        <v>8906.469999999999</v>
+      </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>27,614.80 Cr</t>
+          <t>98,661.20 Cr</t>
         </is>
       </c>
     </row>
@@ -2844,22 +2846,22 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01-06-2026</t>
+          <t>30-05-2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606013320/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605301604/CR</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="3" t="n"/>
       <c r="F96" s="3" t="n">
-        <v>11778.21</v>
+        <v>11643.37</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>39,393.01 Cr</t>
+          <t>110,304.57 Cr</t>
         </is>
       </c>
     </row>
@@ -2869,22 +2871,22 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01-06-2026</t>
+          <t>30-05-2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/077728365159/DR/NAMBURI /YESB/ Q501702001@yb</t>
+          <t>UPIAB/512938102938/CR/SUPPLIER CREDIT NOTE</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
-      <c r="E97" s="3" t="n">
-        <v>10.38</v>
-      </c>
-      <c r="F97" s="3" t="n"/>
+      <c r="E97" s="3" t="n"/>
+      <c r="F97" s="3" t="n">
+        <v>9196.73</v>
+      </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>39,382.63 Cr</t>
+          <t>119,501.30 Cr</t>
         </is>
       </c>
     </row>
@@ -2894,22 +2896,22 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>01-06-2026</t>
+          <t>30-05-2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/443322110099/CR/PROMO DISCOUNT CREDIT</t>
+          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
-      <c r="E98" s="3" t="n"/>
-      <c r="F98" s="3" t="n">
-        <v>263.63</v>
-      </c>
+      <c r="E98" s="3" t="n">
+        <v>9887.129999999999</v>
+      </c>
+      <c r="F98" s="3" t="n"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>39,646.26 Cr</t>
+          <t>109,614.17 Cr</t>
         </is>
       </c>
     </row>
@@ -2919,22 +2921,22 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>01-06-2026</t>
+          <t>30-05-2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/140288398543/DR/73374590/PUNB/7337459005@pty</t>
+          <t>BBMP MUNICIPAL TRADE LICENSE &amp; PROPERTY TAX</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="3" t="n">
-        <v>94.81999999999999</v>
+        <v>7460.34</v>
       </c>
       <c r="F99" s="3" t="n"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>39,551.44 Cr</t>
+          <t>102,153.83 Cr</t>
         </is>
       </c>
     </row>
@@ -2944,22 +2946,22 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>02-06-2026</t>
+          <t>31-05-2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606022356/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605313377/CR</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="3" t="n"/>
       <c r="F100" s="3" t="n">
-        <v>4567.2</v>
+        <v>12366.86</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>44,118.64 Cr</t>
+          <t>114,520.69 Cr</t>
         </is>
       </c>
     </row>
@@ -2969,22 +2971,22 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>03-06-2026</t>
+          <t>31-05-2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606035152/CR</t>
+          <t>LIC PREMIUM AUTO DEBIT CLEARING</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr"/>
-      <c r="E101" s="3" t="n"/>
-      <c r="F101" s="3" t="n">
-        <v>4580.6</v>
-      </c>
+      <c r="E101" s="3" t="n">
+        <v>8182.74</v>
+      </c>
+      <c r="F101" s="3" t="n"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>48,699.24 Cr</t>
+          <t>106,337.95 Cr</t>
         </is>
       </c>
     </row>
@@ -2994,22 +2996,22 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>03-06-2026</t>
+          <t>31-05-2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>BBMP MUNICIPAL TRADE LICENSE &amp; PROPERTY TAX</t>
+          <t>UPIAR/685013228668/DR/LHEMANT/HDFC/hemanth0508@yb</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="3" t="n">
-        <v>6089.05</v>
+        <v>176.97</v>
       </c>
       <c r="F102" s="3" t="n"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>42,610.19 Cr</t>
+          <t>106,160.98 Cr</t>
         </is>
       </c>
     </row>
@@ -3019,22 +3021,22 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>03-06-2026</t>
+          <t>31-05-2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/908129381023/DR/BILLDESK/SBIN/billdesk@sbi</t>
+          <t>COMMERCIAL WAREHOUSE RENT / KORAMANGALA HUB</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr"/>
       <c r="E103" s="3" t="n">
-        <v>695.26</v>
+        <v>41544.39</v>
       </c>
       <c r="F103" s="3" t="n"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>41,914.93 Cr</t>
+          <t>64,616.59 Cr</t>
         </is>
       </c>
     </row>
@@ -3044,22 +3046,22 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>03-06-2026</t>
+          <t>01-06-2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>INVENTORY AUDITOR &amp; CA LEGAL RETAINER</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606019890/CR</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr"/>
-      <c r="E104" s="3" t="n">
-        <v>14081.25</v>
-      </c>
-      <c r="F104" s="3" t="n"/>
+      <c r="E104" s="3" t="n"/>
+      <c r="F104" s="3" t="n">
+        <v>14868.97</v>
+      </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>27,833.68 Cr</t>
+          <t>79,485.56 Cr</t>
         </is>
       </c>
     </row>
@@ -3069,22 +3071,22 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>04-06-2026</t>
+          <t>01-06-2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606044731/CR</t>
+          <t>UPIAR/455944913251/DR/KEMSARAP/SBIN/ 8977604821@yb</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr"/>
-      <c r="E105" s="3" t="n"/>
-      <c r="F105" s="3" t="n">
-        <v>14185.04</v>
-      </c>
+      <c r="E105" s="3" t="n">
+        <v>263.42</v>
+      </c>
+      <c r="F105" s="3" t="n"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>42,018.72 Cr</t>
+          <t>79,222.14 Cr</t>
         </is>
       </c>
     </row>
@@ -3094,22 +3096,22 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04-06-2026</t>
+          <t>01-06-2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/332211009988/DR/BOOKMYSHOW TICKET</t>
+          <t>DELIVERY ELECTRIC VAN MAINTENANCE &amp; AMC</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr"/>
       <c r="E106" s="3" t="n">
-        <v>858.11</v>
+        <v>5534.08</v>
       </c>
       <c r="F106" s="3" t="n"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>41,160.61 Cr</t>
+          <t>73,688.06 Cr</t>
         </is>
       </c>
     </row>
@@ -3119,22 +3121,22 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>05-06-2026</t>
+          <t>02-06-2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606057301/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606027210/CR</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
       <c r="E107" s="3" t="n"/>
       <c r="F107" s="3" t="n">
-        <v>14405.03</v>
+        <v>7081.38</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>55,565.64 Cr</t>
+          <t>80,769.44 Cr</t>
         </is>
       </c>
     </row>
@@ -3144,22 +3146,22 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>05-06-2026</t>
+          <t>03-06-2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>SWIGGY INSTAMART FLEET REIMBURSEMENT</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606033794/CR</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr"/>
-      <c r="E108" s="3" t="n">
-        <v>1652.01</v>
-      </c>
-      <c r="F108" s="3" t="n"/>
+      <c r="E108" s="3" t="n"/>
+      <c r="F108" s="3" t="n">
+        <v>6273.51</v>
+      </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>53,913.63 Cr</t>
+          <t>87,042.95 Cr</t>
         </is>
       </c>
     </row>
@@ -3169,22 +3171,22 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>05-06-2026</t>
+          <t>03-06-2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/235911221570/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+          <t>UPIAB/982301928371/CR/LOCAL VENDOR/ICIC/vendor@icici</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr"/>
-      <c r="E109" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="F109" s="3" t="n"/>
+      <c r="E109" s="3" t="n"/>
+      <c r="F109" s="3" t="n">
+        <v>3279.17</v>
+      </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>53,825.63 Cr</t>
+          <t>90,322.12 Cr</t>
         </is>
       </c>
     </row>
@@ -3194,22 +3196,22 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>06-06-2026</t>
+          <t>04-06-2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606065313/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606046977/CR</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr"/>
       <c r="E110" s="3" t="n"/>
       <c r="F110" s="3" t="n">
-        <v>4072.21</v>
+        <v>9303.67</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>57,897.84 Cr</t>
+          <t>99,625.79 Cr</t>
         </is>
       </c>
     </row>
@@ -3219,22 +3221,22 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>06-06-2026</t>
+          <t>04-06-2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/140288398543/DR/73374590/PUNB/7337459005@pty</t>
+          <t>UPIAR/685013228668/DR/LHEMANT/HDFC/hemanth0508@yb</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr"/>
       <c r="E111" s="3" t="n">
-        <v>64.16</v>
+        <v>188.39</v>
       </c>
       <c r="F111" s="3" t="n"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>57,833.68 Cr</t>
+          <t>99,437.40 Cr</t>
         </is>
       </c>
     </row>
@@ -3244,22 +3246,22 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>07-06-2026</t>
+          <t>04-06-2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606076667/CR</t>
+          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr"/>
-      <c r="E112" s="3" t="n"/>
-      <c r="F112" s="3" t="n">
-        <v>15703.64</v>
-      </c>
+      <c r="E112" s="3" t="n">
+        <v>13020.8</v>
+      </c>
+      <c r="F112" s="3" t="n"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>73,537.32 Cr</t>
+          <t>86,416.60 Cr</t>
         </is>
       </c>
     </row>
@@ -3269,22 +3271,22 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>07-06-2026</t>
+          <t>05-06-2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/789123891023/CR/CUSTOMER REFUND REVERSAL</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606055202/CR</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr"/>
       <c r="E113" s="3" t="n"/>
       <c r="F113" s="3" t="n">
-        <v>704.9</v>
+        <v>10798.68</v>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>74,242.22 Cr</t>
+          <t>97,215.28 Cr</t>
         </is>
       </c>
     </row>
@@ -3294,22 +3296,22 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>05-06-2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606083068/CR</t>
+          <t>UPIAR/619283019283/DR/D-MART/HDFC/dmart@hdfc</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr"/>
-      <c r="E114" s="3" t="n"/>
-      <c r="F114" s="3" t="n">
-        <v>7571.62</v>
-      </c>
+      <c r="E114" s="3" t="n">
+        <v>3012.82</v>
+      </c>
+      <c r="F114" s="3" t="n"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>81,813.84 Cr</t>
+          <t>94,202.46 Cr</t>
         </is>
       </c>
     </row>
@@ -3319,22 +3321,22 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>05-06-2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>PRINTING BARCODE LABELS &amp; BILLING ROLLS</t>
+          <t>UPIAR/812938102938/DR/PETROL PUMP/HPCL/hpcl@icici</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr"/>
       <c r="E115" s="3" t="n">
-        <v>3269.19</v>
+        <v>1084.92</v>
       </c>
       <c r="F115" s="3" t="n"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>78,544.65 Cr</t>
+          <t>93,117.54 Cr</t>
         </is>
       </c>
     </row>
@@ -3344,22 +3346,22 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>05-06-2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
+          <t>UPIAR/758331734676/DR/EKNATHB/YESB/ Q440089343@yb</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr"/>
-      <c r="E116" s="3" t="n"/>
-      <c r="F116" s="3" t="n">
-        <v>1219.68</v>
-      </c>
+      <c r="E116" s="3" t="n">
+        <v>116.27</v>
+      </c>
+      <c r="F116" s="3" t="n"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>79,764.33 Cr</t>
+          <t>93,001.27 Cr</t>
         </is>
       </c>
     </row>
@@ -3369,22 +3371,20 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>06-06-2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/143302589531/DR/Zomato87/AIRP/Zomato8759546.</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606063637/CR</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr"/>
-      <c r="E117" s="3" t="n">
-        <v>188.92</v>
-      </c>
+      <c r="E117" s="3" t="n"/>
       <c r="F117" s="3" t="n"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>79,575.41 Cr</t>
+          <t>86,755.22 Cr</t>
         </is>
       </c>
     </row>
@@ -3394,22 +3394,22 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>09-06-2026</t>
+          <t>06-06-2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606091208/CR</t>
+          <t>UPIAR/123854061954/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr"/>
-      <c r="E118" s="3" t="n"/>
-      <c r="F118" s="3" t="n">
-        <v>9183.440000000001</v>
-      </c>
+      <c r="E118" s="3" t="n">
+        <v>300.16</v>
+      </c>
+      <c r="F118" s="3" t="n"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>88,758.85 Cr</t>
+          <t>86,455.06 Cr</t>
         </is>
       </c>
     </row>
@@ -3419,22 +3419,22 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>09-06-2026</t>
+          <t>06-06-2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/619283019283/DR/D-MART/HDFC/dmart@hdfc</t>
+          <t>UPIAR/685013228668/DR/LHEMANT/HDFC/hemanth0508@yb</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr"/>
       <c r="E119" s="3" t="n">
-        <v>3763.51</v>
+        <v>152.05</v>
       </c>
       <c r="F119" s="3" t="n"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>84,995.34 Cr</t>
+          <t>86,303.01 Cr</t>
         </is>
       </c>
     </row>
@@ -3444,22 +3444,22 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>09-06-2026</t>
+          <t>07-06-2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/140515780706/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606076284/CR</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr"/>
-      <c r="E120" s="3" t="n">
-        <v>359.02</v>
-      </c>
-      <c r="F120" s="3" t="n"/>
+      <c r="E120" s="3" t="n"/>
+      <c r="F120" s="3" t="n">
+        <v>11912.48</v>
+      </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>84,636.32 Cr</t>
+          <t>98,215.49 Cr</t>
         </is>
       </c>
     </row>
@@ -3469,22 +3469,22 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>10-06-2026</t>
+          <t>07-06-2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606103270/CR</t>
+          <t>UPIAR/908129381023/DR/BILLDESK/SBIN/billdesk@sbi</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr"/>
-      <c r="E121" s="3" t="n"/>
-      <c r="F121" s="3" t="n">
-        <v>9350.799999999999</v>
-      </c>
+      <c r="E121" s="3" t="n">
+        <v>1002.13</v>
+      </c>
+      <c r="F121" s="3" t="n"/>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>93,987.12 Cr</t>
+          <t>97,213.36 Cr</t>
         </is>
       </c>
     </row>
@@ -3494,22 +3494,22 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>10-06-2026</t>
+          <t>07-06-2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/619283019283/DR/D-MART/HDFC/dmart@hdfc</t>
+          <t>UPIAR/719421374678/DR/NEWKRSN/YESB/paytmqr6a0ixr@</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr"/>
       <c r="E122" s="3" t="n">
-        <v>3297.51</v>
+        <v>159.48</v>
       </c>
       <c r="F122" s="3" t="n"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>90,689.61 Cr</t>
+          <t>97,053.88 Cr</t>
         </is>
       </c>
     </row>
@@ -3519,22 +3519,22 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>10-06-2026</t>
+          <t>07-06-2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE STAFF WAGES &amp; PACKING CREW</t>
+          <t>UPIAR/347067657684/DR/KAJALVI/YESB/paytm.s1w3jr9@</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr"/>
       <c r="E123" s="3" t="n">
-        <v>32555.85</v>
+        <v>78.12</v>
       </c>
       <c r="F123" s="3" t="n"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>58,133.76 Cr</t>
+          <t>96,975.76 Cr</t>
         </is>
       </c>
     </row>
@@ -3544,22 +3544,22 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>10-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>GST ADVANCE TAX DEPOSIT / GOVT OF INDIA</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606085319/CR</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr"/>
-      <c r="E124" s="3" t="n">
-        <v>18989.77</v>
-      </c>
-      <c r="F124" s="3" t="n"/>
+      <c r="E124" s="3" t="n"/>
+      <c r="F124" s="3" t="n">
+        <v>12291.58</v>
+      </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>39,143.99 Cr</t>
+          <t>109,267.34 Cr</t>
         </is>
       </c>
     </row>
@@ -3569,22 +3569,22 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606114093/CR</t>
+          <t>UPIAB/789123891023/CR/CUSTOMER REFUND REVERSAL</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr"/>
       <c r="E125" s="3" t="n"/>
       <c r="F125" s="3" t="n">
-        <v>5177.96</v>
+        <v>233.67</v>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>44,321.95 Cr</t>
+          <t>109,501.01 Cr</t>
         </is>
       </c>
     </row>
@@ -3594,22 +3594,22 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/998877665544/DR/PAYTM QR VENDOR</t>
+          <t>FIRE SAFETY INSPECTION &amp; EQUIPMENT REFILL</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr"/>
       <c r="E126" s="3" t="n">
-        <v>53.23</v>
+        <v>3341.63</v>
       </c>
       <c r="F126" s="3" t="n"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>44,268.72 Cr</t>
+          <t>106,159.38 Cr</t>
         </is>
       </c>
     </row>
@@ -3619,22 +3619,22 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606123080/CR</t>
+          <t>UPIAR/887766554433/DR/BHARATPE MERCHANT</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr"/>
-      <c r="E127" s="3" t="n"/>
-      <c r="F127" s="3" t="n">
-        <v>9653.57</v>
-      </c>
+      <c r="E127" s="3" t="n">
+        <v>175.94</v>
+      </c>
+      <c r="F127" s="3" t="n"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>53,922.29 Cr</t>
+          <t>105,983.44 Cr</t>
         </is>
       </c>
     </row>
@@ -3644,22 +3644,22 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>09-06-2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/443322110099/CR/PROMO DISCOUNT CREDIT</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606096547/CR</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr"/>
       <c r="E128" s="3" t="n"/>
       <c r="F128" s="3" t="n">
-        <v>76.15000000000001</v>
+        <v>6080.61</v>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>53,998.44 Cr</t>
+          <t>112,064.05 Cr</t>
         </is>
       </c>
     </row>
@@ -3669,22 +3669,22 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>09-06-2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>DELIVERY ELECTRIC VAN MAINTENANCE &amp; AMC</t>
+          <t>DELIVERY FLEET FUEL &amp; DIESEL RECHARGE</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr"/>
       <c r="E129" s="3" t="n">
-        <v>3726.97</v>
+        <v>5047.13</v>
       </c>
       <c r="F129" s="3" t="n"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>50,271.47 Cr</t>
+          <t>107,016.92 Cr</t>
         </is>
       </c>
     </row>
@@ -3694,22 +3694,22 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>09-06-2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/512938102938/CR/SUPPLIER CREDIT NOTE</t>
+          <t>UPIAB/712626244599/CR/PICHIKA/BARB/ 8985068499@ax</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr"/>
       <c r="E130" s="3" t="n"/>
       <c r="F130" s="3" t="n">
-        <v>5855.7</v>
+        <v>582.53</v>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>56,127.17 Cr</t>
+          <t>107,599.45 Cr</t>
         </is>
       </c>
     </row>
@@ -3719,22 +3719,22 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>10-06-2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>GOOGLE WORKSPACE &amp; SLACK CLOUD SUITE</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606102388/CR</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr"/>
-      <c r="E131" s="3" t="n">
-        <v>5895.97</v>
-      </c>
-      <c r="F131" s="3" t="n"/>
+      <c r="E131" s="3" t="n"/>
+      <c r="F131" s="3" t="n">
+        <v>6015.5</v>
+      </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>50,231.20 Cr</t>
+          <t>113,614.95 Cr</t>
         </is>
       </c>
     </row>
@@ -3744,22 +3744,22 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>10-06-2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
+          <t>UPIAB/009988776655/CR/DIVIDEND PAYOUT</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr"/>
-      <c r="E132" s="3" t="n">
-        <v>6872.99</v>
-      </c>
-      <c r="F132" s="3" t="n"/>
+      <c r="E132" s="3" t="n"/>
+      <c r="F132" s="3" t="n">
+        <v>1539.79</v>
+      </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>43,358.21 Cr</t>
+          <t>115,154.74 Cr</t>
         </is>
       </c>
     </row>
@@ -3769,22 +3769,22 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>10-06-2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/143302589531/DR/Zomato87/AIRP/Zomato8759546.</t>
+          <t>UPIAR/908129381023/DR/BILLDESK/SBIN/billdesk@sbi</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr"/>
       <c r="E133" s="3" t="n">
-        <v>151.47</v>
+        <v>376.26</v>
       </c>
       <c r="F133" s="3" t="n"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>43,206.74 Cr</t>
+          <t>114,778.48 Cr</t>
         </is>
       </c>
     </row>
@@ -3794,22 +3794,22 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>10-06-2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>SERVICE CHARGE / MINIMUM BALANCE FEE</t>
+          <t>UPIAR/812938102938/DR/PETROL PUMP/HPCL/hpcl@icici</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr"/>
       <c r="E134" s="3" t="n">
-        <v>213.31</v>
+        <v>1979.02</v>
       </c>
       <c r="F134" s="3" t="n"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>42,993.43 Cr</t>
+          <t>112,799.46 Cr</t>
         </is>
       </c>
     </row>
@@ -3819,22 +3819,22 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>13-06-2026</t>
+          <t>10-06-2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606136788/CR</t>
+          <t>UPIAR/312938102938/DR/ZEPTO/YESB/zepto@yb</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr"/>
-      <c r="E135" s="3" t="n"/>
-      <c r="F135" s="3" t="n">
-        <v>11772.98</v>
-      </c>
+      <c r="E135" s="3" t="n">
+        <v>276.1</v>
+      </c>
+      <c r="F135" s="3" t="n"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>54,766.41 Cr</t>
+          <t>112,523.36 Cr</t>
         </is>
       </c>
     </row>
@@ -3844,22 +3844,22 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>13-06-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/982301928371/CR/LOCAL VENDOR/ICIC/vendor@icici</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606112727/CR</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr"/>
       <c r="E136" s="3" t="n"/>
       <c r="F136" s="3" t="n">
-        <v>4253.34</v>
+        <v>13249.53</v>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>59,019.75 Cr</t>
+          <t>125,772.89 Cr</t>
         </is>
       </c>
     </row>
@@ -3869,22 +3869,22 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>13-06-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/758331734676/DR/EKNATHB/YESB/ Q440089343@yb</t>
+          <t>UPIAB/712626244599/CR/PICHIKA/BARB/ 8985068499@ax</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr"/>
-      <c r="E137" s="3" t="n">
-        <v>103.48</v>
-      </c>
-      <c r="F137" s="3" t="n"/>
+      <c r="E137" s="3" t="n"/>
+      <c r="F137" s="3" t="n">
+        <v>362.38</v>
+      </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>58,916.27 Cr</t>
+          <t>126,135.27 Cr</t>
         </is>
       </c>
     </row>
@@ -3894,22 +3894,22 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>13-06-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>POINT OF SALE (POS) HARDWARE RENTAL</t>
+          <t>UPIAR/301984712093/DR/SWIGGY/HDFC/swiggy@hdfc</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr"/>
       <c r="E138" s="3" t="n">
-        <v>2463.21</v>
+        <v>250.58</v>
       </c>
       <c r="F138" s="3" t="n"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>56,453.06 Cr</t>
+          <t>125,884.69 Cr</t>
         </is>
       </c>
     </row>
@@ -3919,22 +3919,22 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>13-06-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>DELIVERY FLEET FUEL &amp; DIESEL RECHARGE</t>
+          <t>UPIAR/123854061954/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr"/>
       <c r="E139" s="3" t="n">
-        <v>5684.57</v>
+        <v>171.68</v>
       </c>
       <c r="F139" s="3" t="n"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>50,768.49 Cr</t>
+          <t>125,713.01 Cr</t>
         </is>
       </c>
     </row>
@@ -3944,22 +3944,22 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>14-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606147646/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606121179/CR</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr"/>
       <c r="E140" s="3" t="n"/>
       <c r="F140" s="3" t="n">
-        <v>7020.13</v>
+        <v>9855.09</v>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>57,788.62 Cr</t>
+          <t>135,568.10 Cr</t>
         </is>
       </c>
     </row>
@@ -3969,22 +3969,22 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>14-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>SERVICE CHARGE / MINIMUM BALANCE FEE</t>
+          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr"/>
       <c r="E141" s="3" t="n">
-        <v>246.16</v>
+        <v>12454.54</v>
       </c>
       <c r="F141" s="3" t="n"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>57,542.46 Cr</t>
+          <t>123,113.56 Cr</t>
         </is>
       </c>
     </row>
@@ -3994,22 +3994,22 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>14-06-2026</t>
+          <t>13-06-2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/455944913251/DR/KEMSARAP/SBIN/ 8977604821@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606136428/CR</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr"/>
-      <c r="E142" s="3" t="n">
-        <v>212.94</v>
-      </c>
-      <c r="F142" s="3" t="n"/>
+      <c r="E142" s="3" t="n"/>
+      <c r="F142" s="3" t="n">
+        <v>6370.23</v>
+      </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>57,329.52 Cr</t>
+          <t>129,483.79 Cr</t>
         </is>
       </c>
     </row>
@@ -4019,22 +4019,22 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>14-06-2026</t>
+          <t>13-06-2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/140288398543/DR/73374590/PUNB/7337459005@pty</t>
+          <t>UPIAR/124934775512/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr"/>
       <c r="E143" s="3" t="n">
-        <v>135.36</v>
+        <v>504.48</v>
       </c>
       <c r="F143" s="3" t="n"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>57,194.16 Cr</t>
+          <t>128,979.31 Cr</t>
         </is>
       </c>
     </row>
@@ -4049,17 +4049,17 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/857830578859/DR/GAURAV S/YESB/ Q815875629@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606141602/CR</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr"/>
-      <c r="E144" s="3" t="n">
-        <v>254.51</v>
-      </c>
-      <c r="F144" s="3" t="n"/>
+      <c r="E144" s="3" t="n"/>
+      <c r="F144" s="3" t="n">
+        <v>7413.78</v>
+      </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>56,939.65 Cr</t>
+          <t>136,393.09 Cr</t>
         </is>
       </c>
     </row>
@@ -4069,22 +4069,22 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15-06-2026</t>
+          <t>14-06-2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606153064/CR</t>
+          <t>UPIAR/221100998877/DR/UBER RIDE</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr"/>
-      <c r="E145" s="3" t="n"/>
-      <c r="F145" s="3" t="n">
-        <v>8682.1</v>
-      </c>
+      <c r="E145" s="3" t="n">
+        <v>652.61</v>
+      </c>
+      <c r="F145" s="3" t="n"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>65,621.75 Cr</t>
+          <t>135,740.48 Cr</t>
         </is>
       </c>
     </row>
@@ -4094,22 +4094,22 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>15-06-2026</t>
+          <t>14-06-2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/278079065373/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+          <t>UPIAB/624556864731/CR/PICHIKA/UBIN/pvasuviswanadh</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr"/>
-      <c r="E146" s="3" t="n">
-        <v>565.22</v>
-      </c>
-      <c r="F146" s="3" t="n"/>
+      <c r="E146" s="3" t="n"/>
+      <c r="F146" s="3" t="n">
+        <v>2927.09</v>
+      </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>65,056.53 Cr</t>
+          <t>138,667.57 Cr</t>
         </is>
       </c>
     </row>
@@ -4119,22 +4119,22 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>15-06-2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606161887/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606156053/CR</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr"/>
       <c r="E147" s="3" t="n"/>
       <c r="F147" s="3" t="n">
-        <v>6031.9</v>
+        <v>16047.78</v>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>71,088.43 Cr</t>
+          <t>154,715.35 Cr</t>
         </is>
       </c>
     </row>
@@ -4144,22 +4144,22 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>15-06-2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>BESCOM POWER UTILITY / BANGALORE WAREHOUSE</t>
+          <t>UPIAR/645455850592/DR/DDhanus/SBIN/ 7396913943@up</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr"/>
       <c r="E148" s="3" t="n">
-        <v>11700.54</v>
+        <v>175.33</v>
       </c>
       <c r="F148" s="3" t="n"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>59,387.89 Cr</t>
+          <t>154,540.02 Cr</t>
         </is>
       </c>
     </row>
@@ -4169,22 +4169,22 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>17-06-2026</t>
+          <t>15-06-2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606172802/CR</t>
+          <t>UPIAR/717134959917/DR/AoapAmr/AIRP/AoapAmrita.pay</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr"/>
-      <c r="E149" s="3" t="n"/>
-      <c r="F149" s="3" t="n">
-        <v>9780.049999999999</v>
-      </c>
+      <c r="E149" s="3" t="n">
+        <v>2745.15</v>
+      </c>
+      <c r="F149" s="3" t="n"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>69,167.94 Cr</t>
+          <t>151,794.87 Cr</t>
         </is>
       </c>
     </row>
@@ -4194,22 +4194,22 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>17-06-2026</t>
+          <t>15-06-2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/776655443322/CR/CASHBACK REWARD</t>
+          <t>UPIAR/124934775512/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr"/>
-      <c r="E150" s="3" t="n"/>
-      <c r="F150" s="3" t="n">
-        <v>19.16</v>
-      </c>
+      <c r="E150" s="3" t="n">
+        <v>690.5</v>
+      </c>
+      <c r="F150" s="3" t="n"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>69,187.10 Cr</t>
+          <t>151,104.37 Cr</t>
         </is>
       </c>
     </row>
@@ -4219,22 +4219,22 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>17-06-2026</t>
+          <t>15-06-2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/026544681447/DR/SHANTIP/YESB/ Q707874078@yb</t>
+          <t>UPIAB/789123891023/CR/CUSTOMER REFUND REVERSAL</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr"/>
-      <c r="E151" s="3" t="n">
-        <v>402.4</v>
-      </c>
-      <c r="F151" s="3" t="n"/>
+      <c r="E151" s="3" t="n"/>
+      <c r="F151" s="3" t="n">
+        <v>495.15</v>
+      </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>68,784.70 Cr</t>
+          <t>151,599.52 Cr</t>
         </is>
       </c>
     </row>
@@ -4244,22 +4244,22 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606186459/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606169405/CR</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr"/>
       <c r="E152" s="3" t="n"/>
       <c r="F152" s="3" t="n">
-        <v>11678.21</v>
+        <v>7627.4</v>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>80,462.91 Cr</t>
+          <t>159,226.92 Cr</t>
         </is>
       </c>
     </row>
@@ -4269,22 +4269,22 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/701074556047/DR/73374590/PUNB/7337459005@pty</t>
+          <t>UPIAR/172136536211/DR/ZOMATO L/YESB/zomato-order@p</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr"/>
       <c r="E153" s="3" t="n">
-        <v>200.33</v>
+        <v>300.79</v>
       </c>
       <c r="F153" s="3" t="n"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>80,262.58 Cr</t>
+          <t>158,926.13 Cr</t>
         </is>
       </c>
     </row>
@@ -4294,22 +4294,22 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606199705/CR</t>
+          <t>UPIAR/998877665544/DR/PAYTM QR VENDOR</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr"/>
-      <c r="E154" s="3" t="n"/>
-      <c r="F154" s="3" t="n">
-        <v>7785.64</v>
-      </c>
+      <c r="E154" s="3" t="n">
+        <v>133.98</v>
+      </c>
+      <c r="F154" s="3" t="n"/>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>88,048.22 Cr</t>
+          <t>158,792.15 Cr</t>
         </is>
       </c>
     </row>
@@ -4319,22 +4319,22 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>17-06-2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/857830578859/DR/GAURAV S/YESB/ Q815875629@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606173296/CR</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr"/>
-      <c r="E155" s="3" t="n">
-        <v>198.66</v>
-      </c>
-      <c r="F155" s="3" t="n"/>
+      <c r="E155" s="3" t="n"/>
+      <c r="F155" s="3" t="n">
+        <v>4058.16</v>
+      </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>87,849.56 Cr</t>
+          <t>162,850.31 Cr</t>
         </is>
       </c>
     </row>
@@ -4344,22 +4344,22 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>17-06-2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/278079065373/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+          <t>GOOGLE WORKSPACE &amp; SLACK CLOUD SUITE</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr"/>
       <c r="E156" s="3" t="n">
-        <v>524.3</v>
+        <v>4440.77</v>
       </c>
       <c r="F156" s="3" t="n"/>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>87,325.26 Cr</t>
+          <t>158,409.54 Cr</t>
         </is>
       </c>
     </row>
@@ -4369,22 +4369,22 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>20-06-2026</t>
+          <t>17-06-2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606204313/CR</t>
+          <t>IMPS/INWARD/SBIN/DISTRIBUTOR SETTLEMENT</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr"/>
       <c r="E157" s="3" t="n"/>
       <c r="F157" s="3" t="n">
-        <v>11335.82</v>
+        <v>13935.31</v>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>98,661.08 Cr</t>
+          <t>172,344.85 Cr</t>
         </is>
       </c>
     </row>
@@ -4394,22 +4394,22 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>20-06-2026</t>
+          <t>17-06-2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>DELIVERY ELECTRIC VAN MAINTENANCE &amp; AMC</t>
+          <t>UPIAR/665544332211/DR/AMAZON INDIA</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr"/>
       <c r="E158" s="3" t="n">
-        <v>3052.23</v>
+        <v>939.6799999999999</v>
       </c>
       <c r="F158" s="3" t="n"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>95,608.85 Cr</t>
+          <t>171,405.17 Cr</t>
         </is>
       </c>
     </row>
@@ -4419,22 +4419,22 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>20-06-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/221100998877/DR/UBER RIDE</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606185730/CR</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr"/>
-      <c r="E159" s="3" t="n">
-        <v>323.58</v>
-      </c>
-      <c r="F159" s="3" t="n"/>
+      <c r="E159" s="3" t="n"/>
+      <c r="F159" s="3" t="n">
+        <v>15944.86</v>
+      </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>95,285.27 Cr</t>
+          <t>187,350.03 Cr</t>
         </is>
       </c>
     </row>
@@ -4444,22 +4444,22 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>19-06-2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606219852/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606196927/CR</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr"/>
       <c r="E160" s="3" t="n"/>
       <c r="F160" s="3" t="n">
-        <v>10793.98</v>
+        <v>6911.31</v>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>106,079.25 Cr</t>
+          <t>194,261.34 Cr</t>
         </is>
       </c>
     </row>
@@ -4469,22 +4469,22 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>19-06-2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/539631629714/CR/TAIESWA/PPIW/6302476334.wal</t>
+          <t>UPIAB/776655443322/CR/CASHBACK REWARD</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr"/>
       <c r="E161" s="3" t="n"/>
       <c r="F161" s="3" t="n">
-        <v>207.88</v>
+        <v>90.77</v>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>106,287.13 Cr</t>
+          <t>194,352.11 Cr</t>
         </is>
       </c>
     </row>
@@ -4494,22 +4494,22 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>20-06-2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>COMMERCIAL WAREHOUSE RENT / KORAMANGALA HUB</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606204278/CR</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr"/>
-      <c r="E162" s="3" t="n">
-        <v>36853.91</v>
-      </c>
-      <c r="F162" s="3" t="n"/>
+      <c r="E162" s="3" t="n"/>
+      <c r="F162" s="3" t="n">
+        <v>7798.89</v>
+      </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>69,433.22 Cr</t>
+          <t>202,151.00 Cr</t>
         </is>
       </c>
     </row>
@@ -4519,22 +4519,22 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>20-06-2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>DELIVERY ELECTRIC VAN MAINTENANCE &amp; AMC</t>
+          <t>UPIAR/140515780706/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr"/>
       <c r="E163" s="3" t="n">
-        <v>3216.26</v>
+        <v>187.67</v>
       </c>
       <c r="F163" s="3" t="n"/>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>66,216.96 Cr</t>
+          <t>201,963.33 Cr</t>
         </is>
       </c>
     </row>
@@ -4544,22 +4544,22 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>20-06-2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/637338636405/CR/PITCHIKA/SBIN/ 8919861154@yb</t>
+          <t>LIC PREMIUM AUTO DEBIT CLEARING</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr"/>
-      <c r="E164" s="3" t="n"/>
-      <c r="F164" s="3" t="n">
-        <v>3734.28</v>
-      </c>
+      <c r="E164" s="3" t="n">
+        <v>10217.69</v>
+      </c>
+      <c r="F164" s="3" t="n"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>69,951.24 Cr</t>
+          <t>191,745.64 Cr</t>
         </is>
       </c>
     </row>
@@ -4569,22 +4569,22 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>20-06-2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/312938102938/DR/ZEPTO/YESB/zepto@yb</t>
+          <t>UPIAB/022447403071/CR/THIRUVEE/UBIN/9391652831-2@a</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr"/>
-      <c r="E165" s="3" t="n">
-        <v>617.0599999999999</v>
-      </c>
-      <c r="F165" s="3" t="n"/>
+      <c r="E165" s="3" t="n"/>
+      <c r="F165" s="3" t="n">
+        <v>790.33</v>
+      </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>69,334.18 Cr</t>
+          <t>192,535.97 Cr</t>
         </is>
       </c>
     </row>
@@ -4594,22 +4594,22 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>20-06-2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606221676/CR</t>
+          <t>GOOGLE WORKSPACE &amp; SLACK CLOUD SUITE</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr"/>
-      <c r="E166" s="3" t="n"/>
-      <c r="F166" s="3" t="n">
-        <v>689.92</v>
-      </c>
+      <c r="E166" s="3" t="n">
+        <v>4674.81</v>
+      </c>
+      <c r="F166" s="3" t="n"/>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>70,024.10 Cr</t>
+          <t>187,861.16 Cr</t>
         </is>
       </c>
     </row>
@@ -4619,22 +4619,22 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>21-06-2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/539631629714/CR/TAIESWA/PPIW/6302476334.wal</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606214145/CR</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr"/>
       <c r="E167" s="3" t="n"/>
       <c r="F167" s="3" t="n">
-        <v>363.48</v>
+        <v>10966.73</v>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>70,387.58 Cr</t>
+          <t>198,827.89 Cr</t>
         </is>
       </c>
     </row>
@@ -4649,17 +4649,17 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>GST ADVANCE TAX DEPOSIT / GOVT OF INDIA</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606228321/CR</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr"/>
-      <c r="E168" s="3" t="n">
-        <v>16806.34</v>
-      </c>
-      <c r="F168" s="3" t="n"/>
+      <c r="E168" s="3" t="n"/>
+      <c r="F168" s="3" t="n">
+        <v>11268.67</v>
+      </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>53,581.24 Cr</t>
+          <t>210,096.56 Cr</t>
         </is>
       </c>
     </row>
@@ -4674,17 +4674,17 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/412938102938/DR/BIGBASKET/ICIC/bb@icici</t>
+          <t>UPIAB/712626244599/CR/PICHIKA/BARB/ 8985068499@ax</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr"/>
-      <c r="E169" s="3" t="n">
-        <v>1565.6</v>
-      </c>
-      <c r="F169" s="3" t="n"/>
+      <c r="E169" s="3" t="n"/>
+      <c r="F169" s="3" t="n">
+        <v>1147.8</v>
+      </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>52,015.64 Cr</t>
+          <t>211,244.36 Cr</t>
         </is>
       </c>
     </row>
@@ -4694,22 +4694,22 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606231652/CR</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr"/>
       <c r="E170" s="3" t="n"/>
       <c r="F170" s="3" t="n">
-        <v>1336.66</v>
+        <v>9575.790000000001</v>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>53,352.30 Cr</t>
+          <t>220,820.15 Cr</t>
         </is>
       </c>
     </row>
@@ -4724,17 +4724,17 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606232774/CR</t>
+          <t>UPIAB/624556864731/CR/PICHIKA/UBIN/pvasuviswanadh</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr"/>
       <c r="E171" s="3" t="n"/>
       <c r="F171" s="3" t="n">
-        <v>10325</v>
+        <v>2091.25</v>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>63,677.30 Cr</t>
+          <t>222,911.40 Cr</t>
         </is>
       </c>
     </row>
@@ -4749,17 +4749,17 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/800823341214/CR/PITCHIKA/CNRB/ umanag9712@ax</t>
+          <t>DELIVERY FLEET FUEL &amp; DIESEL RECHARGE</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr"/>
-      <c r="E172" s="3" t="n"/>
-      <c r="F172" s="3" t="n">
-        <v>4523.15</v>
-      </c>
+      <c r="E172" s="3" t="n">
+        <v>3954.08</v>
+      </c>
+      <c r="F172" s="3" t="n"/>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>68,200.45 Cr</t>
+          <t>218,957.32 Cr</t>
         </is>
       </c>
     </row>
@@ -4774,17 +4774,17 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>NEFT/INWARD/CITI/GROCERY WHOLESALE REBATE</t>
+          <t>UPIAR/701074556047/DR/73374590/PUNB/7337459005@pty</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr"/>
-      <c r="E173" s="3" t="n"/>
-      <c r="F173" s="3" t="n">
-        <v>7913.1</v>
-      </c>
+      <c r="E173" s="3" t="n">
+        <v>91.39</v>
+      </c>
+      <c r="F173" s="3" t="n"/>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>76,113.55 Cr</t>
+          <t>218,865.93 Cr</t>
         </is>
       </c>
     </row>
@@ -4799,17 +4799,17 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/800823341214/CR/PITCHIKA/CNRB/ umanag9712@ax</t>
+          <t>SERVICE CHARGE / MINIMUM BALANCE FEE</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr"/>
-      <c r="E174" s="3" t="n"/>
-      <c r="F174" s="3" t="n">
-        <v>4445.4</v>
-      </c>
+      <c r="E174" s="3" t="n">
+        <v>226.41</v>
+      </c>
+      <c r="F174" s="3" t="n"/>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>80,558.95 Cr</t>
+          <t>218,639.52 Cr</t>
         </is>
       </c>
     </row>
@@ -4824,17 +4824,17 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/278079065373/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+          <t>UPIAB/322671730620/CR/PITCHIKA/SBIN/ 8919861154@ax</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr"/>
-      <c r="E175" s="3" t="n">
-        <v>453.95</v>
-      </c>
-      <c r="F175" s="3" t="n"/>
+      <c r="E175" s="3" t="n"/>
+      <c r="F175" s="3" t="n">
+        <v>858.24</v>
+      </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>80,105.00 Cr</t>
+          <t>219,497.76 Cr</t>
         </is>
       </c>
     </row>
@@ -4844,22 +4844,22 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606244888/CR</t>
+          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr"/>
-      <c r="E176" s="3" t="n"/>
-      <c r="F176" s="3" t="n">
-        <v>15267.23</v>
-      </c>
+      <c r="E176" s="3" t="n">
+        <v>11048.71</v>
+      </c>
+      <c r="F176" s="3" t="n"/>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>95,372.23 Cr</t>
+          <t>208,449.05 Cr</t>
         </is>
       </c>
     </row>
@@ -4874,17 +4874,17 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/124934775512/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606246916/CR</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr"/>
-      <c r="E177" s="3" t="n">
-        <v>500.11</v>
-      </c>
-      <c r="F177" s="3" t="n"/>
+      <c r="E177" s="3" t="n"/>
+      <c r="F177" s="3" t="n">
+        <v>14172.77</v>
+      </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>94,872.12 Cr</t>
+          <t>222,621.82 Cr</t>
         </is>
       </c>
     </row>
@@ -4899,17 +4899,17 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>NEFT/OUTWARD/UTI MUTUAL FUND SIP</t>
+          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr"/>
       <c r="E178" s="3" t="n">
-        <v>4864.39</v>
+        <v>9945.82</v>
       </c>
       <c r="F178" s="3" t="n"/>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>90,007.73 Cr</t>
+          <t>212,676.00 Cr</t>
         </is>
       </c>
     </row>
@@ -4919,22 +4919,22 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606251372/CR</t>
+          <t>FIRE SAFETY INSPECTION &amp; EQUIPMENT REFILL</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr"/>
-      <c r="E179" s="3" t="n"/>
-      <c r="F179" s="3" t="n">
-        <v>7398.4</v>
-      </c>
+      <c r="E179" s="3" t="n">
+        <v>3021.03</v>
+      </c>
+      <c r="F179" s="3" t="n"/>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>97,406.13 Cr</t>
+          <t>209,654.97 Cr</t>
         </is>
       </c>
     </row>
@@ -4949,17 +4949,17 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>INVENTORY AUDITOR &amp; CA LEGAL RETAINER</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606253826/CR</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr"/>
-      <c r="E180" s="3" t="n">
-        <v>14217.34</v>
-      </c>
-      <c r="F180" s="3" t="n"/>
+      <c r="E180" s="3" t="n"/>
+      <c r="F180" s="3" t="n">
+        <v>16308.21</v>
+      </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>83,188.79 Cr</t>
+          <t>225,963.18 Cr</t>
         </is>
       </c>
     </row>
@@ -4974,17 +4974,17 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/140515780706/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+          <t>WAREHOUSE STAFF WAGES &amp; PACKING CREW</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr"/>
       <c r="E181" s="3" t="n">
-        <v>90.97</v>
+        <v>39333.22</v>
       </c>
       <c r="F181" s="3" t="n"/>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>83,097.82 Cr</t>
+          <t>186,629.96 Cr</t>
         </is>
       </c>
     </row>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606266668/CR</t>
+          <t>FIRE SAFETY INSPECTION &amp; EQUIPMENT REFILL</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr"/>
-      <c r="E182" s="3" t="n"/>
-      <c r="F182" s="3" t="n">
-        <v>8108.59</v>
-      </c>
+      <c r="E182" s="3" t="n">
+        <v>2582.75</v>
+      </c>
+      <c r="F182" s="3" t="n"/>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>91,206.41 Cr</t>
+          <t>184,047.21 Cr</t>
         </is>
       </c>
     </row>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/124934775512/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+          <t>UPIAR/812938102938/DR/PETROL PUMP/HPCL/hpcl@icici</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr"/>
       <c r="E183" s="3" t="n">
-        <v>492.09</v>
+        <v>1664.45</v>
       </c>
       <c r="F183" s="3" t="n"/>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>90,714.32 Cr</t>
+          <t>182,382.76 Cr</t>
         </is>
       </c>
     </row>
@@ -5049,17 +5049,17 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/140515780706/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606269025/CR</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr"/>
-      <c r="E184" s="3" t="n">
-        <v>330.74</v>
-      </c>
-      <c r="F184" s="3" t="n"/>
+      <c r="E184" s="3" t="n"/>
+      <c r="F184" s="3" t="n">
+        <v>2506.26</v>
+      </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>90,383.58 Cr</t>
+          <t>184,889.02 Cr</t>
         </is>
       </c>
     </row>
@@ -5069,22 +5069,22 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606278681/CR</t>
+          <t>UPIAR/758331734676/DR/EKNATHB/YESB/ Q440089343@yb</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr"/>
-      <c r="E185" s="3" t="n"/>
-      <c r="F185" s="3" t="n">
-        <v>1915.86</v>
-      </c>
+      <c r="E185" s="3" t="n">
+        <v>59.89</v>
+      </c>
+      <c r="F185" s="3" t="n"/>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>92,299.44 Cr</t>
+          <t>184,829.13 Cr</t>
         </is>
       </c>
     </row>
@@ -5094,22 +5094,22 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/322671730620/CR/PITCHIKA/SBIN/ 8919861154@ax</t>
+          <t>UPIAB/443322110099/CR/PROMO DISCOUNT CREDIT</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr"/>
       <c r="E186" s="3" t="n"/>
       <c r="F186" s="3" t="n">
-        <v>3514.36</v>
+        <v>237.95</v>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>95,813.80 Cr</t>
+          <t>185,067.08 Cr</t>
         </is>
       </c>
     </row>
@@ -5119,22 +5119,22 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>FIRE SAFETY INSPECTION &amp; EQUIPMENT REFILL</t>
+          <t>UPIAR/887766554433/DR/BHARATPE MERCHANT</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr"/>
       <c r="E187" s="3" t="n">
-        <v>4165.51</v>
+        <v>116.55</v>
       </c>
       <c r="F187" s="3" t="n"/>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>91,648.29 Cr</t>
+          <t>184,950.53 Cr</t>
         </is>
       </c>
     </row>
@@ -5149,17 +5149,17 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/172136536211/DR/ZOMATO L/YESB/zomato-order@p</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606273877/CR</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr"/>
-      <c r="E188" s="3" t="n">
-        <v>174.24</v>
-      </c>
-      <c r="F188" s="3" t="n"/>
+      <c r="E188" s="3" t="n"/>
+      <c r="F188" s="3" t="n">
+        <v>2696.43</v>
+      </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>91,474.05 Cr</t>
+          <t>187,646.96 Cr</t>
         </is>
       </c>
     </row>

--- a/generated_data/bank_statement_union_bank.xlsx
+++ b/generated_data/bank_statement_union_bank.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,17 +501,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605011934/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605014040/CR</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n">
-        <v>5659.68</v>
+        <v>11741.28</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>15,659.68 Cr</t>
+          <t>21,741.28 Cr</t>
         </is>
       </c>
     </row>
@@ -521,22 +521,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01-05-2026</t>
+          <t>02-05-2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/373995020793/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605025256/CR</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="3" t="n">
-        <v>2055.28</v>
-      </c>
-      <c r="F3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n">
+        <v>9586.879999999999</v>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>13,604.40 Cr</t>
+          <t>31,328.16 Cr</t>
         </is>
       </c>
     </row>
@@ -546,22 +546,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>01-05-2026</t>
+          <t>03-05-2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/685013228668/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605031750/CR</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="3" t="n">
-        <v>47.01</v>
-      </c>
-      <c r="F4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n">
+        <v>4723.37</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,557.39 Cr</t>
+          <t>36,051.53 Cr</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>02-05-2026</t>
+          <t>03-05-2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605021556/CR</t>
+          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n">
-        <v>1628.4</v>
+        <v>2243.54</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,185.79 Cr</t>
+          <t>38,295.07 Cr</t>
         </is>
       </c>
     </row>
@@ -596,22 +596,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>02-05-2026</t>
+          <t>03-05-2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/332211009988/DR/BOOKMYSHOW TICKET</t>
+          <t>UPIAB/539631629714/CR/TAIESWA/PPIW/6302476334.wal</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="3" t="n">
-        <v>913.12</v>
-      </c>
-      <c r="F6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n">
+        <v>252.84</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14,272.67 Cr</t>
+          <t>38,547.91 Cr</t>
         </is>
       </c>
     </row>
@@ -626,17 +626,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605036870/CR</t>
+          <t>UPIAB/624556864731/CR/PICHIKA/UBIN/pvasuviswanadh</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n">
-        <v>1434.79</v>
+        <v>1498.43</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,707.46 Cr</t>
+          <t>40,046.34 Cr</t>
         </is>
       </c>
     </row>
@@ -646,22 +646,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04-05-2026</t>
+          <t>03-05-2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605047215/CR</t>
+          <t>UPIAR/204208208508/DR/Zomato87/AIRP/Zomato8759546.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n">
-        <v>5820.67</v>
-      </c>
+      <c r="E8" s="3" t="n">
+        <v>277.44</v>
+      </c>
+      <c r="F8" s="3" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>21,528.13 Cr</t>
+          <t>39,768.90 Cr</t>
         </is>
       </c>
     </row>
@@ -671,22 +671,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>05-05-2026</t>
+          <t>03-05-2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605055684/CR</t>
+          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n">
-        <v>2823.61</v>
+        <v>2020.67</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,351.74 Cr</t>
+          <t>41,789.57 Cr</t>
         </is>
       </c>
     </row>
@@ -696,22 +696,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>05-05-2026</t>
+          <t>03-05-2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/312938102938/DR/ZEPTO/YESB/zepto@yb</t>
+          <t>UPIAR/719421374678/DR/NEWKRSN/YESB/paytmqr6a0ixr@</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="3" t="n">
-        <v>819.97</v>
+        <v>79.03</v>
       </c>
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,531.77 Cr</t>
+          <t>41,710.54 Cr</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>06-05-2026</t>
+          <t>04-05-2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605061525/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605043970/CR</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n">
-        <v>557.41</v>
+        <v>15024.94</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,089.18 Cr</t>
+          <t>56,735.48 Cr</t>
         </is>
       </c>
     </row>
@@ -746,22 +746,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>07-05-2026</t>
+          <t>05-05-2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605077760/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605052676/CR</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n">
-        <v>6236.52</v>
+        <v>12975.09</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>30,325.70 Cr</t>
+          <t>69,710.57 Cr</t>
         </is>
       </c>
     </row>
@@ -771,22 +771,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>07-05-2026</t>
+          <t>05-05-2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/123854061954/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+          <t>UPIAR/026544681447/DR/SHANTIP/YESB/ Q707874078@yb</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="3" t="n">
-        <v>301.03</v>
+        <v>874.8200000000001</v>
       </c>
       <c r="F13" s="3" t="n"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,024.67 Cr</t>
+          <t>68,835.75 Cr</t>
         </is>
       </c>
     </row>
@@ -796,22 +796,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>07-05-2026</t>
+          <t>06-05-2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/908931590719/DR/Mr Raju/YESB/ Q249677790@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605068706/CR</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="3" t="n">
-        <v>82.69</v>
-      </c>
-      <c r="F14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n">
+        <v>5730.49</v>
+      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>29,941.98 Cr</t>
+          <t>74,566.24 Cr</t>
         </is>
       </c>
     </row>
@@ -821,22 +821,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08-05-2026</t>
+          <t>06-05-2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605088074/CR</t>
+          <t>UPIAR/123854061954/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n">
-        <v>1873.98</v>
-      </c>
+      <c r="E15" s="3" t="n">
+        <v>339.97</v>
+      </c>
+      <c r="F15" s="3" t="n"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31,815.96 Cr</t>
+          <t>74,226.27 Cr</t>
         </is>
       </c>
     </row>
@@ -846,22 +846,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>08-05-2026</t>
+          <t>06-05-2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/908129381023/DR/BILLDESK/SBIN/billdesk@sbi</t>
+          <t>BANK SMS ALERTS &amp; ANNUAL MAINT CHARGES</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="3" t="n">
-        <v>1103.27</v>
+        <v>117.04</v>
       </c>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>30,712.69 Cr</t>
+          <t>74,109.23 Cr</t>
         </is>
       </c>
     </row>
@@ -871,22 +871,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>06-05-2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605093670/CR</t>
+          <t>UPIAR/619283019283/DR/D-MART/HDFC/dmart@hdfc</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n">
-        <v>1425.72</v>
-      </c>
+      <c r="E17" s="3" t="n">
+        <v>2201.74</v>
+      </c>
+      <c r="F17" s="3" t="n"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,138.41 Cr</t>
+          <t>71,907.49 Cr</t>
         </is>
       </c>
     </row>
@@ -896,22 +896,22 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>06-05-2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/077728365159/DR/NAMBURI /YESB/ Q501702001@yb</t>
+          <t>UPIAB/800823341214/CR/PITCHIKA/CNRB/ umanag9712@ax</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="3" t="n">
-        <v>76.95999999999999</v>
-      </c>
-      <c r="F18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n">
+        <v>3356.39</v>
+      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32,061.45 Cr</t>
+          <t>75,263.88 Cr</t>
         </is>
       </c>
     </row>
@@ -921,22 +921,22 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10-05-2026</t>
+          <t>06-05-2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605107111/CR</t>
+          <t>UPIAR/140288398543/DR/73374590/PUNB/7337459005@pty</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n">
-        <v>3246.71</v>
-      </c>
+      <c r="E19" s="3" t="n">
+        <v>146.28</v>
+      </c>
+      <c r="F19" s="3" t="n"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>35,308.16 Cr</t>
+          <t>75,117.60 Cr</t>
         </is>
       </c>
     </row>
@@ -946,22 +946,22 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>10-05-2026</t>
+          <t>07-05-2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/455944913251/DR/KEMSARAP/SBIN/ 8977604821@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605073558/CR</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="3" t="n">
-        <v>96.51000000000001</v>
-      </c>
-      <c r="F20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n">
+        <v>7997.11</v>
+      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>35,211.65 Cr</t>
+          <t>83,114.71 Cr</t>
         </is>
       </c>
     </row>
@@ -971,22 +971,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11-05-2026</t>
+          <t>07-05-2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605115672/CR</t>
+          <t>UPIAR/701074556047/DR/73374590/PUNB/7337459005@pty</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n">
-        <v>1795.53</v>
-      </c>
+      <c r="E21" s="3" t="n">
+        <v>142.36</v>
+      </c>
+      <c r="F21" s="3" t="n"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37,007.18 Cr</t>
+          <t>82,972.35 Cr</t>
         </is>
       </c>
     </row>
@@ -996,22 +996,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>12-05-2026</t>
+          <t>08-05-2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605128069/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605085437/CR</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n">
-        <v>1948.46</v>
+        <v>6951.52</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>38,955.64 Cr</t>
+          <t>89,923.87 Cr</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>12-05-2026</t>
+          <t>08-05-2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/712626244599/CR/PICHIKA/BARB/ 8985068499@ax</t>
+          <t>COMMERCIAL WAREHOUSE RENT / KORAMANGALA HUB</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n">
-        <v>560.52</v>
-      </c>
+      <c r="E23" s="3" t="n">
+        <v>42532.44</v>
+      </c>
+      <c r="F23" s="3" t="n"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>39,516.16 Cr</t>
+          <t>47,391.43 Cr</t>
         </is>
       </c>
     </row>
@@ -1046,22 +1046,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>12-05-2026</t>
+          <t>08-05-2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>FIRE SAFETY INSPECTION &amp; EQUIPMENT REFILL</t>
+          <t>UPIAR/172136536211/DR/ZOMATO L/YESB/zomato-order@p</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="3" t="n">
-        <v>4001.3</v>
+        <v>373.12</v>
       </c>
       <c r="F24" s="3" t="n"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>35,514.86 Cr</t>
+          <t>47,018.31 Cr</t>
         </is>
       </c>
     </row>
@@ -1071,22 +1071,22 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>13-05-2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605132506/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605091844/CR</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n">
-        <v>5152.18</v>
+        <v>11021.2</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>40,667.04 Cr</t>
+          <t>58,039.51 Cr</t>
         </is>
       </c>
     </row>
@@ -1096,22 +1096,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13-05-2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/554433221100/DR/FLIPKART ONLINE</t>
+          <t>IMPS/OUTWARD/612984019283/RAW INGREDIENTS</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="3" t="n">
-        <v>3472.91</v>
+        <v>28977.56</v>
       </c>
       <c r="F26" s="3" t="n"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>37,194.13 Cr</t>
+          <t>29,061.95 Cr</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>14-05-2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605146813/CR</t>
+          <t>UPIAB/982301928371/CR/LOCAL VENDOR/ICIC/vendor@icici</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="n">
-        <v>3292.47</v>
+        <v>5483.17</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>40,486.60 Cr</t>
+          <t>34,545.12 Cr</t>
         </is>
       </c>
     </row>
@@ -1146,22 +1146,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>14-05-2026</t>
+          <t>10-05-2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>OFFICE PANTRY &amp; FRESH REFRESHMENTS</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605103737/CR</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="3" t="n">
-        <v>928.39</v>
-      </c>
-      <c r="F28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n">
+        <v>9292.969999999999</v>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>39,558.21 Cr</t>
+          <t>43,838.09 Cr</t>
         </is>
       </c>
     </row>
@@ -1171,22 +1171,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>15-05-2026</t>
+          <t>10-05-2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605156921/CR</t>
+          <t>UPIAR/110099887766/DR/OLA CABS</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n">
-        <v>2370.25</v>
-      </c>
+      <c r="E29" s="3" t="n">
+        <v>639.6799999999999</v>
+      </c>
+      <c r="F29" s="3" t="n"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>41,928.46 Cr</t>
+          <t>43,198.41 Cr</t>
         </is>
       </c>
     </row>
@@ -1196,22 +1196,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>15-05-2026</t>
+          <t>10-05-2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/812938102938/DR/PETROL PUMP/HPCL/hpcl@icici</t>
+          <t>UPIAB/800823341214/CR/PITCHIKA/CNRB/ umanag9712@ax</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="3" t="n">
-        <v>1296.24</v>
-      </c>
-      <c r="F30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n">
+        <v>3742.46</v>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>40,632.22 Cr</t>
+          <t>46,940.87 Cr</t>
         </is>
       </c>
     </row>
@@ -1221,22 +1221,22 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>16-05-2026</t>
+          <t>11-05-2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605161016/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605111210/CR</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n">
-        <v>2028.87</v>
+        <v>6385.62</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>42,661.09 Cr</t>
+          <t>53,326.49 Cr</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17-05-2026</t>
+          <t>11-05-2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605176240/CR</t>
+          <t>IMPS/OUTWARD/612984019283/RAW INGREDIENTS</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n">
-        <v>1338.08</v>
-      </c>
+      <c r="E32" s="3" t="n">
+        <v>20736.61</v>
+      </c>
+      <c r="F32" s="3" t="n"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>43,999.17 Cr</t>
+          <t>32,589.88 Cr</t>
         </is>
       </c>
     </row>
@@ -1271,22 +1271,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17-05-2026</t>
+          <t>11-05-2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/009988776655/CR/DIVIDEND PAYOUT</t>
+          <t>UPIAB/112938102938/CR/WHOLESALE MILK DEPOSIT</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="n">
-        <v>653.83</v>
+        <v>8992.610000000001</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>44,653.00 Cr</t>
+          <t>41,582.49 Cr</t>
         </is>
       </c>
     </row>
@@ -1296,22 +1296,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>18-05-2026</t>
+          <t>11-05-2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605184992/CR</t>
+          <t>PRINTING BARCODE LABELS &amp; BILLING ROLLS</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n">
-        <v>2225.84</v>
-      </c>
+      <c r="E34" s="3" t="n">
+        <v>3566.41</v>
+      </c>
+      <c r="F34" s="3" t="n"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>46,878.84 Cr</t>
+          <t>38,016.08 Cr</t>
         </is>
       </c>
     </row>
@@ -1321,22 +1321,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>19-05-2026</t>
+          <t>11-05-2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605196300/CR</t>
+          <t>UPIAB/624556864731/CR/PICHIKA/UBIN/pvasuviswanadh</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n">
-        <v>1083.31</v>
+        <v>2530.9</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>47,962.15 Cr</t>
+          <t>40,546.98 Cr</t>
         </is>
       </c>
     </row>
@@ -1346,22 +1346,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>19-05-2026</t>
+          <t>12-05-2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>DELIVERY ELECTRIC VAN MAINTENANCE &amp; AMC</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605121465/CR</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="3" t="n">
-        <v>3765.15</v>
-      </c>
-      <c r="F36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="n">
+        <v>8474.83</v>
+      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>44,197.00 Cr</t>
+          <t>49,021.81 Cr</t>
         </is>
       </c>
     </row>
@@ -1371,22 +1371,22 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20-05-2026</t>
+          <t>12-05-2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605201337/CR</t>
+          <t>BBMP MUNICIPAL TRADE LICENSE &amp; PROPERTY TAX</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n">
-        <v>6561.5</v>
-      </c>
+      <c r="E37" s="3" t="n">
+        <v>7620.26</v>
+      </c>
+      <c r="F37" s="3" t="n"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>50,758.50 Cr</t>
+          <t>41,401.55 Cr</t>
         </is>
       </c>
     </row>
@@ -1396,22 +1396,22 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>20-05-2026</t>
+          <t>12-05-2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/789123891023/CR/CUSTOMER REFUND REVERSAL</t>
+          <t>UPIAB/322671730620/CR/PITCHIKA/SBIN/ 8919861154@ax</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="3" t="n"/>
       <c r="F38" s="3" t="n">
-        <v>315.76</v>
+        <v>4868.35</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>51,074.26 Cr</t>
+          <t>46,269.90 Cr</t>
         </is>
       </c>
     </row>
@@ -1421,20 +1421,22 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>21-05-2026</t>
+          <t>12-05-2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605212278/CR</t>
+          <t>UPIAB/982301928371/CR/LOCAL VENDOR/ICIC/vendor@icici</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="3" t="n"/>
-      <c r="F39" s="3" t="n"/>
+      <c r="F39" s="3" t="n">
+        <v>6061.99</v>
+      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>36,217.28 Cr</t>
+          <t>52,331.89 Cr</t>
         </is>
       </c>
     </row>
@@ -1444,22 +1446,22 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>21-05-2026</t>
+          <t>13-05-2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/776655443322/CR/CASHBACK REWARD</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605137615/CR</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="n">
-        <v>94.56999999999999</v>
+        <v>10992.24</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>36,311.85 Cr</t>
+          <t>63,324.13 Cr</t>
         </is>
       </c>
     </row>
@@ -1469,22 +1471,22 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22-05-2026</t>
+          <t>13-05-2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605224668/CR</t>
+          <t>POINT OF SALE (POS) HARDWARE RENTAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n">
-        <v>5369.34</v>
-      </c>
+      <c r="E41" s="3" t="n">
+        <v>3006.57</v>
+      </c>
+      <c r="F41" s="3" t="n"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>41,681.19 Cr</t>
+          <t>60,317.56 Cr</t>
         </is>
       </c>
     </row>
@@ -1494,22 +1496,22 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>23-05-2026</t>
+          <t>13-05-2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605231921/CR</t>
+          <t>IMPS/OUTWARD/612984019283/RAW INGREDIENTS</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="3" t="n"/>
-      <c r="F42" s="3" t="n">
-        <v>4065.91</v>
-      </c>
+      <c r="E42" s="3" t="n">
+        <v>29835.58</v>
+      </c>
+      <c r="F42" s="3" t="n"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>45,747.10 Cr</t>
+          <t>30,481.98 Cr</t>
         </is>
       </c>
     </row>
@@ -1519,22 +1521,22 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>23-05-2026</t>
+          <t>14-05-2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/758331734676/DR/EKNATHB/YESB/ Q440089343@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605147037/CR</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="3" t="n">
-        <v>73.47</v>
-      </c>
-      <c r="F43" s="3" t="n"/>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n">
+        <v>7220.09</v>
+      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>45,673.63 Cr</t>
+          <t>37,702.07 Cr</t>
         </is>
       </c>
     </row>
@@ -1544,22 +1546,22 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>24-05-2026</t>
+          <t>14-05-2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605245466/CR</t>
+          <t>UPIAB/112938102938/CR/WHOLESALE MILK DEPOSIT</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n">
-        <v>1799.6</v>
+        <v>7136.39</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>47,473.23 Cr</t>
+          <t>44,838.46 Cr</t>
         </is>
       </c>
     </row>
@@ -1569,22 +1571,22 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>24-05-2026</t>
+          <t>14-05-2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/322671730620/CR/PITCHIKA/SBIN/ 8919861154@ax</t>
+          <t>UPIAR/908129381023/DR/BILLDESK/SBIN/billdesk@sbi</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n">
-        <v>3090.7</v>
-      </c>
+      <c r="E45" s="3" t="n">
+        <v>982.76</v>
+      </c>
+      <c r="F45" s="3" t="n"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>50,563.93 Cr</t>
+          <t>43,855.70 Cr</t>
         </is>
       </c>
     </row>
@@ -1594,22 +1596,22 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>25-05-2026</t>
+          <t>15-05-2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605253073/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605156893/CR</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="n">
-        <v>5395.74</v>
+        <v>4029.1</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>55,959.67 Cr</t>
+          <t>47,884.80 Cr</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1621,22 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>25-05-2026</t>
+          <t>15-05-2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/221100998877/DR/UBER RIDE</t>
+          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="3" t="n">
-        <v>791.28</v>
+        <v>9131.35</v>
       </c>
       <c r="F47" s="3" t="n"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>55,168.39 Cr</t>
+          <t>38,753.45 Cr</t>
         </is>
       </c>
     </row>
@@ -1644,22 +1646,22 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>26-05-2026</t>
+          <t>16-05-2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605265570/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605169287/CR</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="3" t="n"/>
       <c r="F48" s="3" t="n">
-        <v>2419.16</v>
+        <v>8072.58</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>57,587.55 Cr</t>
+          <t>46,826.03 Cr</t>
         </is>
       </c>
     </row>
@@ -1669,22 +1671,22 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27-05-2026</t>
+          <t>17-05-2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605278688/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605175626/CR</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="3" t="n"/>
       <c r="F49" s="3" t="n">
-        <v>1713</v>
+        <v>5966.26</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>59,300.55 Cr</t>
+          <t>52,792.29 Cr</t>
         </is>
       </c>
     </row>
@@ -1694,22 +1696,22 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>28-05-2026</t>
+          <t>17-05-2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605288138/CR</t>
+          <t>PRINTING BARCODE LABELS &amp; BILLING ROLLS</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
-      <c r="E50" s="3" t="n"/>
-      <c r="F50" s="3" t="n">
-        <v>3491.81</v>
-      </c>
+      <c r="E50" s="3" t="n">
+        <v>4014.41</v>
+      </c>
+      <c r="F50" s="3" t="n"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>62,792.36 Cr</t>
+          <t>48,777.88 Cr</t>
         </is>
       </c>
     </row>
@@ -1719,22 +1721,22 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>28-05-2026</t>
+          <t>17-05-2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/800823341214/CR/PITCHIKA/CNRB/ umanag9712@ax</t>
+          <t>UPIAR/172136536211/DR/ZOMATO L/YESB/zomato-order@p</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
-      <c r="E51" s="3" t="n"/>
-      <c r="F51" s="3" t="n">
-        <v>1892.79</v>
-      </c>
+      <c r="E51" s="3" t="n">
+        <v>363.1</v>
+      </c>
+      <c r="F51" s="3" t="n"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>64,685.15 Cr</t>
+          <t>48,414.78 Cr</t>
         </is>
       </c>
     </row>
@@ -1744,22 +1746,22 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>28-05-2026</t>
+          <t>17-05-2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>JNS-PMSBY-25-26-00289608474-301-631272322</t>
+          <t>UPIAB/020074062699/CR/THIRUVEE/UBIN/9391652831-2@a</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F52" s="3" t="n"/>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="3" t="n">
+        <v>1074.2</v>
+      </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>64,665.15 Cr</t>
+          <t>49,488.98 Cr</t>
         </is>
       </c>
     </row>
@@ -1769,22 +1771,22 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>29-05-2026</t>
+          <t>18-05-2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605291374/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605182352/CR</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="3" t="n"/>
       <c r="F53" s="3" t="n">
-        <v>3946.78</v>
+        <v>19323.76</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>68,611.93 Cr</t>
+          <t>68,812.74 Cr</t>
         </is>
       </c>
     </row>
@@ -1794,22 +1796,22 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>29-05-2026</t>
+          <t>19-05-2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/857830578859/DR/GAURAV S/YESB/ Q815875629@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605199306/CR</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
-      <c r="E54" s="3" t="n">
-        <v>149.58</v>
-      </c>
-      <c r="F54" s="3" t="n"/>
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="3" t="n">
+        <v>5326.49</v>
+      </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>68,462.35 Cr</t>
+          <t>74,139.23 Cr</t>
         </is>
       </c>
     </row>
@@ -1819,22 +1821,22 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>29-05-2026</t>
+          <t>19-05-2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
+          <t>INVENTORY AUDITOR &amp; CA LEGAL RETAINER</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" s="3" t="n">
-        <v>6744.81</v>
+        <v>13944.92</v>
       </c>
       <c r="F55" s="3" t="n"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>61,717.54 Cr</t>
+          <t>60,194.31 Cr</t>
         </is>
       </c>
     </row>
@@ -1844,22 +1846,22 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>30-05-2026</t>
+          <t>19-05-2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605301613/CR</t>
+          <t>AIRTEL CORPORATE BROADBAND &amp; FIBER</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
-      <c r="E56" s="3" t="n"/>
-      <c r="F56" s="3" t="n">
-        <v>2715.78</v>
-      </c>
+      <c r="E56" s="3" t="n">
+        <v>3800.84</v>
+      </c>
+      <c r="F56" s="3" t="n"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>64,433.32 Cr</t>
+          <t>56,393.47 Cr</t>
         </is>
       </c>
     </row>
@@ -1869,22 +1871,22 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>31-05-2026</t>
+          <t>19-05-2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605318148/CR</t>
+          <t>IMPS/INWARD/SBIN/DISTRIBUTOR SETTLEMENT</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="3" t="n"/>
       <c r="F57" s="3" t="n">
-        <v>1439.06</v>
+        <v>18257.54</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>65,872.38 Cr</t>
+          <t>74,651.01 Cr</t>
         </is>
       </c>
     </row>
@@ -1894,22 +1896,22 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>01-06-2026</t>
+          <t>20-05-2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606012274/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605204772/CR</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="3" t="n"/>
       <c r="F58" s="3" t="n">
-        <v>2937.24</v>
+        <v>6584.4</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>68,809.62 Cr</t>
+          <t>81,235.41 Cr</t>
         </is>
       </c>
     </row>
@@ -1919,22 +1921,22 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>02-06-2026</t>
+          <t>20-05-2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606029493/CR</t>
+          <t>UPIAR/887766554433/DR/BHARATPE MERCHANT</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
-      <c r="E59" s="3" t="n"/>
-      <c r="F59" s="3" t="n">
-        <v>2156.35</v>
-      </c>
+      <c r="E59" s="3" t="n">
+        <v>127.65</v>
+      </c>
+      <c r="F59" s="3" t="n"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>70,965.97 Cr</t>
+          <t>81,107.76 Cr</t>
         </is>
       </c>
     </row>
@@ -1944,22 +1946,22 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>02-06-2026</t>
+          <t>20-05-2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>BANK SMS ALERTS &amp; ANNUAL MAINT CHARGES</t>
+          <t>UPIAR/123854061954/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="3" t="n">
-        <v>145.18</v>
+        <v>349.38</v>
       </c>
       <c r="F60" s="3" t="n"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>70,820.79 Cr</t>
+          <t>80,758.38 Cr</t>
         </is>
       </c>
     </row>
@@ -1969,22 +1971,22 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>02-06-2026</t>
+          <t>20-05-2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/887766554433/DR/BHARATPE MERCHANT</t>
+          <t>UPIAB/112938102938/CR/WHOLESALE MILK DEPOSIT</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
-      <c r="E61" s="3" t="n">
-        <v>87.59</v>
-      </c>
-      <c r="F61" s="3" t="n"/>
+      <c r="E61" s="3" t="n"/>
+      <c r="F61" s="3" t="n">
+        <v>5899.53</v>
+      </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>70,733.20 Cr</t>
+          <t>86,657.91 Cr</t>
         </is>
       </c>
     </row>
@@ -1994,22 +1996,22 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>03-06-2026</t>
+          <t>21-05-2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606036395/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605217887/CR</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="3" t="n"/>
       <c r="F62" s="3" t="n">
-        <v>2294.85</v>
+        <v>10256.72</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>73,028.05 Cr</t>
+          <t>96,914.63 Cr</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2021,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>03-06-2026</t>
+          <t>21-05-2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -2029,12 +2031,12 @@
       </c>
       <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" s="3" t="n">
-        <v>3673.99</v>
+        <v>11525.78</v>
       </c>
       <c r="F63" s="3" t="n"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>69,354.06 Cr</t>
+          <t>85,388.85 Cr</t>
         </is>
       </c>
     </row>
@@ -2044,22 +2046,22 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>04-06-2026</t>
+          <t>21-05-2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606043854/CR</t>
+          <t>UPIAR/301984712093/DR/SWIGGY/HDFC/swiggy@hdfc</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="3" t="n"/>
-      <c r="F64" s="3" t="n">
-        <v>2377.39</v>
-      </c>
+      <c r="E64" s="3" t="n">
+        <v>449.59</v>
+      </c>
+      <c r="F64" s="3" t="n"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>71,731.45 Cr</t>
+          <t>84,939.26 Cr</t>
         </is>
       </c>
     </row>
@@ -2069,22 +2071,22 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>05-06-2026</t>
+          <t>21-05-2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606051953/CR</t>
+          <t>PRINTING BARCODE LABELS &amp; BILLING ROLLS</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
-      <c r="E65" s="3" t="n"/>
-      <c r="F65" s="3" t="n">
-        <v>3174.71</v>
-      </c>
+      <c r="E65" s="3" t="n">
+        <v>2032.79</v>
+      </c>
+      <c r="F65" s="3" t="n"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>74,906.16 Cr</t>
+          <t>82,906.47 Cr</t>
         </is>
       </c>
     </row>
@@ -2094,22 +2096,22 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05-06-2026</t>
+          <t>21-05-2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/124934775512/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+          <t>UPIAR/347067657684/DR/KAJALVI/YESB/paytm.s1w3jr9@</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="3" t="n">
-        <v>596.41</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="F66" s="3" t="n"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>74,309.75 Cr</t>
+          <t>82,821.54 Cr</t>
         </is>
       </c>
     </row>
@@ -2119,22 +2121,22 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05-06-2026</t>
+          <t>21-05-2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COMMERCIAL WAREHOUSE RENT / KORAMANGALA HUB</t>
+          <t>IMPS/INWARD/SBIN/DISTRIBUTOR SETTLEMENT</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
-      <c r="E67" s="3" t="n">
-        <v>40641.57</v>
-      </c>
-      <c r="F67" s="3" t="n"/>
+      <c r="E67" s="3" t="n"/>
+      <c r="F67" s="3" t="n">
+        <v>26086.66</v>
+      </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>33,668.18 Cr</t>
+          <t>108,908.20 Cr</t>
         </is>
       </c>
     </row>
@@ -2144,22 +2146,22 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>06-06-2026</t>
+          <t>21-05-2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606063856/CR</t>
+          <t>FIRE SAFETY INSPECTION &amp; EQUIPMENT REFILL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
-      <c r="E68" s="3" t="n"/>
-      <c r="F68" s="3" t="n">
-        <v>6900.09</v>
-      </c>
+      <c r="E68" s="3" t="n">
+        <v>4512.03</v>
+      </c>
+      <c r="F68" s="3" t="n"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>40,568.27 Cr</t>
+          <t>104,396.17 Cr</t>
         </is>
       </c>
     </row>
@@ -2169,22 +2171,20 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>06-06-2026</t>
+          <t>22-05-2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>GST ADVANCE TAX DEPOSIT / GOVT OF INDIA</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605226209/CR</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
-      <c r="E69" s="3" t="n">
-        <v>15157.8</v>
-      </c>
+      <c r="E69" s="3" t="n"/>
       <c r="F69" s="3" t="n"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>25,410.47 Cr</t>
+          <t>92,100.83 Cr</t>
         </is>
       </c>
     </row>
@@ -2194,22 +2194,22 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07-06-2026</t>
+          <t>22-05-2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606074542/CR</t>
+          <t>UPIAB/009988776655/CR/DIVIDEND PAYOUT</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="3" t="n"/>
       <c r="F70" s="3" t="n">
-        <v>2737.58</v>
+        <v>1183.78</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>28,148.05 Cr</t>
+          <t>93,284.61 Cr</t>
         </is>
       </c>
     </row>
@@ -2219,22 +2219,22 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07-06-2026</t>
+          <t>22-05-2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>ATM CASH WITHDRAWAL / KORAMANGALA BRANCH</t>
+          <t>UPIAB/512938102938/CR/SUPPLIER CREDIT NOTE</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
-      <c r="E71" s="3" t="n">
-        <v>3503.7</v>
-      </c>
-      <c r="F71" s="3" t="n"/>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n">
+        <v>7451.93</v>
+      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>24,644.35 Cr</t>
+          <t>100,736.54 Cr</t>
         </is>
       </c>
     </row>
@@ -2244,22 +2244,22 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>07-06-2026</t>
+          <t>22-05-2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/624556864731/CR/PICHIKA/UBIN/pvasuviswanadh</t>
+          <t>UPIAR/123854061954/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
-      <c r="E72" s="3" t="n"/>
-      <c r="F72" s="3" t="n">
-        <v>2909.67</v>
-      </c>
+      <c r="E72" s="3" t="n">
+        <v>261.63</v>
+      </c>
+      <c r="F72" s="3" t="n"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>27,554.02 Cr</t>
+          <t>100,474.91 Cr</t>
         </is>
       </c>
     </row>
@@ -2269,22 +2269,22 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>23-05-2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606086147/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605235998/CR</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="3" t="n"/>
       <c r="F73" s="3" t="n">
-        <v>2741.18</v>
+        <v>6737.43</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>30,295.20 Cr</t>
+          <t>107,212.34 Cr</t>
         </is>
       </c>
     </row>
@@ -2294,22 +2294,22 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>09-06-2026</t>
+          <t>23-05-2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606097478/CR</t>
+          <t>AWS CLOUD SERVER HOSTING &amp; INFRASTRUCTURE</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
-      <c r="E74" s="3" t="n"/>
-      <c r="F74" s="3" t="n">
-        <v>2555.81</v>
-      </c>
+      <c r="E74" s="3" t="n">
+        <v>6965.54</v>
+      </c>
+      <c r="F74" s="3" t="n"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>32,851.01 Cr</t>
+          <t>100,246.80 Cr</t>
         </is>
       </c>
     </row>
@@ -2319,22 +2319,22 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>10-06-2026</t>
+          <t>23-05-2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606103106/CR</t>
+          <t>UPIAR/717134959917/DR/AoapAmr/AIRP/AoapAmrita.pay</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
-      <c r="E75" s="3" t="n"/>
-      <c r="F75" s="3" t="n">
-        <v>3225.23</v>
-      </c>
+      <c r="E75" s="3" t="n">
+        <v>3916.23</v>
+      </c>
+      <c r="F75" s="3" t="n"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>36,076.24 Cr</t>
+          <t>96,330.57 Cr</t>
         </is>
       </c>
     </row>
@@ -2344,22 +2344,22 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>24-05-2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606117859/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605249699/CR</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="3" t="n"/>
       <c r="F76" s="3" t="n">
-        <v>3226.24</v>
+        <v>13825.8</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>39,302.48 Cr</t>
+          <t>110,156.37 Cr</t>
         </is>
       </c>
     </row>
@@ -2369,22 +2369,22 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>24-05-2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/512938102938/CR/SUPPLIER CREDIT NOTE</t>
+          <t>UPIAR/026544681447/DR/SHANTIP/YESB/ Q707874078@yb</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
-      <c r="E77" s="3" t="n"/>
-      <c r="F77" s="3" t="n">
-        <v>6585.44</v>
-      </c>
+      <c r="E77" s="3" t="n">
+        <v>434.24</v>
+      </c>
+      <c r="F77" s="3" t="n"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>45,887.92 Cr</t>
+          <t>109,722.13 Cr</t>
         </is>
       </c>
     </row>
@@ -2394,22 +2394,22 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>24-05-2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606125662/CR</t>
+          <t>UPIAB/624556864731/CR/PICHIKA/UBIN/pvasuviswanadh</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="3" t="n"/>
       <c r="F78" s="3" t="n">
-        <v>3295.52</v>
+        <v>1029.33</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>49,183.44 Cr</t>
+          <t>110,751.46 Cr</t>
         </is>
       </c>
     </row>
@@ -2419,22 +2419,22 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>13-06-2026</t>
+          <t>25-05-2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606137592/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605255186/CR</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
       <c r="E79" s="3" t="n"/>
       <c r="F79" s="3" t="n">
-        <v>3820.33</v>
+        <v>4101.67</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>53,003.77 Cr</t>
+          <t>114,853.13 Cr</t>
         </is>
       </c>
     </row>
@@ -2444,22 +2444,22 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>14-06-2026</t>
+          <t>25-05-2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606146866/CR</t>
+          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
-      <c r="E80" s="3" t="n"/>
-      <c r="F80" s="3" t="n">
-        <v>1541.88</v>
-      </c>
+      <c r="E80" s="3" t="n">
+        <v>7400.34</v>
+      </c>
+      <c r="F80" s="3" t="n"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>54,545.65 Cr</t>
+          <t>107,452.79 Cr</t>
         </is>
       </c>
     </row>
@@ -2469,22 +2469,1447 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>15-06-2026</t>
+          <t>25-05-2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606152898/CR</t>
+          <t>UPIAB/776655443322/CR/CASHBACK REWARD</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" s="3" t="n"/>
       <c r="F81" s="3" t="n">
-        <v>1992.19</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>56,537.84 Cr</t>
+          <t>107,543.69 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>26-05-2026</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605269206/CR</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="3" t="n"/>
+      <c r="F82" s="3" t="n">
+        <v>8705.469999999999</v>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>116,249.16 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>26-05-2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/271988123471/CR/THIRUVEE/UBIN/9391652831-2@a</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
+      <c r="E83" s="3" t="n"/>
+      <c r="F83" s="3" t="n">
+        <v>306.93</v>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>116,556.09 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>27-05-2026</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605272228/CR</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
+      <c r="E84" s="3" t="n"/>
+      <c r="F84" s="3" t="n">
+        <v>7104.13</v>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>123,660.22 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>27-05-2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/512938102938/CR/SUPPLIER CREDIT NOTE</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr"/>
+      <c r="E85" s="3" t="n"/>
+      <c r="F85" s="3" t="n">
+        <v>6521.31</v>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>130,181.53 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>27-05-2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>SECURITY GUARD SERVICES &amp; CCTV MONITORING</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr"/>
+      <c r="E86" s="3" t="n">
+        <v>5510.81</v>
+      </c>
+      <c r="F86" s="3" t="n"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>124,670.72 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>27-05-2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/998877665544/DR/PAYTM QR VENDOR</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
+      <c r="E87" s="3" t="n">
+        <v>99.29000000000001</v>
+      </c>
+      <c r="F87" s="3" t="n"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>124,571.43 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>28-05-2026</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605283489/CR</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="n">
+        <v>5608.5</v>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>130,179.93 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>28-05-2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>LIC PREMIUM AUTO DEBIT CLEARING</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr"/>
+      <c r="E89" s="3" t="n">
+        <v>5555.55</v>
+      </c>
+      <c r="F89" s="3" t="n"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>124,624.38 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>28-05-2026</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>NEFT/INWARD/CITI/GROCERY WHOLESALE REBATE</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
+      <c r="E90" s="3" t="n"/>
+      <c r="F90" s="3" t="n">
+        <v>11668.55</v>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>136,292.93 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>29-05-2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605293912/CR</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr"/>
+      <c r="E91" s="3" t="n"/>
+      <c r="F91" s="3" t="n">
+        <v>7973.41</v>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>144,266.34 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>29-05-2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/143302589531/DR/Zomato87/AIRP/Zomato8759546.</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr"/>
+      <c r="E92" s="3" t="n">
+        <v>223.7</v>
+      </c>
+      <c r="F92" s="3" t="n"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>144,042.64 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>29-05-2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/812938102938/DR/PETROL PUMP/HPCL/hpcl@icici</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr"/>
+      <c r="E93" s="3" t="n">
+        <v>1238.57</v>
+      </c>
+      <c r="F93" s="3" t="n"/>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>142,804.07 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>29-05-2026</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>BBMP MUNICIPAL TRADE LICENSE &amp; PROPERTY TAX</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr"/>
+      <c r="E94" s="3" t="n">
+        <v>7476.97</v>
+      </c>
+      <c r="F94" s="3" t="n"/>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>135,327.10 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>30-05-2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605306330/CR</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr"/>
+      <c r="E95" s="3" t="n"/>
+      <c r="F95" s="3" t="n">
+        <v>6675.73</v>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>142,002.83 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>30-05-2026</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/347067657684/DR/KAJALVI/YESB/paytm.s1w3jr9@</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr"/>
+      <c r="E96" s="3" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="F96" s="3" t="n"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>141,981.06 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>30-05-2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>NEFT/OUTWARD/HDFC/FARMERS COOP SUPPLY</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr"/>
+      <c r="E97" s="3" t="n">
+        <v>24044.71</v>
+      </c>
+      <c r="F97" s="3" t="n"/>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>117,936.35 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>30-05-2026</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/800823341214/CR/PITCHIKA/CNRB/ umanag9712@ax</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr"/>
+      <c r="E98" s="3" t="n"/>
+      <c r="F98" s="3" t="n">
+        <v>2328.93</v>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>120,265.28 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31-05-2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605312613/CR</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr"/>
+      <c r="E99" s="3" t="n"/>
+      <c r="F99" s="3" t="n">
+        <v>9803.440000000001</v>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>130,068.72 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>31-05-2026</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>CHQ PAID / CLEARING NO 004812</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr"/>
+      <c r="E100" s="3" t="n">
+        <v>13781.91</v>
+      </c>
+      <c r="F100" s="3" t="n"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>116,286.81 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01-06-2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606018346/CR</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr"/>
+      <c r="E101" s="3" t="n"/>
+      <c r="F101" s="3" t="n">
+        <v>7992.78</v>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>124,279.59 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>01-06-2026</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/554433221100/DR/FLIPKART ONLINE</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
+      <c r="E102" s="3" t="n">
+        <v>2906.55</v>
+      </c>
+      <c r="F102" s="3" t="n"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>121,373.04 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>02-06-2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606024469/CR</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr"/>
+      <c r="E103" s="3" t="n"/>
+      <c r="F103" s="3" t="n">
+        <v>8293.75</v>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>129,666.79 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>02-06-2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/776655443322/CR/CASHBACK REWARD</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr"/>
+      <c r="E104" s="3" t="n"/>
+      <c r="F104" s="3" t="n">
+        <v>84.95</v>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>129,751.74 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>02-06-2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>POINT OF SALE (POS) HARDWARE RENTAL</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr"/>
+      <c r="E105" s="3" t="n">
+        <v>3957.45</v>
+      </c>
+      <c r="F105" s="3" t="n"/>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>125,794.29 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>02-06-2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>AIRTEL CORPORATE BROADBAND &amp; FIBER</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr"/>
+      <c r="E106" s="3" t="n">
+        <v>1578.57</v>
+      </c>
+      <c r="F106" s="3" t="n"/>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>124,215.72 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>03-06-2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606034693/CR</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr"/>
+      <c r="E107" s="3" t="n"/>
+      <c r="F107" s="3" t="n">
+        <v>10108.84</v>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>134,324.56 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>04-06-2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606045227/CR</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr"/>
+      <c r="E108" s="3" t="n"/>
+      <c r="F108" s="3" t="n">
+        <v>4330.17</v>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>138,654.73 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>04-06-2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr"/>
+      <c r="E109" s="3" t="n"/>
+      <c r="F109" s="3" t="n">
+        <v>1770.13</v>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>140,424.86 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>04-06-2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/143302589531/DR/Zomato87/AIRP/Zomato8759546.</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr"/>
+      <c r="E110" s="3" t="n">
+        <v>361.34</v>
+      </c>
+      <c r="F110" s="3" t="n"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>140,063.52 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>05-06-2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606051406/CR</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr"/>
+      <c r="E111" s="3" t="n"/>
+      <c r="F111" s="3" t="n">
+        <v>18379.48</v>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>158,443.00 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>05-06-2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/789123891023/CR/CUSTOMER REFUND REVERSAL</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr"/>
+      <c r="E112" s="3" t="n"/>
+      <c r="F112" s="3" t="n">
+        <v>687.28</v>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>159,130.28 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>05-06-2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/624556864731/CR/PICHIKA/UBIN/pvasuviswanadh</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr"/>
+      <c r="E113" s="3" t="n"/>
+      <c r="F113" s="3" t="n">
+        <v>1706.11</v>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>160,836.39 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>05-06-2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>BBMP MUNICIPAL TRADE LICENSE &amp; PROPERTY TAX</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr"/>
+      <c r="E114" s="3" t="n">
+        <v>5653.52</v>
+      </c>
+      <c r="F114" s="3" t="n"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>155,182.87 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06-06-2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606066449/CR</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr"/>
+      <c r="E115" s="3" t="n"/>
+      <c r="F115" s="3" t="n">
+        <v>3259.97</v>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>158,442.84 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>06-06-2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/665544332211/DR/AMAZON INDIA</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr"/>
+      <c r="E116" s="3" t="n">
+        <v>751.45</v>
+      </c>
+      <c r="F116" s="3" t="n"/>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>157,691.39 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>06-06-2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr"/>
+      <c r="E117" s="3" t="n"/>
+      <c r="F117" s="3" t="n">
+        <v>1851.57</v>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>159,542.96 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>07-06-2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606076055/CR</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr"/>
+      <c r="E118" s="3" t="n"/>
+      <c r="F118" s="3" t="n">
+        <v>11921.83</v>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>171,464.79 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>07-06-2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/512938102938/CR/SUPPLIER CREDIT NOTE</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr"/>
+      <c r="E119" s="3" t="n"/>
+      <c r="F119" s="3" t="n">
+        <v>9941.51</v>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>181,406.30 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>07-06-2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/278079065373/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr"/>
+      <c r="E120" s="3" t="n">
+        <v>338.96</v>
+      </c>
+      <c r="F120" s="3" t="n"/>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>181,067.34 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>07-06-2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/020074062699/CR/THIRUVEE/UBIN/9391652831-2@a</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr"/>
+      <c r="E121" s="3" t="n"/>
+      <c r="F121" s="3" t="n">
+        <v>243.72</v>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>181,311.06 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>08-06-2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606084936/CR</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr"/>
+      <c r="E122" s="3" t="n"/>
+      <c r="F122" s="3" t="n">
+        <v>4662.51</v>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>185,973.57 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>09-06-2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606097885/CR</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr"/>
+      <c r="E123" s="3" t="n"/>
+      <c r="F123" s="3" t="n">
+        <v>4421.52</v>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>190,395.09 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>09-06-2026</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>COMMERCIAL WAREHOUSE RENT / KORAMANGALA HUB</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr"/>
+      <c r="E124" s="3" t="n">
+        <v>39913.06</v>
+      </c>
+      <c r="F124" s="3" t="n"/>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>150,482.03 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606106884/CR</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr"/>
+      <c r="E125" s="3" t="n"/>
+      <c r="F125" s="3" t="n">
+        <v>10876.82</v>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>161,358.85 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/512938102938/CR/SUPPLIER CREDIT NOTE</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr"/>
+      <c r="E126" s="3" t="n"/>
+      <c r="F126" s="3" t="n">
+        <v>8552.42</v>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>169,911.27 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>10-06-2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/332211009988/DR/BOOKMYSHOW TICKET</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr"/>
+      <c r="E127" s="3" t="n">
+        <v>908.03</v>
+      </c>
+      <c r="F127" s="3" t="n"/>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>169,003.24 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>11-06-2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606117995/CR</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr"/>
+      <c r="E128" s="3" t="n"/>
+      <c r="F128" s="3" t="n">
+        <v>8671.76</v>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>177,675.00 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>11-06-2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>NEFT/OUTWARD/UTI MUTUAL FUND SIP</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr"/>
+      <c r="E129" s="3" t="n">
+        <v>3291.97</v>
+      </c>
+      <c r="F129" s="3" t="n"/>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>174,383.03 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>11-06-2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/443322110099/CR/PROMO DISCOUNT CREDIT</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr"/>
+      <c r="E130" s="3" t="n"/>
+      <c r="F130" s="3" t="n">
+        <v>173.48</v>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>174,556.51 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>12-06-2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606125659/CR</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr"/>
+      <c r="E131" s="3" t="n"/>
+      <c r="F131" s="3" t="n">
+        <v>14422.54</v>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>188,979.05 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>13-06-2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606137956/CR</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr"/>
+      <c r="E132" s="3" t="n"/>
+      <c r="F132" s="3" t="n">
+        <v>5866.92</v>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>194,845.97 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>13-06-2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/124934775512/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr"/>
+      <c r="E133" s="3" t="n">
+        <v>133.17</v>
+      </c>
+      <c r="F133" s="3" t="n"/>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>194,712.80 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>14-06-2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606143292/CR</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr"/>
+      <c r="E134" s="3" t="n"/>
+      <c r="F134" s="3" t="n">
+        <v>6726.58</v>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>201,439.38 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>14-06-2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/332211009988/DR/BOOKMYSHOW TICKET</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr"/>
+      <c r="E135" s="3" t="n">
+        <v>395.77</v>
+      </c>
+      <c r="F135" s="3" t="n"/>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>201,043.61 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>14-06-2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/908129381023/DR/BILLDESK/SBIN/billdesk@sbi</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr"/>
+      <c r="E136" s="3" t="n">
+        <v>1042.09</v>
+      </c>
+      <c r="F136" s="3" t="n"/>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>200,001.52 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606154135/CR</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr"/>
+      <c r="E137" s="3" t="n"/>
+      <c r="F137" s="3" t="n">
+        <v>2097.48</v>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>202,099.00 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/112938102938/CR/WHOLESALE MILK DEPOSIT</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr"/>
+      <c r="E138" s="3" t="n"/>
+      <c r="F138" s="3" t="n">
+        <v>7110.08</v>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>209,209.08 Cr</t>
         </is>
       </c>
     </row>

--- a/generated_data/bank_statement_union_bank.xlsx
+++ b/generated_data/bank_statement_union_bank.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,17 +501,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605014040/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605011427/CR</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n">
-        <v>11741.28</v>
+        <v>2287.46</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>21,741.28 Cr</t>
+          <t>17,287.46 Cr</t>
         </is>
       </c>
     </row>
@@ -521,22 +521,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>02-05-2026</t>
+          <t>01-05-2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605025256/CR</t>
+          <t>UPIAR/554433221100/DR/FLIPKART ONLINE</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n">
-        <v>9586.879999999999</v>
-      </c>
+      <c r="E3" s="3" t="n">
+        <v>1497.57</v>
+      </c>
+      <c r="F3" s="3" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>31,328.16 Cr</t>
+          <t>15,789.89 Cr</t>
         </is>
       </c>
     </row>
@@ -546,22 +546,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>03-05-2026</t>
+          <t>02-05-2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605031750/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605028087/CR</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n">
-        <v>4723.37</v>
+        <v>6400</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>36,051.53 Cr</t>
+          <t>22,189.89 Cr</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>03-05-2026</t>
+          <t>02-05-2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
+          <t>UPIAB/271988123471/CR/THIRUVEE/UBIN/9391652831-2@a</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n">
-        <v>2243.54</v>
+        <v>167.47</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,295.07 Cr</t>
+          <t>22,357.36 Cr</t>
         </is>
       </c>
     </row>
@@ -596,22 +596,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>03-05-2026</t>
+          <t>02-05-2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/539631629714/CR/TAIESWA/PPIW/6302476334.wal</t>
+          <t>NEFT/OUTWARD/UTI MUTUAL FUND SIP</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n">
-        <v>252.84</v>
-      </c>
+      <c r="E6" s="3" t="n">
+        <v>9214.370000000001</v>
+      </c>
+      <c r="F6" s="3" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>38,547.91 Cr</t>
+          <t>13,142.99 Cr</t>
         </is>
       </c>
     </row>
@@ -621,22 +621,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>03-05-2026</t>
+          <t>02-05-2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/624556864731/CR/PICHIKA/UBIN/pvasuviswanadh</t>
+          <t>UPIAB/776655443322/CR/CASHBACK REWARD</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n">
-        <v>1498.43</v>
+        <v>146.29</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,046.34 Cr</t>
+          <t>13,289.28 Cr</t>
         </is>
       </c>
     </row>
@@ -651,17 +651,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/204208208508/DR/Zomato87/AIRP/Zomato8759546.</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605036742/CR</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="3" t="n">
-        <v>277.44</v>
-      </c>
-      <c r="F8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n">
+        <v>8984.190000000001</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>39,768.90 Cr</t>
+          <t>22,273.47 Cr</t>
         </is>
       </c>
     </row>
@@ -676,17 +676,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
+          <t>WATER TANKER &amp; SANITATION CHARGES</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n">
-        <v>2020.67</v>
-      </c>
+      <c r="E9" s="3" t="n">
+        <v>3463.18</v>
+      </c>
+      <c r="F9" s="3" t="n"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,789.57 Cr</t>
+          <t>18,810.29 Cr</t>
         </is>
       </c>
     </row>
@@ -701,17 +701,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/719421374678/DR/NEWKRSN/YESB/paytmqr6a0ixr@</t>
+          <t>UPIAR/908129381023/DR/BILLDESK/SBIN/billdesk@sbi</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="3" t="n">
-        <v>79.03</v>
+        <v>1167.7</v>
       </c>
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>41,710.54 Cr</t>
+          <t>17,642.59 Cr</t>
         </is>
       </c>
     </row>
@@ -726,17 +726,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605043970/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605049127/CR</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n">
-        <v>15024.94</v>
+        <v>3923.73</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,735.48 Cr</t>
+          <t>21,566.32 Cr</t>
         </is>
       </c>
     </row>
@@ -746,22 +746,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>05-05-2026</t>
+          <t>04-05-2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605052676/CR</t>
+          <t>UPIAR/455944913251/DR/KEMSARAP/SBIN/ 8977604821@yb</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n">
-        <v>12975.09</v>
-      </c>
+      <c r="E12" s="3" t="n">
+        <v>74.31999999999999</v>
+      </c>
+      <c r="F12" s="3" t="n"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>69,710.57 Cr</t>
+          <t>21,492.00 Cr</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/026544681447/DR/SHANTIP/YESB/ Q707874078@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605054959/CR</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
-      <c r="E13" s="3" t="n">
-        <v>874.8200000000001</v>
-      </c>
-      <c r="F13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n">
+        <v>4448.73</v>
+      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>68,835.75 Cr</t>
+          <t>25,940.73 Cr</t>
         </is>
       </c>
     </row>
@@ -796,22 +796,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>06-05-2026</t>
+          <t>05-05-2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605068706/CR</t>
+          <t>UPIAB/712626244599/CR/PICHIKA/BARB/ 8985068499@ax</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n">
-        <v>5730.49</v>
+        <v>491.8</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>74,566.24 Cr</t>
+          <t>26,432.53 Cr</t>
         </is>
       </c>
     </row>
@@ -821,22 +821,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>06-05-2026</t>
+          <t>05-05-2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/123854061954/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+          <t>WATER TANKER &amp; SANITATION CHARGES</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="3" t="n">
-        <v>339.97</v>
+        <v>2569.68</v>
       </c>
       <c r="F15" s="3" t="n"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>74,226.27 Cr</t>
+          <t>23,862.85 Cr</t>
         </is>
       </c>
     </row>
@@ -846,22 +846,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>06-05-2026</t>
+          <t>05-05-2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>BANK SMS ALERTS &amp; ANNUAL MAINT CHARGES</t>
+          <t>COMMERCIAL WAREHOUSE RENT / KORAMANGALA HUB</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="3" t="n">
-        <v>117.04</v>
+        <v>39005.09</v>
       </c>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>74,109.23 Cr</t>
+          <t>-15,142.24 Cr</t>
         </is>
       </c>
     </row>
@@ -876,17 +876,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/619283019283/DR/D-MART/HDFC/dmart@hdfc</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605067549/CR</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="3" t="n">
-        <v>2201.74</v>
-      </c>
-      <c r="F17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n">
+        <v>2245.42</v>
+      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>71,907.49 Cr</t>
+          <t>-12,896.82 Cr</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/800823341214/CR/PITCHIKA/CNRB/ umanag9712@ax</t>
+          <t>UPIAB/009988776655/CR/DIVIDEND PAYOUT</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n">
-        <v>3356.39</v>
+        <v>1310.58</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>75,263.88 Cr</t>
+          <t>-11,586.24 Cr</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/140288398543/DR/73374590/PUNB/7337459005@pty</t>
+          <t>LIC PREMIUM AUTO DEBIT CLEARING</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="3" t="n">
-        <v>146.28</v>
+        <v>9851.209999999999</v>
       </c>
       <c r="F19" s="3" t="n"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>75,117.60 Cr</t>
+          <t>-21,437.45 Cr</t>
         </is>
       </c>
     </row>
@@ -946,22 +946,22 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>07-05-2026</t>
+          <t>06-05-2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605073558/CR</t>
+          <t>COMMERCIAL WAREHOUSE RENT / KORAMANGALA HUB</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n">
-        <v>7997.11</v>
-      </c>
+      <c r="E20" s="3" t="n">
+        <v>40575.4</v>
+      </c>
+      <c r="F20" s="3" t="n"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>83,114.71 Cr</t>
+          <t>-62,012.85 Cr</t>
         </is>
       </c>
     </row>
@@ -971,22 +971,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>07-05-2026</t>
+          <t>06-05-2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/701074556047/DR/73374590/PUNB/7337459005@pty</t>
+          <t>UPIAR/412938102938/DR/BIGBASKET/ICIC/bb@icici</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="3" t="n">
-        <v>142.36</v>
+        <v>682.6799999999999</v>
       </c>
       <c r="F21" s="3" t="n"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>82,972.35 Cr</t>
+          <t>-62,695.53 Cr</t>
         </is>
       </c>
     </row>
@@ -996,22 +996,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08-05-2026</t>
+          <t>07-05-2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605085437/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605075172/CR</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n">
-        <v>6951.52</v>
+        <v>4935.5</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>89,923.87 Cr</t>
+          <t>-57,760.03 Cr</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08-05-2026</t>
+          <t>07-05-2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COMMERCIAL WAREHOUSE RENT / KORAMANGALA HUB</t>
+          <t>UPIAR/455944913251/DR/KEMSARAP/SBIN/ 8977604821@yb</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="3" t="n">
-        <v>42532.44</v>
+        <v>293</v>
       </c>
       <c r="F23" s="3" t="n"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>47,391.43 Cr</t>
+          <t>-58,053.03 Cr</t>
         </is>
       </c>
     </row>
@@ -1046,22 +1046,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>08-05-2026</t>
+          <t>07-05-2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/172136536211/DR/ZOMATO L/YESB/zomato-order@p</t>
+          <t>COMMERCIAL WAREHOUSE RENT / KORAMANGALA HUB</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="3" t="n">
-        <v>373.12</v>
+        <v>46600.77</v>
       </c>
       <c r="F24" s="3" t="n"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>47,018.31 Cr</t>
+          <t>-104,653.80 Cr</t>
         </is>
       </c>
     </row>
@@ -1071,22 +1071,22 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>08-05-2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605091844/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605082353/CR</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n">
-        <v>11021.2</v>
+        <v>9357.01</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>58,039.51 Cr</t>
+          <t>-95,296.79 Cr</t>
         </is>
       </c>
     </row>
@@ -1096,22 +1096,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>08-05-2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>IMPS/OUTWARD/612984019283/RAW INGREDIENTS</t>
+          <t>UPIAB/982301928371/CR/LOCAL VENDOR/ICIC/vendor@icici</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="3" t="n">
-        <v>28977.56</v>
-      </c>
-      <c r="F26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n">
+        <v>3435.21</v>
+      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>29,061.95 Cr</t>
+          <t>-91,861.58 Cr</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>08-05-2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/982301928371/CR/LOCAL VENDOR/ICIC/vendor@icici</t>
+          <t>EMPLOYEE FIELD COMMUTE &amp; TRAVEL REIMBURSEMENT</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n">
-        <v>5483.17</v>
-      </c>
+      <c r="E27" s="3" t="n">
+        <v>3957.88</v>
+      </c>
+      <c r="F27" s="3" t="n"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>34,545.12 Cr</t>
+          <t>-95,819.46 Cr</t>
         </is>
       </c>
     </row>
@@ -1146,22 +1146,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>10-05-2026</t>
+          <t>08-05-2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605103737/CR</t>
+          <t>UPIAB/800823341214/CR/PITCHIKA/CNRB/ umanag9712@ax</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="n">
-        <v>9292.969999999999</v>
+        <v>2336.55</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>43,838.09 Cr</t>
+          <t>-93,482.91 Cr</t>
         </is>
       </c>
     </row>
@@ -1171,22 +1171,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>10-05-2026</t>
+          <t>08-05-2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/110099887766/DR/OLA CABS</t>
+          <t>UPIAR/554433221100/DR/FLIPKART ONLINE</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="3" t="n">
-        <v>639.6799999999999</v>
+        <v>1611.34</v>
       </c>
       <c r="F29" s="3" t="n"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>43,198.41 Cr</t>
+          <t>-95,094.25 Cr</t>
         </is>
       </c>
     </row>
@@ -1196,22 +1196,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>10-05-2026</t>
+          <t>08-05-2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/800823341214/CR/PITCHIKA/CNRB/ umanag9712@ax</t>
+          <t>EMPLOYEE FIELD COMMUTE &amp; TRAVEL REIMBURSEMENT</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n">
-        <v>3742.46</v>
-      </c>
+      <c r="E30" s="3" t="n">
+        <v>4117.78</v>
+      </c>
+      <c r="F30" s="3" t="n"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>46,940.87 Cr</t>
+          <t>-99,212.03 Cr</t>
         </is>
       </c>
     </row>
@@ -1221,22 +1221,22 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11-05-2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605111210/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605092491/CR</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n">
-        <v>6385.62</v>
+        <v>2416.85</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>53,326.49 Cr</t>
+          <t>-96,795.18 Cr</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>11-05-2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>IMPS/OUTWARD/612984019283/RAW INGREDIENTS</t>
+          <t>UPIAB/776655443322/CR/CASHBACK REWARD</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="3" t="n">
-        <v>20736.61</v>
-      </c>
-      <c r="F32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n">
+        <v>123.86</v>
+      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>32,589.88 Cr</t>
+          <t>-96,671.32 Cr</t>
         </is>
       </c>
     </row>
@@ -1271,22 +1271,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>11-05-2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/112938102938/CR/WHOLESALE MILK DEPOSIT</t>
+          <t>UPIAR/645455850592/DR/DDhanus/SBIN/ 7396913943@up</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n">
-        <v>8992.610000000001</v>
-      </c>
+      <c r="E33" s="3" t="n">
+        <v>110.36</v>
+      </c>
+      <c r="F33" s="3" t="n"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>41,582.49 Cr</t>
+          <t>-96,781.68 Cr</t>
         </is>
       </c>
     </row>
@@ -1296,22 +1296,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>11-05-2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>PRINTING BARCODE LABELS &amp; BILLING ROLLS</t>
+          <t>UPIAB/637338636405/CR/PITCHIKA/SBIN/ 8919861154@yb</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="3" t="n">
-        <v>3566.41</v>
-      </c>
-      <c r="F34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n">
+        <v>3606.27</v>
+      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>38,016.08 Cr</t>
+          <t>-93,175.41 Cr</t>
         </is>
       </c>
     </row>
@@ -1321,22 +1321,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>11-05-2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/624556864731/CR/PICHIKA/UBIN/pvasuviswanadh</t>
+          <t>UPIAR/455944913251/DR/KEMSARAP/SBIN/ 8977604821@yb</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n">
-        <v>2530.9</v>
-      </c>
+      <c r="E35" s="3" t="n">
+        <v>147.06</v>
+      </c>
+      <c r="F35" s="3" t="n"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>40,546.98 Cr</t>
+          <t>-93,322.47 Cr</t>
         </is>
       </c>
     </row>
@@ -1346,22 +1346,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>12-05-2026</t>
+          <t>10-05-2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605121465/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605102312/CR</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="n">
-        <v>8474.83</v>
+        <v>3828.16</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>49,021.81 Cr</t>
+          <t>-89,494.31 Cr</t>
         </is>
       </c>
     </row>
@@ -1371,22 +1371,22 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>12-05-2026</t>
+          <t>10-05-2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>BBMP MUNICIPAL TRADE LICENSE &amp; PROPERTY TAX</t>
+          <t>UPIAR/908931590719/DR/Mr Raju/YESB/ Q249677790@yb</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="3" t="n">
-        <v>7620.26</v>
+        <v>97.95</v>
       </c>
       <c r="F37" s="3" t="n"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>41,401.55 Cr</t>
+          <t>-89,592.26 Cr</t>
         </is>
       </c>
     </row>
@@ -1396,22 +1396,22 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>12-05-2026</t>
+          <t>10-05-2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/322671730620/CR/PITCHIKA/SBIN/ 8919861154@ax</t>
+          <t>OFFICE PANTRY &amp; FRESH REFRESHMENTS</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n">
-        <v>4868.35</v>
-      </c>
+      <c r="E38" s="3" t="n">
+        <v>2450.43</v>
+      </c>
+      <c r="F38" s="3" t="n"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>46,269.90 Cr</t>
+          <t>-92,042.69 Cr</t>
         </is>
       </c>
     </row>
@@ -1421,22 +1421,22 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>12-05-2026</t>
+          <t>11-05-2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/982301928371/CR/LOCAL VENDOR/ICIC/vendor@icici</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605111290/CR</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="n">
-        <v>6061.99</v>
+        <v>9607.370000000001</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>52,331.89 Cr</t>
+          <t>-82,435.32 Cr</t>
         </is>
       </c>
     </row>
@@ -1446,22 +1446,22 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>13-05-2026</t>
+          <t>11-05-2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605137615/CR</t>
+          <t>AIRTEL CORPORATE BROADBAND &amp; FIBER</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="3" t="n"/>
-      <c r="F40" s="3" t="n">
-        <v>10992.24</v>
-      </c>
+      <c r="E40" s="3" t="n">
+        <v>3071.74</v>
+      </c>
+      <c r="F40" s="3" t="n"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>63,324.13 Cr</t>
+          <t>-85,507.06 Cr</t>
         </is>
       </c>
     </row>
@@ -1471,22 +1471,22 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>13-05-2026</t>
+          <t>12-05-2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>POINT OF SALE (POS) HARDWARE RENTAL</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605125975/CR</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
-      <c r="E41" s="3" t="n">
-        <v>3006.57</v>
-      </c>
-      <c r="F41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n">
+        <v>6386.75</v>
+      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>60,317.56 Cr</t>
+          <t>-79,120.31 Cr</t>
         </is>
       </c>
     </row>
@@ -1496,22 +1496,22 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>13-05-2026</t>
+          <t>12-05-2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>IMPS/OUTWARD/612984019283/RAW INGREDIENTS</t>
+          <t>SWIGGY INSTAMART FLEET REIMBURSEMENT</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="3" t="n">
-        <v>29835.58</v>
+        <v>1456.79</v>
       </c>
       <c r="F42" s="3" t="n"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>30,481.98 Cr</t>
+          <t>-80,577.10 Cr</t>
         </is>
       </c>
     </row>
@@ -1521,22 +1521,22 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>14-05-2026</t>
+          <t>12-05-2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605147037/CR</t>
+          <t>EMPLOYEE FIELD COMMUTE &amp; TRAVEL REIMBURSEMENT</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="3" t="n"/>
-      <c r="F43" s="3" t="n">
-        <v>7220.09</v>
-      </c>
+      <c r="E43" s="3" t="n">
+        <v>3939.67</v>
+      </c>
+      <c r="F43" s="3" t="n"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>37,702.07 Cr</t>
+          <t>-84,516.77 Cr</t>
         </is>
       </c>
     </row>
@@ -1546,22 +1546,22 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>14-05-2026</t>
+          <t>13-05-2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/112938102938/CR/WHOLESALE MILK DEPOSIT</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605139045/CR</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n">
-        <v>7136.39</v>
+        <v>4646.51</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>44,838.46 Cr</t>
+          <t>-79,870.26 Cr</t>
         </is>
       </c>
     </row>
@@ -1571,22 +1571,22 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>14-05-2026</t>
+          <t>13-05-2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/908129381023/DR/BILLDESK/SBIN/billdesk@sbi</t>
+          <t>UPIAB/624556864731/CR/PICHIKA/UBIN/pvasuviswanadh</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
-      <c r="E45" s="3" t="n">
-        <v>982.76</v>
-      </c>
-      <c r="F45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="n">
+        <v>1567.21</v>
+      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>43,855.70 Cr</t>
+          <t>-78,303.05 Cr</t>
         </is>
       </c>
     </row>
@@ -1596,22 +1596,22 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15-05-2026</t>
+          <t>14-05-2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605156893/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605146115/CR</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="n">
-        <v>4029.1</v>
+        <v>2821.71</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>47,884.80 Cr</t>
+          <t>-75,481.34 Cr</t>
         </is>
       </c>
     </row>
@@ -1621,22 +1621,22 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15-05-2026</t>
+          <t>14-05-2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
+          <t>UPIAB/637338636405/CR/PITCHIKA/SBIN/ 8919861154@yb</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
-      <c r="E47" s="3" t="n">
-        <v>9131.35</v>
-      </c>
-      <c r="F47" s="3" t="n"/>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="n">
+        <v>2238.73</v>
+      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>38,753.45 Cr</t>
+          <t>-73,242.61 Cr</t>
         </is>
       </c>
     </row>
@@ -1646,22 +1646,22 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>16-05-2026</t>
+          <t>14-05-2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605169287/CR</t>
+          <t>NEFT/OUTWARD/HDFC/FARMERS COOP SUPPLY</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="3" t="n"/>
-      <c r="F48" s="3" t="n">
-        <v>8072.58</v>
-      </c>
+      <c r="E48" s="3" t="n">
+        <v>18951.27</v>
+      </c>
+      <c r="F48" s="3" t="n"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>46,826.03 Cr</t>
+          <t>-92,193.88 Cr</t>
         </is>
       </c>
     </row>
@@ -1671,22 +1671,22 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>17-05-2026</t>
+          <t>15-05-2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605175626/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605154901/CR</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="3" t="n"/>
       <c r="F49" s="3" t="n">
-        <v>5966.26</v>
+        <v>4744.68</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>52,792.29 Cr</t>
+          <t>-87,449.20 Cr</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17-05-2026</t>
+          <t>15-05-2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="3" t="n">
-        <v>4014.41</v>
+        <v>2749.33</v>
       </c>
       <c r="F50" s="3" t="n"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>48,777.88 Cr</t>
+          <t>-90,198.53 Cr</t>
         </is>
       </c>
     </row>
@@ -1721,22 +1721,22 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17-05-2026</t>
+          <t>15-05-2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/172136536211/DR/ZOMATO L/YESB/zomato-order@p</t>
+          <t>UPIAB/637338636405/CR/PITCHIKA/SBIN/ 8919861154@yb</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
-      <c r="E51" s="3" t="n">
-        <v>363.1</v>
-      </c>
-      <c r="F51" s="3" t="n"/>
+      <c r="E51" s="3" t="n"/>
+      <c r="F51" s="3" t="n">
+        <v>2832.86</v>
+      </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>48,414.78 Cr</t>
+          <t>-87,365.67 Cr</t>
         </is>
       </c>
     </row>
@@ -1746,22 +1746,22 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>17-05-2026</t>
+          <t>16-05-2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/020074062699/CR/THIRUVEE/UBIN/9391652831-2@a</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605165632/CR</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="3" t="n"/>
       <c r="F52" s="3" t="n">
-        <v>1074.2</v>
+        <v>6015.05</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>49,488.98 Cr</t>
+          <t>-81,350.62 Cr</t>
         </is>
       </c>
     </row>
@@ -1771,22 +1771,22 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>18-05-2026</t>
+          <t>16-05-2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605182352/CR</t>
+          <t>BESCOM POWER UTILITY / BANGALORE WAREHOUSE</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
-      <c r="E53" s="3" t="n"/>
-      <c r="F53" s="3" t="n">
-        <v>19323.76</v>
-      </c>
+      <c r="E53" s="3" t="n">
+        <v>12936.37</v>
+      </c>
+      <c r="F53" s="3" t="n"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>68,812.74 Cr</t>
+          <t>-94,286.99 Cr</t>
         </is>
       </c>
     </row>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>19-05-2026</t>
+          <t>17-05-2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605199306/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605177523/CR</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="3" t="n"/>
       <c r="F54" s="3" t="n">
-        <v>5326.49</v>
+        <v>5169.24</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>74,139.23 Cr</t>
+          <t>-89,117.75 Cr</t>
         </is>
       </c>
     </row>
@@ -1821,22 +1821,22 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>19-05-2026</t>
+          <t>17-05-2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>INVENTORY AUDITOR &amp; CA LEGAL RETAINER</t>
+          <t>UPIAB/512938102938/CR/SUPPLIER CREDIT NOTE</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
-      <c r="E55" s="3" t="n">
-        <v>13944.92</v>
-      </c>
-      <c r="F55" s="3" t="n"/>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="n">
+        <v>2534.22</v>
+      </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>60,194.31 Cr</t>
+          <t>-86,583.53 Cr</t>
         </is>
       </c>
     </row>
@@ -1846,22 +1846,22 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>19-05-2026</t>
+          <t>17-05-2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>AIRTEL CORPORATE BROADBAND &amp; FIBER</t>
+          <t>UPIAR/347067657684/DR/KAJALVI/YESB/paytm.s1w3jr9@</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="3" t="n">
-        <v>3800.84</v>
+        <v>181.44</v>
       </c>
       <c r="F56" s="3" t="n"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>56,393.47 Cr</t>
+          <t>-86,764.97 Cr</t>
         </is>
       </c>
     </row>
@@ -1871,22 +1871,22 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>19-05-2026</t>
+          <t>18-05-2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>IMPS/INWARD/SBIN/DISTRIBUTOR SETTLEMENT</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605189488/CR</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="3" t="n"/>
       <c r="F57" s="3" t="n">
-        <v>18257.54</v>
+        <v>4498.86</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>74,651.01 Cr</t>
+          <t>-82,266.11 Cr</t>
         </is>
       </c>
     </row>
@@ -1896,22 +1896,22 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20-05-2026</t>
+          <t>19-05-2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605204772/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605191295/CR</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="3" t="n"/>
       <c r="F58" s="3" t="n">
-        <v>6584.4</v>
+        <v>8178.15</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>81,235.41 Cr</t>
+          <t>-74,087.96 Cr</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20-05-2026</t>
+          <t>19-05-2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/887766554433/DR/BHARATPE MERCHANT</t>
+          <t>UPIAR/719421374678/DR/NEWKRSN/YESB/paytmqr6a0ixr@</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="3" t="n">
-        <v>127.65</v>
+        <v>295.34</v>
       </c>
       <c r="F59" s="3" t="n"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>81,107.76 Cr</t>
+          <t>-74,383.30 Cr</t>
         </is>
       </c>
     </row>
@@ -1946,22 +1946,22 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>20-05-2026</t>
+          <t>19-05-2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/123854061954/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+          <t>UPIAR/124934775512/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="3" t="n">
-        <v>349.38</v>
+        <v>204.47</v>
       </c>
       <c r="F60" s="3" t="n"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>80,758.38 Cr</t>
+          <t>-74,587.77 Cr</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>20-05-2026</t>
+          <t>19-05-2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -1982,11 +1982,11 @@
       <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="3" t="n"/>
       <c r="F61" s="3" t="n">
-        <v>5899.53</v>
+        <v>8403.860000000001</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>86,657.91 Cr</t>
+          <t>-66,183.91 Cr</t>
         </is>
       </c>
     </row>
@@ -1996,22 +1996,22 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>21-05-2026</t>
+          <t>20-05-2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605217887/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605206093/CR</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="3" t="n"/>
       <c r="F62" s="3" t="n">
-        <v>10256.72</v>
+        <v>6366.98</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>96,914.63 Cr</t>
+          <t>-59,816.93 Cr</t>
         </is>
       </c>
     </row>
@@ -2026,17 +2026,17 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>LIC PREMIUM AUTO DEBIT CLEARING</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605214649/CR</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
-      <c r="E63" s="3" t="n">
-        <v>11525.78</v>
-      </c>
-      <c r="F63" s="3" t="n"/>
+      <c r="E63" s="3" t="n"/>
+      <c r="F63" s="3" t="n">
+        <v>4127.73</v>
+      </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>85,388.85 Cr</t>
+          <t>-55,689.20 Cr</t>
         </is>
       </c>
     </row>
@@ -2051,17 +2051,17 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/301984712093/DR/SWIGGY/HDFC/swiggy@hdfc</t>
+          <t>UPIAR/221100998877/DR/UBER RIDE</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
       <c r="E64" s="3" t="n">
-        <v>449.59</v>
+        <v>683.02</v>
       </c>
       <c r="F64" s="3" t="n"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>84,939.26 Cr</t>
+          <t>-56,372.22 Cr</t>
         </is>
       </c>
     </row>
@@ -2076,17 +2076,17 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>PRINTING BARCODE LABELS &amp; BILLING ROLLS</t>
+          <t>UPIAR/301984712093/DR/SWIGGY/HDFC/swiggy@hdfc</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
       <c r="E65" s="3" t="n">
-        <v>2032.79</v>
+        <v>354.78</v>
       </c>
       <c r="F65" s="3" t="n"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>82,906.47 Cr</t>
+          <t>-56,727.00 Cr</t>
         </is>
       </c>
     </row>
@@ -2101,17 +2101,17 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/347067657684/DR/KAJALVI/YESB/paytm.s1w3jr9@</t>
+          <t>BESCOM POWER UTILITY / BANGALORE WAREHOUSE</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="3" t="n">
-        <v>84.93000000000001</v>
+        <v>10967.91</v>
       </c>
       <c r="F66" s="3" t="n"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>82,821.54 Cr</t>
+          <t>-67,694.91 Cr</t>
         </is>
       </c>
     </row>
@@ -2121,22 +2121,22 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>21-05-2026</t>
+          <t>22-05-2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>IMPS/INWARD/SBIN/DISTRIBUTOR SETTLEMENT</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605226247/CR</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="3" t="n"/>
       <c r="F67" s="3" t="n">
-        <v>26086.66</v>
+        <v>3930.89</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>108,908.20 Cr</t>
+          <t>-63,764.02 Cr</t>
         </is>
       </c>
     </row>
@@ -2146,22 +2146,22 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>21-05-2026</t>
+          <t>22-05-2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>FIRE SAFETY INSPECTION &amp; EQUIPMENT REFILL</t>
+          <t>UPIAR/998877665544/DR/PAYTM QR VENDOR</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="3" t="n">
-        <v>4512.03</v>
+        <v>117.66</v>
       </c>
       <c r="F68" s="3" t="n"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>104,396.17 Cr</t>
+          <t>-63,881.68 Cr</t>
         </is>
       </c>
     </row>
@@ -2171,20 +2171,22 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>22-05-2026</t>
+          <t>23-05-2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605226209/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605232837/CR</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
       <c r="E69" s="3" t="n"/>
-      <c r="F69" s="3" t="n"/>
+      <c r="F69" s="3" t="n">
+        <v>3861.09</v>
+      </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>92,100.83 Cr</t>
+          <t>-60,020.59 Cr</t>
         </is>
       </c>
     </row>
@@ -2194,22 +2196,22 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22-05-2026</t>
+          <t>23-05-2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/009988776655/CR/DIVIDEND PAYOUT</t>
+          <t>UPIAR/998877665544/DR/PAYTM QR VENDOR</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="3" t="n"/>
-      <c r="F70" s="3" t="n">
-        <v>1183.78</v>
-      </c>
+      <c r="E70" s="3" t="n">
+        <v>170.76</v>
+      </c>
+      <c r="F70" s="3" t="n"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>93,284.61 Cr</t>
+          <t>-60,191.35 Cr</t>
         </is>
       </c>
     </row>
@@ -2219,22 +2221,22 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22-05-2026</t>
+          <t>24-05-2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/512938102938/CR/SUPPLIER CREDIT NOTE</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605241075/CR</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" s="3" t="n"/>
       <c r="F71" s="3" t="n">
-        <v>7451.93</v>
+        <v>7034.63</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>100,736.54 Cr</t>
+          <t>-53,156.72 Cr</t>
         </is>
       </c>
     </row>
@@ -2244,22 +2246,22 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>22-05-2026</t>
+          <t>24-05-2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/123854061954/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+          <t>UPIAR/140288398543/DR/73374590/PUNB/7337459005@pty</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="3" t="n">
-        <v>261.63</v>
+        <v>169.45</v>
       </c>
       <c r="F72" s="3" t="n"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>100,474.91 Cr</t>
+          <t>-53,326.17 Cr</t>
         </is>
       </c>
     </row>
@@ -2269,22 +2271,22 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>23-05-2026</t>
+          <t>25-05-2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605235998/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605251628/CR</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="3" t="n"/>
       <c r="F73" s="3" t="n">
-        <v>6737.43</v>
+        <v>2700.43</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>107,212.34 Cr</t>
+          <t>-50,625.74 Cr</t>
         </is>
       </c>
     </row>
@@ -2294,22 +2296,22 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>23-05-2026</t>
+          <t>25-05-2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>AWS CLOUD SERVER HOSTING &amp; INFRASTRUCTURE</t>
+          <t>UPIAR/110099887766/DR/OLA CABS</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="3" t="n">
-        <v>6965.54</v>
+        <v>584.5599999999999</v>
       </c>
       <c r="F74" s="3" t="n"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>100,246.80 Cr</t>
+          <t>-51,210.30 Cr</t>
         </is>
       </c>
     </row>
@@ -2319,22 +2321,22 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>23-05-2026</t>
+          <t>26-05-2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/717134959917/DR/AoapAmr/AIRP/AoapAmrita.pay</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605263985/CR</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
-      <c r="E75" s="3" t="n">
-        <v>3916.23</v>
-      </c>
-      <c r="F75" s="3" t="n"/>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="n">
+        <v>4322.51</v>
+      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>96,330.57 Cr</t>
+          <t>-46,887.79 Cr</t>
         </is>
       </c>
     </row>
@@ -2344,22 +2346,22 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>24-05-2026</t>
+          <t>26-05-2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605249699/CR</t>
+          <t>UPIAR/645455850592/DR/DDhanus/SBIN/ 7396913943@up</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
-      <c r="E76" s="3" t="n"/>
-      <c r="F76" s="3" t="n">
-        <v>13825.8</v>
-      </c>
+      <c r="E76" s="3" t="n">
+        <v>256.6</v>
+      </c>
+      <c r="F76" s="3" t="n"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>110,156.37 Cr</t>
+          <t>-47,144.39 Cr</t>
         </is>
       </c>
     </row>
@@ -2369,22 +2371,22 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>24-05-2026</t>
+          <t>27-05-2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/026544681447/DR/SHANTIP/YESB/ Q707874078@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605272263/CR</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
-      <c r="E77" s="3" t="n">
-        <v>434.24</v>
-      </c>
-      <c r="F77" s="3" t="n"/>
+      <c r="E77" s="3" t="n"/>
+      <c r="F77" s="3" t="n">
+        <v>5077.32</v>
+      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>109,722.13 Cr</t>
+          <t>-42,067.07 Cr</t>
         </is>
       </c>
     </row>
@@ -2394,22 +2396,22 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>24-05-2026</t>
+          <t>28-05-2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/624556864731/CR/PICHIKA/UBIN/pvasuviswanadh</t>
+          <t>UPIAB/776655443322/CR/CASHBACK REWARD</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="3" t="n"/>
       <c r="F78" s="3" t="n">
-        <v>1029.33</v>
+        <v>21.93</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>110,751.46 Cr</t>
+          <t>-42,045.14 Cr</t>
         </is>
       </c>
     </row>
@@ -2419,22 +2421,22 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>25-05-2026</t>
+          <t>29-05-2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605255186/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605295449/CR</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
       <c r="E79" s="3" t="n"/>
       <c r="F79" s="3" t="n">
-        <v>4101.67</v>
+        <v>1465.23</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>114,853.13 Cr</t>
+          <t>-40,579.91 Cr</t>
         </is>
       </c>
     </row>
@@ -2444,22 +2446,22 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>25-05-2026</t>
+          <t>29-05-2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
+          <t>UPIAR/665544332211/DR/AMAZON INDIA</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="3" t="n">
-        <v>7400.34</v>
+        <v>2021.65</v>
       </c>
       <c r="F80" s="3" t="n"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>107,452.79 Cr</t>
+          <t>-42,601.56 Cr</t>
         </is>
       </c>
     </row>
@@ -2469,22 +2471,22 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>25-05-2026</t>
+          <t>29-05-2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/776655443322/CR/CASHBACK REWARD</t>
+          <t>LIC PREMIUM AUTO DEBIT CLEARING</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
-      <c r="E81" s="3" t="n"/>
-      <c r="F81" s="3" t="n">
-        <v>90.90000000000001</v>
-      </c>
+      <c r="E81" s="3" t="n">
+        <v>7663.51</v>
+      </c>
+      <c r="F81" s="3" t="n"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>107,543.69 Cr</t>
+          <t>-50,265.07 Cr</t>
         </is>
       </c>
     </row>
@@ -2494,22 +2496,22 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>26-05-2026</t>
+          <t>30-05-2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605269206/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605305620/CR</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="3" t="n"/>
       <c r="F82" s="3" t="n">
-        <v>8705.469999999999</v>
+        <v>7865.48</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>116,249.16 Cr</t>
+          <t>-42,399.59 Cr</t>
         </is>
       </c>
     </row>
@@ -2519,22 +2521,22 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>26-05-2026</t>
+          <t>30-05-2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/271988123471/CR/THIRUVEE/UBIN/9391652831-2@a</t>
+          <t>FIRE SAFETY INSPECTION &amp; EQUIPMENT REFILL</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
-      <c r="E83" s="3" t="n"/>
-      <c r="F83" s="3" t="n">
-        <v>306.93</v>
-      </c>
+      <c r="E83" s="3" t="n">
+        <v>3953.87</v>
+      </c>
+      <c r="F83" s="3" t="n"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>116,556.09 Cr</t>
+          <t>-46,353.46 Cr</t>
         </is>
       </c>
     </row>
@@ -2544,22 +2546,22 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>27-05-2026</t>
+          <t>31-05-2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605272228/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605318122/CR</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="3" t="n"/>
       <c r="F84" s="3" t="n">
-        <v>7104.13</v>
+        <v>2743.79</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>123,660.22 Cr</t>
+          <t>-43,609.67 Cr</t>
         </is>
       </c>
     </row>
@@ -2569,22 +2571,22 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>27-05-2026</t>
+          <t>31-05-2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/512938102938/CR/SUPPLIER CREDIT NOTE</t>
+          <t>WATER TANKER &amp; SANITATION CHARGES</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
-      <c r="E85" s="3" t="n"/>
-      <c r="F85" s="3" t="n">
-        <v>6521.31</v>
-      </c>
+      <c r="E85" s="3" t="n">
+        <v>2173.36</v>
+      </c>
+      <c r="F85" s="3" t="n"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>130,181.53 Cr</t>
+          <t>-45,783.03 Cr</t>
         </is>
       </c>
     </row>
@@ -2594,22 +2596,22 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>27-05-2026</t>
+          <t>01-06-2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>SECURITY GUARD SERVICES &amp; CCTV MONITORING</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606012908/CR</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
-      <c r="E86" s="3" t="n">
-        <v>5510.81</v>
-      </c>
-      <c r="F86" s="3" t="n"/>
+      <c r="E86" s="3" t="n"/>
+      <c r="F86" s="3" t="n">
+        <v>5631.71</v>
+      </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>124,670.72 Cr</t>
+          <t>-40,151.32 Cr</t>
         </is>
       </c>
     </row>
@@ -2619,22 +2621,22 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>27-05-2026</t>
+          <t>01-06-2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/998877665544/DR/PAYTM QR VENDOR</t>
+          <t>BESCOM POWER UTILITY / BANGALORE WAREHOUSE</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="3" t="n">
-        <v>99.29000000000001</v>
+        <v>16172.63</v>
       </c>
       <c r="F87" s="3" t="n"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>124,571.43 Cr</t>
+          <t>-56,323.95 Cr</t>
         </is>
       </c>
     </row>
@@ -2644,22 +2646,22 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>28-05-2026</t>
+          <t>02-06-2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605283489/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606027181/CR</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="3" t="n"/>
       <c r="F88" s="3" t="n">
-        <v>5608.5</v>
+        <v>6305.1</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>130,179.93 Cr</t>
+          <t>-50,018.85 Cr</t>
         </is>
       </c>
     </row>
@@ -2669,22 +2671,22 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>28-05-2026</t>
+          <t>02-06-2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>LIC PREMIUM AUTO DEBIT CLEARING</t>
+          <t>UPIAB/443322110099/CR/PROMO DISCOUNT CREDIT</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
-      <c r="E89" s="3" t="n">
-        <v>5555.55</v>
-      </c>
-      <c r="F89" s="3" t="n"/>
+      <c r="E89" s="3" t="n"/>
+      <c r="F89" s="3" t="n">
+        <v>123.63</v>
+      </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>124,624.38 Cr</t>
+          <t>-49,895.22 Cr</t>
         </is>
       </c>
     </row>
@@ -2694,22 +2696,22 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>28-05-2026</t>
+          <t>02-06-2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>NEFT/INWARD/CITI/GROCERY WHOLESALE REBATE</t>
+          <t>UPIAB/637338636405/CR/PITCHIKA/SBIN/ 8919861154@yb</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="3" t="n"/>
       <c r="F90" s="3" t="n">
-        <v>11668.55</v>
+        <v>1958.06</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>136,292.93 Cr</t>
+          <t>-47,937.16 Cr</t>
         </is>
       </c>
     </row>
@@ -2719,22 +2721,22 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>29-05-2026</t>
+          <t>02-06-2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605293912/CR</t>
+          <t>SERVICE CHARGE / MINIMUM BALANCE FEE</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
-      <c r="E91" s="3" t="n"/>
-      <c r="F91" s="3" t="n">
-        <v>7973.41</v>
-      </c>
+      <c r="E91" s="3" t="n">
+        <v>181.53</v>
+      </c>
+      <c r="F91" s="3" t="n"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>144,266.34 Cr</t>
+          <t>-48,118.69 Cr</t>
         </is>
       </c>
     </row>
@@ -2744,22 +2746,22 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>29-05-2026</t>
+          <t>02-06-2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/143302589531/DR/Zomato87/AIRP/Zomato8759546.</t>
+          <t>DELIVERY ELECTRIC VAN MAINTENANCE &amp; AMC</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
       <c r="E92" s="3" t="n">
-        <v>223.7</v>
+        <v>3837.15</v>
       </c>
       <c r="F92" s="3" t="n"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>144,042.64 Cr</t>
+          <t>-51,955.84 Cr</t>
         </is>
       </c>
     </row>
@@ -2769,22 +2771,22 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>29-05-2026</t>
+          <t>03-06-2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/812938102938/DR/PETROL PUMP/HPCL/hpcl@icici</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606033544/CR</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
-      <c r="E93" s="3" t="n">
-        <v>1238.57</v>
-      </c>
-      <c r="F93" s="3" t="n"/>
+      <c r="E93" s="3" t="n"/>
+      <c r="F93" s="3" t="n">
+        <v>7288.22</v>
+      </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>142,804.07 Cr</t>
+          <t>-44,667.62 Cr</t>
         </is>
       </c>
     </row>
@@ -2794,22 +2796,22 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>29-05-2026</t>
+          <t>03-06-2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>BBMP MUNICIPAL TRADE LICENSE &amp; PROPERTY TAX</t>
+          <t>UPIAB/443322110099/CR/PROMO DISCOUNT CREDIT</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
-      <c r="E94" s="3" t="n">
-        <v>7476.97</v>
-      </c>
-      <c r="F94" s="3" t="n"/>
+      <c r="E94" s="3" t="n"/>
+      <c r="F94" s="3" t="n">
+        <v>195.95</v>
+      </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>135,327.10 Cr</t>
+          <t>-44,471.67 Cr</t>
         </is>
       </c>
     </row>
@@ -2819,22 +2821,22 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>30-05-2026</t>
+          <t>04-06-2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605306330/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606045096/CR</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="3" t="n"/>
       <c r="F95" s="3" t="n">
-        <v>6675.73</v>
+        <v>7571.24</v>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>142,002.83 Cr</t>
+          <t>-36,900.43 Cr</t>
         </is>
       </c>
     </row>
@@ -2844,22 +2846,22 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>30-05-2026</t>
+          <t>04-06-2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/347067657684/DR/KAJALVI/YESB/paytm.s1w3jr9@</t>
+          <t>WATER TANKER &amp; SANITATION CHARGES</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="3" t="n">
-        <v>21.77</v>
+        <v>2428.33</v>
       </c>
       <c r="F96" s="3" t="n"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>141,981.06 Cr</t>
+          <t>-39,328.76 Cr</t>
         </is>
       </c>
     </row>
@@ -2869,22 +2871,22 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>30-05-2026</t>
+          <t>04-06-2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>NEFT/OUTWARD/HDFC/FARMERS COOP SUPPLY</t>
+          <t>UPIAB/022447403071/CR/THIRUVEE/UBIN/9391652831-2@a</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
-      <c r="E97" s="3" t="n">
-        <v>24044.71</v>
-      </c>
-      <c r="F97" s="3" t="n"/>
+      <c r="E97" s="3" t="n"/>
+      <c r="F97" s="3" t="n">
+        <v>752.12</v>
+      </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>117,936.35 Cr</t>
+          <t>-38,576.64 Cr</t>
         </is>
       </c>
     </row>
@@ -2894,22 +2896,22 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>30-05-2026</t>
+          <t>05-06-2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/800823341214/CR/PITCHIKA/CNRB/ umanag9712@ax</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606053262/CR</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
       <c r="E98" s="3" t="n"/>
       <c r="F98" s="3" t="n">
-        <v>2328.93</v>
+        <v>4379.83</v>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>120,265.28 Cr</t>
+          <t>-34,196.81 Cr</t>
         </is>
       </c>
     </row>
@@ -2919,22 +2921,22 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>31-05-2026</t>
+          <t>05-06-2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605312613/CR</t>
+          <t>UPIAR/554433221100/DR/FLIPKART ONLINE</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr"/>
-      <c r="E99" s="3" t="n"/>
-      <c r="F99" s="3" t="n">
-        <v>9803.440000000001</v>
-      </c>
+      <c r="E99" s="3" t="n">
+        <v>3535.6</v>
+      </c>
+      <c r="F99" s="3" t="n"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>130,068.72 Cr</t>
+          <t>-37,732.41 Cr</t>
         </is>
       </c>
     </row>
@@ -2944,22 +2946,22 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>31-05-2026</t>
+          <t>05-06-2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>CHQ PAID / CLEARING NO 004812</t>
+          <t>UPIAR/645455850592/DR/DDhanus/SBIN/ 7396913943@up</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="3" t="n">
-        <v>13781.91</v>
+        <v>270.65</v>
       </c>
       <c r="F100" s="3" t="n"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>116,286.81 Cr</t>
+          <t>-38,003.06 Cr</t>
         </is>
       </c>
     </row>
@@ -2969,22 +2971,22 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01-06-2026</t>
+          <t>06-06-2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606018346/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606067588/CR</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr"/>
       <c r="E101" s="3" t="n"/>
       <c r="F101" s="3" t="n">
-        <v>7992.78</v>
+        <v>5315.95</v>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>124,279.59 Cr</t>
+          <t>-32,687.11 Cr</t>
         </is>
       </c>
     </row>
@@ -2994,22 +2996,22 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>01-06-2026</t>
+          <t>06-06-2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/554433221100/DR/FLIPKART ONLINE</t>
+          <t>UPIAR/665544332211/DR/AMAZON INDIA</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="3" t="n">
-        <v>2906.55</v>
+        <v>1266.84</v>
       </c>
       <c r="F102" s="3" t="n"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>121,373.04 Cr</t>
+          <t>-33,953.95 Cr</t>
         </is>
       </c>
     </row>
@@ -3019,22 +3021,22 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>02-06-2026</t>
+          <t>07-06-2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606024469/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606073974/CR</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr"/>
       <c r="E103" s="3" t="n"/>
       <c r="F103" s="3" t="n">
-        <v>8293.75</v>
+        <v>4031.17</v>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>129,666.79 Cr</t>
+          <t>-29,922.78 Cr</t>
         </is>
       </c>
     </row>
@@ -3044,22 +3046,22 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>02-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/776655443322/CR/CASHBACK REWARD</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606088690/CR</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr"/>
       <c r="E104" s="3" t="n"/>
       <c r="F104" s="3" t="n">
-        <v>84.95</v>
+        <v>6109.48</v>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>129,751.74 Cr</t>
+          <t>-23,813.30 Cr</t>
         </is>
       </c>
     </row>
@@ -3069,22 +3071,22 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>02-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>POINT OF SALE (POS) HARDWARE RENTAL</t>
+          <t>UPIAR/172136536211/DR/ZOMATO L/YESB/zomato-order@p</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr"/>
       <c r="E105" s="3" t="n">
-        <v>3957.45</v>
+        <v>507.82</v>
       </c>
       <c r="F105" s="3" t="n"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>125,794.29 Cr</t>
+          <t>-24,321.12 Cr</t>
         </is>
       </c>
     </row>
@@ -3094,22 +3096,22 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>02-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>AIRTEL CORPORATE BROADBAND &amp; FIBER</t>
+          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr"/>
-      <c r="E106" s="3" t="n">
-        <v>1578.57</v>
-      </c>
-      <c r="F106" s="3" t="n"/>
+      <c r="E106" s="3" t="n"/>
+      <c r="F106" s="3" t="n">
+        <v>1440.37</v>
+      </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>124,215.72 Cr</t>
+          <t>-22,880.75 Cr</t>
         </is>
       </c>
     </row>
@@ -3119,22 +3121,22 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>03-06-2026</t>
+          <t>09-06-2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606034693/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606092277/CR</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
       <c r="E107" s="3" t="n"/>
       <c r="F107" s="3" t="n">
-        <v>10108.84</v>
+        <v>1996.2</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>134,324.56 Cr</t>
+          <t>-20,884.55 Cr</t>
         </is>
       </c>
     </row>
@@ -3144,22 +3146,22 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>04-06-2026</t>
+          <t>09-06-2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606045227/CR</t>
+          <t>UPIAR/347067657684/DR/KAJALVI/YESB/paytm.s1w3jr9@</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr"/>
-      <c r="E108" s="3" t="n"/>
-      <c r="F108" s="3" t="n">
-        <v>4330.17</v>
-      </c>
+      <c r="E108" s="3" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="F108" s="3" t="n"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>138,654.73 Cr</t>
+          <t>-20,949.30 Cr</t>
         </is>
       </c>
     </row>
@@ -3169,22 +3171,22 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>04-06-2026</t>
+          <t>09-06-2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
+          <t>GST ADVANCE TAX DEPOSIT / GOVT OF INDIA</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr"/>
-      <c r="E109" s="3" t="n"/>
-      <c r="F109" s="3" t="n">
-        <v>1770.13</v>
-      </c>
+      <c r="E109" s="3" t="n">
+        <v>21504.87</v>
+      </c>
+      <c r="F109" s="3" t="n"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>140,424.86 Cr</t>
+          <t>-42,454.17 Cr</t>
         </is>
       </c>
     </row>
@@ -3194,22 +3196,22 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>04-06-2026</t>
+          <t>10-06-2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/143302589531/DR/Zomato87/AIRP/Zomato8759546.</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606103051/CR</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr"/>
-      <c r="E110" s="3" t="n">
-        <v>361.34</v>
-      </c>
-      <c r="F110" s="3" t="n"/>
+      <c r="E110" s="3" t="n"/>
+      <c r="F110" s="3" t="n">
+        <v>3352.57</v>
+      </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>140,063.52 Cr</t>
+          <t>-39,101.60 Cr</t>
         </is>
       </c>
     </row>
@@ -3219,22 +3221,22 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>05-06-2026</t>
+          <t>10-06-2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606051406/CR</t>
+          <t>AIRTEL CORPORATE BROADBAND &amp; FIBER</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr"/>
-      <c r="E111" s="3" t="n"/>
-      <c r="F111" s="3" t="n">
-        <v>18379.48</v>
-      </c>
+      <c r="E111" s="3" t="n">
+        <v>2105.8</v>
+      </c>
+      <c r="F111" s="3" t="n"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>158,443.00 Cr</t>
+          <t>-41,207.40 Cr</t>
         </is>
       </c>
     </row>
@@ -3244,22 +3246,22 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>05-06-2026</t>
+          <t>10-06-2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/789123891023/CR/CUSTOMER REFUND REVERSAL</t>
+          <t>UPIAR/455944913251/DR/KEMSARAP/SBIN/ 8977604821@yb</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr"/>
-      <c r="E112" s="3" t="n"/>
-      <c r="F112" s="3" t="n">
-        <v>687.28</v>
-      </c>
+      <c r="E112" s="3" t="n">
+        <v>229.43</v>
+      </c>
+      <c r="F112" s="3" t="n"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>159,130.28 Cr</t>
+          <t>-41,436.83 Cr</t>
         </is>
       </c>
     </row>
@@ -3269,22 +3271,22 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>05-06-2026</t>
+          <t>10-06-2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/624556864731/CR/PICHIKA/UBIN/pvasuviswanadh</t>
+          <t>UPIAB/789123891023/CR/CUSTOMER REFUND REVERSAL</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr"/>
       <c r="E113" s="3" t="n"/>
       <c r="F113" s="3" t="n">
-        <v>1706.11</v>
+        <v>419.56</v>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>160,836.39 Cr</t>
+          <t>-41,017.27 Cr</t>
         </is>
       </c>
     </row>
@@ -3294,22 +3296,22 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>05-06-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>BBMP MUNICIPAL TRADE LICENSE &amp; PROPERTY TAX</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606117331/CR</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr"/>
-      <c r="E114" s="3" t="n">
-        <v>5653.52</v>
-      </c>
-      <c r="F114" s="3" t="n"/>
+      <c r="E114" s="3" t="n"/>
+      <c r="F114" s="3" t="n">
+        <v>8814</v>
+      </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>155,182.87 Cr</t>
+          <t>-32,203.27 Cr</t>
         </is>
       </c>
     </row>
@@ -3319,22 +3321,22 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>06-06-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606066449/CR</t>
+          <t>UPIAB/539631629714/CR/TAIESWA/PPIW/6302476334.wal</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr"/>
       <c r="E115" s="3" t="n"/>
       <c r="F115" s="3" t="n">
-        <v>3259.97</v>
+        <v>431.17</v>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>158,442.84 Cr</t>
+          <t>-31,772.10 Cr</t>
         </is>
       </c>
     </row>
@@ -3344,22 +3346,22 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>06-06-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/665544332211/DR/AMAZON INDIA</t>
+          <t>UPIAR/908931590719/DR/Mr Raju/YESB/ Q249677790@yb</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr"/>
       <c r="E116" s="3" t="n">
-        <v>751.45</v>
+        <v>107.09</v>
       </c>
       <c r="F116" s="3" t="n"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>157,691.39 Cr</t>
+          <t>-31,879.19 Cr</t>
         </is>
       </c>
     </row>
@@ -3369,22 +3371,22 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>06-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606126882/CR</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr"/>
       <c r="E117" s="3" t="n"/>
       <c r="F117" s="3" t="n">
-        <v>1851.57</v>
+        <v>6513.41</v>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>159,542.96 Cr</t>
+          <t>-25,365.78 Cr</t>
         </is>
       </c>
     </row>
@@ -3394,22 +3396,22 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>07-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606076055/CR</t>
+          <t>AWS CLOUD SERVER HOSTING &amp; INFRASTRUCTURE</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr"/>
-      <c r="E118" s="3" t="n"/>
-      <c r="F118" s="3" t="n">
-        <v>11921.83</v>
-      </c>
+      <c r="E118" s="3" t="n">
+        <v>5200.17</v>
+      </c>
+      <c r="F118" s="3" t="n"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>171,464.79 Cr</t>
+          <t>-30,565.95 Cr</t>
         </is>
       </c>
     </row>
@@ -3419,22 +3421,22 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>07-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/512938102938/CR/SUPPLIER CREDIT NOTE</t>
+          <t>PACKAGING SUPPLIES / ECO CORRUGATED BOXES</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr"/>
-      <c r="E119" s="3" t="n"/>
-      <c r="F119" s="3" t="n">
-        <v>9941.51</v>
-      </c>
+      <c r="E119" s="3" t="n">
+        <v>14452.77</v>
+      </c>
+      <c r="F119" s="3" t="n"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>181,406.30 Cr</t>
+          <t>-45,018.72 Cr</t>
         </is>
       </c>
     </row>
@@ -3444,22 +3446,22 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>07-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/278079065373/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+          <t>UPIAR/204208208508/DR/Zomato87/AIRP/Zomato8759546.</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr"/>
       <c r="E120" s="3" t="n">
-        <v>338.96</v>
+        <v>235.26</v>
       </c>
       <c r="F120" s="3" t="n"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>181,067.34 Cr</t>
+          <t>-45,253.98 Cr</t>
         </is>
       </c>
     </row>
@@ -3469,22 +3471,22 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>07-06-2026</t>
+          <t>13-06-2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/020074062699/CR/THIRUVEE/UBIN/9391652831-2@a</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606137807/CR</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr"/>
       <c r="E121" s="3" t="n"/>
       <c r="F121" s="3" t="n">
-        <v>243.72</v>
+        <v>6801.31</v>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>181,311.06 Cr</t>
+          <t>-38,452.67 Cr</t>
         </is>
       </c>
     </row>
@@ -3494,22 +3496,22 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>13-06-2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606084936/CR</t>
+          <t>UPIAR/077728365159/DR/NAMBURI /YESB/ Q501702001@yb</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr"/>
-      <c r="E122" s="3" t="n"/>
-      <c r="F122" s="3" t="n">
-        <v>4662.51</v>
-      </c>
+      <c r="E122" s="3" t="n">
+        <v>75.64</v>
+      </c>
+      <c r="F122" s="3" t="n"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>185,973.57 Cr</t>
+          <t>-38,528.31 Cr</t>
         </is>
       </c>
     </row>
@@ -3519,22 +3521,22 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>09-06-2026</t>
+          <t>13-06-2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606097885/CR</t>
+          <t>UPIAB/020074062699/CR/THIRUVEE/UBIN/9391652831-2@a</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr"/>
       <c r="E123" s="3" t="n"/>
       <c r="F123" s="3" t="n">
-        <v>4421.52</v>
+        <v>1229.9</v>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>190,395.09 Cr</t>
+          <t>-37,298.41 Cr</t>
         </is>
       </c>
     </row>
@@ -3544,22 +3546,22 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>09-06-2026</t>
+          <t>13-06-2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>COMMERCIAL WAREHOUSE RENT / KORAMANGALA HUB</t>
+          <t>UPIAB/982301928371/CR/LOCAL VENDOR/ICIC/vendor@icici</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr"/>
-      <c r="E124" s="3" t="n">
-        <v>39913.06</v>
-      </c>
-      <c r="F124" s="3" t="n"/>
+      <c r="E124" s="3" t="n"/>
+      <c r="F124" s="3" t="n">
+        <v>6316.3</v>
+      </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>150,482.03 Cr</t>
+          <t>-30,982.11 Cr</t>
         </is>
       </c>
     </row>
@@ -3569,22 +3571,22 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>10-06-2026</t>
+          <t>14-06-2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606106884/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606146460/CR</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr"/>
       <c r="E125" s="3" t="n"/>
       <c r="F125" s="3" t="n">
-        <v>10876.82</v>
+        <v>7437.04</v>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>161,358.85 Cr</t>
+          <t>-23,545.07 Cr</t>
         </is>
       </c>
     </row>
@@ -3594,22 +3596,22 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>10-06-2026</t>
+          <t>14-06-2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/512938102938/CR/SUPPLIER CREDIT NOTE</t>
+          <t>UPIAR/312938102938/DR/ZEPTO/YESB/zepto@yb</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr"/>
-      <c r="E126" s="3" t="n"/>
-      <c r="F126" s="3" t="n">
-        <v>8552.42</v>
-      </c>
+      <c r="E126" s="3" t="n">
+        <v>561.24</v>
+      </c>
+      <c r="F126" s="3" t="n"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>169,911.27 Cr</t>
+          <t>-24,106.31 Cr</t>
         </is>
       </c>
     </row>
@@ -3619,22 +3621,22 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>10-06-2026</t>
+          <t>14-06-2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/332211009988/DR/BOOKMYSHOW TICKET</t>
+          <t>UPIAR/312938102938/DR/ZEPTO/YESB/zepto@yb</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr"/>
       <c r="E127" s="3" t="n">
-        <v>908.03</v>
+        <v>400.23</v>
       </c>
       <c r="F127" s="3" t="n"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>169,003.24 Cr</t>
+          <t>-24,506.54 Cr</t>
         </is>
       </c>
     </row>
@@ -3644,22 +3646,22 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>14-06-2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606117995/CR</t>
+          <t>UPIAR/026544681447/DR/SHANTIP/YESB/ Q707874078@yb</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr"/>
-      <c r="E128" s="3" t="n"/>
-      <c r="F128" s="3" t="n">
-        <v>8671.76</v>
-      </c>
+      <c r="E128" s="3" t="n">
+        <v>386.44</v>
+      </c>
+      <c r="F128" s="3" t="n"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>177,675.00 Cr</t>
+          <t>-24,892.98 Cr</t>
         </is>
       </c>
     </row>
@@ -3669,22 +3671,22 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>15-06-2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>NEFT/OUTWARD/UTI MUTUAL FUND SIP</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606155668/CR</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr"/>
-      <c r="E129" s="3" t="n">
-        <v>3291.97</v>
-      </c>
-      <c r="F129" s="3" t="n"/>
+      <c r="E129" s="3" t="n"/>
+      <c r="F129" s="3" t="n">
+        <v>2757</v>
+      </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>174,383.03 Cr</t>
+          <t>-22,135.98 Cr</t>
         </is>
       </c>
     </row>
@@ -3694,22 +3696,22 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/443322110099/CR/PROMO DISCOUNT CREDIT</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606165005/CR</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr"/>
       <c r="E130" s="3" t="n"/>
       <c r="F130" s="3" t="n">
-        <v>173.48</v>
+        <v>3857.39</v>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>174,556.51 Cr</t>
+          <t>-18,278.59 Cr</t>
         </is>
       </c>
     </row>
@@ -3719,22 +3721,22 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606125659/CR</t>
+          <t>PACKAGING SUPPLIES / ECO CORRUGATED BOXES</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr"/>
-      <c r="E131" s="3" t="n"/>
-      <c r="F131" s="3" t="n">
-        <v>14422.54</v>
-      </c>
+      <c r="E131" s="3" t="n">
+        <v>10686.26</v>
+      </c>
+      <c r="F131" s="3" t="n"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>188,979.05 Cr</t>
+          <t>-28,964.85 Cr</t>
         </is>
       </c>
     </row>
@@ -3744,22 +3746,22 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>13-06-2026</t>
+          <t>17-06-2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606137956/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606178072/CR</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr"/>
       <c r="E132" s="3" t="n"/>
       <c r="F132" s="3" t="n">
-        <v>5866.92</v>
+        <v>6720.32</v>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>194,845.97 Cr</t>
+          <t>-22,244.53 Cr</t>
         </is>
       </c>
     </row>
@@ -3769,22 +3771,22 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>13-06-2026</t>
+          <t>17-06-2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/124934775512/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+          <t>UPIAB/271988123471/CR/THIRUVEE/UBIN/9391652831-2@a</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr"/>
-      <c r="E133" s="3" t="n">
-        <v>133.17</v>
-      </c>
-      <c r="F133" s="3" t="n"/>
+      <c r="E133" s="3" t="n"/>
+      <c r="F133" s="3" t="n">
+        <v>509.26</v>
+      </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>194,712.80 Cr</t>
+          <t>-21,735.27 Cr</t>
         </is>
       </c>
     </row>
@@ -3794,22 +3796,22 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>14-06-2026</t>
+          <t>17-06-2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606143292/CR</t>
+          <t>UPIAB/712626244599/CR/PICHIKA/BARB/ 8985068499@ax</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr"/>
       <c r="E134" s="3" t="n"/>
       <c r="F134" s="3" t="n">
-        <v>6726.58</v>
+        <v>249.76</v>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>201,439.38 Cr</t>
+          <t>-21,485.51 Cr</t>
         </is>
       </c>
     </row>
@@ -3819,22 +3821,22 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>14-06-2026</t>
+          <t>17-06-2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/332211009988/DR/BOOKMYSHOW TICKET</t>
+          <t>OFFICE PANTRY &amp; FRESH REFRESHMENTS</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr"/>
       <c r="E135" s="3" t="n">
-        <v>395.77</v>
+        <v>1043.63</v>
       </c>
       <c r="F135" s="3" t="n"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>201,043.61 Cr</t>
+          <t>-22,529.14 Cr</t>
         </is>
       </c>
     </row>
@@ -3844,22 +3846,22 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>14-06-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/908129381023/DR/BILLDESK/SBIN/billdesk@sbi</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606182653/CR</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr"/>
-      <c r="E136" s="3" t="n">
-        <v>1042.09</v>
-      </c>
-      <c r="F136" s="3" t="n"/>
+      <c r="E136" s="3" t="n"/>
+      <c r="F136" s="3" t="n">
+        <v>8910.01</v>
+      </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>200,001.52 Cr</t>
+          <t>-13,619.13 Cr</t>
         </is>
       </c>
     </row>
@@ -3869,22 +3871,22 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>15-06-2026</t>
+          <t>19-06-2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606154135/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606193446/CR</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr"/>
       <c r="E137" s="3" t="n"/>
       <c r="F137" s="3" t="n">
-        <v>2097.48</v>
+        <v>1898.71</v>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>202,099.00 Cr</t>
+          <t>-11,720.42 Cr</t>
         </is>
       </c>
     </row>
@@ -3894,22 +3896,1795 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>15-06-2026</t>
+          <t>19-06-2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/112938102938/CR/WHOLESALE MILK DEPOSIT</t>
+          <t>EMPLOYEE FIELD COMMUTE &amp; TRAVEL REIMBURSEMENT</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr"/>
-      <c r="E138" s="3" t="n"/>
-      <c r="F138" s="3" t="n">
-        <v>7110.08</v>
-      </c>
+      <c r="E138" s="3" t="n">
+        <v>5919.96</v>
+      </c>
+      <c r="F138" s="3" t="n"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>209,209.08 Cr</t>
+          <t>-17,640.38 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>19-06-2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/235911221570/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr"/>
+      <c r="E139" s="3" t="n">
+        <v>42.78</v>
+      </c>
+      <c r="F139" s="3" t="n"/>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>-17,683.16 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>19-06-2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/443322110099/CR/PROMO DISCOUNT CREDIT</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr"/>
+      <c r="E140" s="3" t="n"/>
+      <c r="F140" s="3" t="n">
+        <v>77.58</v>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>-17,605.58 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>20-06-2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606202980/CR</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr"/>
+      <c r="E141" s="3" t="n"/>
+      <c r="F141" s="3" t="n">
+        <v>8363.01</v>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>-9,242.57 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>20-06-2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/301984712093/DR/SWIGGY/HDFC/swiggy@hdfc</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr"/>
+      <c r="E142" s="3" t="n">
+        <v>577.59</v>
+      </c>
+      <c r="F142" s="3" t="n"/>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>-9,820.16 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>21-06-2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606214056/CR</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr"/>
+      <c r="E143" s="3" t="n"/>
+      <c r="F143" s="3" t="n">
+        <v>3009.13</v>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>-6,811.03 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>21-06-2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>BANK SMS ALERTS &amp; ANNUAL MAINT CHARGES</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr"/>
+      <c r="E144" s="3" t="n">
+        <v>93.23</v>
+      </c>
+      <c r="F144" s="3" t="n"/>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>-6,904.26 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606227744/CR</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr"/>
+      <c r="E145" s="3" t="n"/>
+      <c r="F145" s="3" t="n">
+        <v>5357.8</v>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>-1,546.46 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>JNS-PMSBY-25-26-00289608474-301-631272322</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr"/>
+      <c r="E146" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F146" s="3" t="n"/>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>-1,566.46 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>23-06-2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606231322/CR</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr"/>
+      <c r="E147" s="3" t="n"/>
+      <c r="F147" s="3" t="n">
+        <v>9841.469999999999</v>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>8,275.01 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>23-06-2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>DELIVERY ELECTRIC VAN MAINTENANCE &amp; AMC</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr"/>
+      <c r="E148" s="3" t="n">
+        <v>4574.61</v>
+      </c>
+      <c r="F148" s="3" t="n"/>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>3,700.40 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606242706/CR</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr"/>
+      <c r="E149" s="3" t="n"/>
+      <c r="F149" s="3" t="n">
+        <v>2545.62</v>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>6,246.02 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>CHQ PAID / CLEARING NO 004812</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr"/>
+      <c r="E150" s="3" t="n">
+        <v>12450.18</v>
+      </c>
+      <c r="F150" s="3" t="n"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>-6,204.16 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/982301928371/CR/LOCAL VENDOR/ICIC/vendor@icici</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr"/>
+      <c r="E151" s="3" t="n"/>
+      <c r="F151" s="3" t="n">
+        <v>4278.93</v>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>-1,925.23 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606254407/CR</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr"/>
+      <c r="E152" s="3" t="n"/>
+      <c r="F152" s="3" t="n">
+        <v>7364.36</v>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>5,439.13 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/412938102938/DR/BIGBASKET/ICIC/bb@icici</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr"/>
+      <c r="E153" s="3" t="n">
+        <v>1093.01</v>
+      </c>
+      <c r="F153" s="3" t="n"/>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>4,346.12 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/701074556047/DR/73374590/PUNB/7337459005@pty</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr"/>
+      <c r="E154" s="3" t="n">
+        <v>153.47</v>
+      </c>
+      <c r="F154" s="3" t="n"/>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>4,192.65 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>26-06-2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606268473/CR</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr"/>
+      <c r="E155" s="3" t="n"/>
+      <c r="F155" s="3" t="n">
+        <v>3173.05</v>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>7,365.70 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>26-06-2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr"/>
+      <c r="E156" s="3" t="n">
+        <v>12217.36</v>
+      </c>
+      <c r="F156" s="3" t="n"/>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>-4,851.66 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>27-06-2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606273957/CR</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr"/>
+      <c r="E157" s="3" t="n"/>
+      <c r="F157" s="3" t="n">
+        <v>10202.06</v>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>5,350.40 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>27-06-2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>COMMERCIAL WAREHOUSE RENT / KORAMANGALA HUB</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr"/>
+      <c r="E158" s="3" t="n">
+        <v>44344.23</v>
+      </c>
+      <c r="F158" s="3" t="n"/>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>-38,993.83 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>28-06-2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606285235/CR</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr"/>
+      <c r="E159" s="3" t="n"/>
+      <c r="F159" s="3" t="n">
+        <v>2674.8</v>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>-36,319.03 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>28-06-2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>CHQ PAID / CLEARING NO 004812</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr"/>
+      <c r="E160" s="3" t="n">
+        <v>12749.7</v>
+      </c>
+      <c r="F160" s="3" t="n"/>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>-49,068.73 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>28-06-2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>AWS CLOUD SERVER HOSTING &amp; INFRASTRUCTURE</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr"/>
+      <c r="E161" s="3" t="n">
+        <v>7931.75</v>
+      </c>
+      <c r="F161" s="3" t="n"/>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>-57,000.48 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606293722/CR</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr"/>
+      <c r="E162" s="3" t="n"/>
+      <c r="F162" s="3" t="n">
+        <v>6531.87</v>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>-50,468.61 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/789123891023/CR/CUSTOMER REFUND REVERSAL</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr"/>
+      <c r="E163" s="3" t="n"/>
+      <c r="F163" s="3" t="n">
+        <v>702.25</v>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>-49,766.36 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/455944913251/DR/KEMSARAP/SBIN/ 8977604821@yb</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr"/>
+      <c r="E164" s="3" t="n">
+        <v>104.26</v>
+      </c>
+      <c r="F164" s="3" t="n"/>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>-49,870.62 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606306927/CR</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr"/>
+      <c r="E165" s="3" t="n"/>
+      <c r="F165" s="3" t="n">
+        <v>6062.44</v>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>-43,808.18 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>01-07-2026</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607016477/CR</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr"/>
+      <c r="E166" s="3" t="n"/>
+      <c r="F166" s="3" t="n">
+        <v>4067.15</v>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>-39,741.03 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607022682/CR</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr"/>
+      <c r="E167" s="3" t="n"/>
+      <c r="F167" s="3" t="n">
+        <v>7380.75</v>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>-32,360.28 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/857830578859/DR/GAURAV S/YESB/ Q815875629@yb</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr"/>
+      <c r="E168" s="3" t="n">
+        <v>203.27</v>
+      </c>
+      <c r="F168" s="3" t="n"/>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>-32,563.55 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/347067657684/DR/KAJALVI/YESB/paytm.s1w3jr9@</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr"/>
+      <c r="E169" s="3" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="F169" s="3" t="n"/>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>-32,678.05 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/776655443322/CR/CASHBACK REWARD</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr"/>
+      <c r="E170" s="3" t="n"/>
+      <c r="F170" s="3" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>-32,626.35 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>03-07-2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607036464/CR</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr"/>
+      <c r="E171" s="3" t="n"/>
+      <c r="F171" s="3" t="n">
+        <v>3663.3</v>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-28,963.05 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>04-07-2026</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607047215/CR</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr"/>
+      <c r="E172" s="3" t="n"/>
+      <c r="F172" s="3" t="n">
+        <v>3411.62</v>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>-25,551.43 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>04-07-2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/412938102938/DR/BIGBASKET/ICIC/bb@icici</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr"/>
+      <c r="E173" s="3" t="n">
+        <v>1797.16</v>
+      </c>
+      <c r="F173" s="3" t="n"/>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-27,348.59 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>05-07-2026</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607058720/CR</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr"/>
+      <c r="E174" s="3" t="n"/>
+      <c r="F174" s="3" t="n">
+        <v>4789.83</v>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>-22,558.76 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>05-07-2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>AWS CLOUD SERVER HOSTING &amp; INFRASTRUCTURE</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr"/>
+      <c r="E175" s="3" t="n">
+        <v>7462.98</v>
+      </c>
+      <c r="F175" s="3" t="n"/>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-30,021.74 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>05-07-2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/022447403071/CR/THIRUVEE/UBIN/9391652831-2@a</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr"/>
+      <c r="E176" s="3" t="n"/>
+      <c r="F176" s="3" t="n">
+        <v>752.0700000000001</v>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>-29,269.67 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>06-07-2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607067745/CR</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr"/>
+      <c r="E177" s="3" t="n"/>
+      <c r="F177" s="3" t="n">
+        <v>2290.54</v>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>-26,979.13 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>06-07-2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/857830578859/DR/GAURAV S/YESB/ Q815875629@yb</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr"/>
+      <c r="E178" s="3" t="n">
+        <v>182.64</v>
+      </c>
+      <c r="F178" s="3" t="n"/>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>-27,161.77 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>06-07-2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/172136536211/DR/ZOMATO L/YESB/zomato-order@p</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr"/>
+      <c r="E179" s="3" t="n">
+        <v>408.5</v>
+      </c>
+      <c r="F179" s="3" t="n"/>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>-27,570.27 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>06-07-2026</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/908129381023/DR/BILLDESK/SBIN/billdesk@sbi</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr"/>
+      <c r="E180" s="3" t="n">
+        <v>1040.42</v>
+      </c>
+      <c r="F180" s="3" t="n"/>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>-28,610.69 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>07-07-2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607077969/CR</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr"/>
+      <c r="E181" s="3" t="n"/>
+      <c r="F181" s="3" t="n">
+        <v>3591.45</v>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>-25,019.24 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>07-07-2026</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/077728365159/DR/NAMBURI /YESB/ Q501702001@yb</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr"/>
+      <c r="E182" s="3" t="n">
+        <v>66.48</v>
+      </c>
+      <c r="F182" s="3" t="n"/>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>-25,085.72 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>08-07-2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605282597/CR</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr"/>
+      <c r="E183" s="3" t="n"/>
+      <c r="F183" s="3" t="n"/>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>-52,822.51 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>08-07-2026</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607081320/CR</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr"/>
+      <c r="E184" s="3" t="n"/>
+      <c r="F184" s="3" t="n">
+        <v>7372.48</v>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>-45,450.03 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>08-07-2026</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/719421374678/DR/NEWKRSN/YESB/paytmqr6a0ixr@</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr"/>
+      <c r="E185" s="3" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="F185" s="3" t="n"/>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>-45,552.23 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>08-07-2026</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE STAFF WAGES &amp; PACKING CREW</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr"/>
+      <c r="E186" s="3" t="n">
+        <v>36763.2</v>
+      </c>
+      <c r="F186" s="3" t="n"/>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>-82,315.43 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>08-07-2026</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/554433221100/DR/FLIPKART ONLINE</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr"/>
+      <c r="E187" s="3" t="n">
+        <v>3876.83</v>
+      </c>
+      <c r="F187" s="3" t="n"/>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>-86,192.26 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>08-07-2026</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/455944913251/DR/KEMSARAP/SBIN/ 8977604821@yb</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr"/>
+      <c r="E188" s="3" t="n">
+        <v>63.06</v>
+      </c>
+      <c r="F188" s="3" t="n"/>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>-86,255.32 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>09-07-2026</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607092736/CR</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr"/>
+      <c r="E189" s="3" t="n"/>
+      <c r="F189" s="3" t="n">
+        <v>7946.47</v>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>-78,308.85 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>09-07-2026</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>UPIAB/271988123471/CR/THIRUVEE/UBIN/9391652831-2@a</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr"/>
+      <c r="E190" s="3" t="n"/>
+      <c r="F190" s="3" t="n">
+        <v>207.62</v>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>-78,101.23 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>09-07-2026</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>GOOGLE WORKSPACE &amp; SLACK CLOUD SUITE</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr"/>
+      <c r="E191" s="3" t="n">
+        <v>6501.68</v>
+      </c>
+      <c r="F191" s="3" t="n"/>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>-84,602.91 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>10-07-2026</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607103466/CR</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr"/>
+      <c r="E192" s="3" t="n"/>
+      <c r="F192" s="3" t="n">
+        <v>5328.15</v>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>-79,274.76 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>10-07-2026</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>CHQ PAID / CLEARING NO 004812</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr"/>
+      <c r="E193" s="3" t="n">
+        <v>13092.28</v>
+      </c>
+      <c r="F193" s="3" t="n"/>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>-92,367.04 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>11-07-2026</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607112876/CR</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr"/>
+      <c r="E194" s="3" t="n"/>
+      <c r="F194" s="3" t="n">
+        <v>5179.4</v>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>-87,187.64 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>11-07-2026</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/123854061954/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr"/>
+      <c r="E195" s="3" t="n">
+        <v>203.06</v>
+      </c>
+      <c r="F195" s="3" t="n"/>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>-87,390.70 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>11-07-2026</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/221100998877/DR/UBER RIDE</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr"/>
+      <c r="E196" s="3" t="n">
+        <v>740.91</v>
+      </c>
+      <c r="F196" s="3" t="n"/>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>-88,131.61 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>12-07-2026</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607129486/CR</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr"/>
+      <c r="E197" s="3" t="n"/>
+      <c r="F197" s="3" t="n">
+        <v>3021.33</v>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>-85,110.28 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>12-07-2026</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/908931590719/DR/Mr Raju/YESB/ Q249677790@yb</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr"/>
+      <c r="E198" s="3" t="n">
+        <v>64.56999999999999</v>
+      </c>
+      <c r="F198" s="3" t="n"/>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>-85,174.85 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>13-07-2026</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607135659/CR</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr"/>
+      <c r="E199" s="3" t="n"/>
+      <c r="F199" s="3" t="n">
+        <v>4498.75</v>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>-80,676.10 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>13-07-2026</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/812938102938/DR/PETROL PUMP/HPCL/hpcl@icici</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr"/>
+      <c r="E200" s="3" t="n">
+        <v>1292.6</v>
+      </c>
+      <c r="F200" s="3" t="n"/>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>-81,968.70 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>13-07-2026</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>JNS-PMSBY-25-26-00289608474-301-631272322</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr"/>
+      <c r="E201" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F201" s="3" t="n"/>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>-81,988.70 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>14-07-2026</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607144495/CR</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr"/>
+      <c r="E202" s="3" t="n"/>
+      <c r="F202" s="3" t="n">
+        <v>1782.85</v>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>-80,205.85 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>14-07-2026</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>POINT OF SALE (POS) HARDWARE RENTAL</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr"/>
+      <c r="E203" s="3" t="n">
+        <v>2705.12</v>
+      </c>
+      <c r="F203" s="3" t="n"/>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>-82,910.97 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>14-07-2026</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>NEFT/INWARD/CITI/GROCERY WHOLESALE REBATE</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr"/>
+      <c r="E204" s="3" t="n"/>
+      <c r="F204" s="3" t="n">
+        <v>17024.04</v>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>-65,886.93 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>15-07-2026</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607155953/CR</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr"/>
+      <c r="E205" s="3" t="n"/>
+      <c r="F205" s="3" t="n">
+        <v>1771.87</v>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>-64,115.06 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>15-07-2026</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/719421374678/DR/NEWKRSN/YESB/paytmqr6a0ixr@</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr"/>
+      <c r="E206" s="3" t="n">
+        <v>234.32</v>
+      </c>
+      <c r="F206" s="3" t="n"/>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>-64,349.38 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>15-07-2026</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/332211009988/DR/BOOKMYSHOW TICKET</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr"/>
+      <c r="E207" s="3" t="n">
+        <v>834.78</v>
+      </c>
+      <c r="F207" s="3" t="n"/>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>-65,184.16 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>15-07-2026</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>UPIAR/301984712093/DR/SWIGGY/HDFC/swiggy@hdfc</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr"/>
+      <c r="E208" s="3" t="n">
+        <v>604.8</v>
+      </c>
+      <c r="F208" s="3" t="n"/>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>-65,788.96 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>15-07-2026</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>SECURITY GUARD SERVICES &amp; CCTV MONITORING</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr"/>
+      <c r="E209" s="3" t="n">
+        <v>7566.12</v>
+      </c>
+      <c r="F209" s="3" t="n"/>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>-73,355.08 Cr</t>
         </is>
       </c>
     </row>

--- a/generated_data/bank_statement_union_bank.xlsx
+++ b/generated_data/bank_statement_union_bank.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G209"/>
+  <dimension ref="A1:G208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,17 +501,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605011427/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605018503/CR</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n">
-        <v>2287.46</v>
+        <v>9365.389999999999</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>17,287.46 Cr</t>
+          <t>24,365.39 Cr</t>
         </is>
       </c>
     </row>
@@ -521,22 +521,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01-05-2026</t>
+          <t>02-05-2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/554433221100/DR/FLIPKART ONLINE</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605027965/CR</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="3" t="n">
-        <v>1497.57</v>
-      </c>
-      <c r="F3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n">
+        <v>2409.27</v>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>15,789.89 Cr</t>
+          <t>26,774.66 Cr</t>
         </is>
       </c>
     </row>
@@ -551,17 +551,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605028087/CR</t>
+          <t>UPIAR/373995020793/DR/LHEMANT/HDFC/hemanth0508@yb</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n">
-        <v>6400</v>
-      </c>
+      <c r="E4" s="3" t="n">
+        <v>1141.84</v>
+      </c>
+      <c r="F4" s="3" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>22,189.89 Cr</t>
+          <t>25,632.82 Cr</t>
         </is>
       </c>
     </row>
@@ -576,17 +576,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/271988123471/CR/THIRUVEE/UBIN/9391652831-2@a</t>
+          <t>UPIAR/212938102938/DR/BLINKIT/KOTAK/blinkit@kotak</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n">
-        <v>167.47</v>
-      </c>
+      <c r="E5" s="3" t="n">
+        <v>238.53</v>
+      </c>
+      <c r="F5" s="3" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,357.36 Cr</t>
+          <t>25,394.29 Cr</t>
         </is>
       </c>
     </row>
@@ -601,17 +601,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>NEFT/OUTWARD/UTI MUTUAL FUND SIP</t>
+          <t>UPIAB/712626244599/CR/PICHIKA/BARB/ 8985068499@ax</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="3" t="n">
-        <v>9214.370000000001</v>
-      </c>
-      <c r="F6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n">
+        <v>459.04</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13,142.99 Cr</t>
+          <t>25,853.33 Cr</t>
         </is>
       </c>
     </row>
@@ -626,17 +626,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/776655443322/CR/CASHBACK REWARD</t>
+          <t>PRINTING BARCODE LABELS &amp; BILLING ROLLS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n">
-        <v>146.29</v>
-      </c>
+      <c r="E7" s="3" t="n">
+        <v>3496.96</v>
+      </c>
+      <c r="F7" s="3" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,289.28 Cr</t>
+          <t>22,356.37 Cr</t>
         </is>
       </c>
     </row>
@@ -651,17 +651,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605036742/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605035309/CR</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n">
-        <v>8984.190000000001</v>
+        <v>1322.72</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>22,273.47 Cr</t>
+          <t>23,679.09 Cr</t>
         </is>
       </c>
     </row>
@@ -676,17 +676,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>WATER TANKER &amp; SANITATION CHARGES</t>
+          <t>UPIAR/908931590719/DR/Mr Raju/YESB/ Q249677790@yb</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="3" t="n">
-        <v>3463.18</v>
+        <v>127.3</v>
       </c>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,810.29 Cr</t>
+          <t>23,551.79 Cr</t>
         </is>
       </c>
     </row>
@@ -701,17 +701,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/908129381023/DR/BILLDESK/SBIN/billdesk@sbi</t>
+          <t>UPIAR/554433221100/DR/FLIPKART ONLINE</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="3" t="n">
-        <v>1167.7</v>
+        <v>2092.46</v>
       </c>
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,642.59 Cr</t>
+          <t>21,459.33 Cr</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>04-05-2026</t>
+          <t>03-05-2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605049127/CR</t>
+          <t>NEFT/INWARD/CITI/GROCERY WHOLESALE REBATE</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n">
-        <v>3923.73</v>
+        <v>12251.46</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,566.32 Cr</t>
+          <t>33,710.79 Cr</t>
         </is>
       </c>
     </row>
@@ -751,17 +751,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/455944913251/DR/KEMSARAP/SBIN/ 8977604821@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605048309/CR</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="3" t="n">
-        <v>74.31999999999999</v>
-      </c>
-      <c r="F12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n">
+        <v>9181.969999999999</v>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>21,492.00 Cr</t>
+          <t>42,892.76 Cr</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605054959/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605052593/CR</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n">
-        <v>4448.73</v>
+        <v>5748.41</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,940.73 Cr</t>
+          <t>48,641.17 Cr</t>
         </is>
       </c>
     </row>
@@ -801,17 +801,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/712626244599/CR/PICHIKA/BARB/ 8985068499@ax</t>
+          <t>COMMERCIAL WAREHOUSE RENT / KORAMANGALA HUB</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n">
-        <v>491.8</v>
-      </c>
+      <c r="E14" s="3" t="n">
+        <v>46921.38</v>
+      </c>
+      <c r="F14" s="3" t="n"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>26,432.53 Cr</t>
+          <t>1,719.79 Cr</t>
         </is>
       </c>
     </row>
@@ -821,22 +821,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05-05-2026</t>
+          <t>06-05-2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>WATER TANKER &amp; SANITATION CHARGES</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605066230/CR</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="3" t="n">
-        <v>2569.68</v>
-      </c>
-      <c r="F15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n">
+        <v>3153.56</v>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,862.85 Cr</t>
+          <t>4,873.35 Cr</t>
         </is>
       </c>
     </row>
@@ -846,22 +846,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>05-05-2026</t>
+          <t>06-05-2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COMMERCIAL WAREHOUSE RENT / KORAMANGALA HUB</t>
+          <t>NEFT/INWARD/CITI/GROCERY WHOLESALE REBATE</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="3" t="n">
-        <v>39005.09</v>
-      </c>
-      <c r="F16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n">
+        <v>7158.67</v>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-15,142.24 Cr</t>
+          <t>12,032.02 Cr</t>
         </is>
       </c>
     </row>
@@ -876,17 +876,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605067549/CR</t>
+          <t>FIRE SAFETY INSPECTION &amp; EQUIPMENT REFILL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n">
-        <v>2245.42</v>
-      </c>
+      <c r="E17" s="3" t="n">
+        <v>4757.85</v>
+      </c>
+      <c r="F17" s="3" t="n"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,896.82 Cr</t>
+          <t>7,274.17 Cr</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/009988776655/CR/DIVIDEND PAYOUT</t>
+          <t>UPIAB/020074062699/CR/THIRUVEE/UBIN/9391652831-2@a</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n">
-        <v>1310.58</v>
+        <v>743.29</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-11,586.24 Cr</t>
+          <t>8,017.46 Cr</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>LIC PREMIUM AUTO DEBIT CLEARING</t>
+          <t>UPIAB/637338636405/CR/PITCHIKA/SBIN/ 8919861154@yb</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="3" t="n">
-        <v>9851.209999999999</v>
-      </c>
-      <c r="F19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n">
+        <v>2831.66</v>
+      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,437.45 Cr</t>
+          <t>10,849.12 Cr</t>
         </is>
       </c>
     </row>
@@ -946,22 +946,22 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>06-05-2026</t>
+          <t>07-05-2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COMMERCIAL WAREHOUSE RENT / KORAMANGALA HUB</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605071114/CR</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="3" t="n">
-        <v>40575.4</v>
-      </c>
-      <c r="F20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n">
+        <v>4945.96</v>
+      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-62,012.85 Cr</t>
+          <t>15,795.08 Cr</t>
         </is>
       </c>
     </row>
@@ -971,22 +971,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>06-05-2026</t>
+          <t>07-05-2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/412938102938/DR/BIGBASKET/ICIC/bb@icici</t>
+          <t>DELIVERY ELECTRIC VAN MAINTENANCE &amp; AMC</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="3" t="n">
-        <v>682.6799999999999</v>
+        <v>3225.67</v>
       </c>
       <c r="F21" s="3" t="n"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-62,695.53 Cr</t>
+          <t>12,569.41 Cr</t>
         </is>
       </c>
     </row>
@@ -996,22 +996,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>07-05-2026</t>
+          <t>08-05-2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605075172/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605087060/CR</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n">
-        <v>4935.5</v>
+        <v>6267.17</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-57,760.03 Cr</t>
+          <t>18,836.58 Cr</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>07-05-2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/455944913251/DR/KEMSARAP/SBIN/ 8977604821@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605097315/CR</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
-      <c r="E23" s="3" t="n">
-        <v>293</v>
-      </c>
-      <c r="F23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n">
+        <v>4005.05</v>
+      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-58,053.03 Cr</t>
+          <t>22,841.63 Cr</t>
         </is>
       </c>
     </row>
@@ -1046,22 +1046,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07-05-2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COMMERCIAL WAREHOUSE RENT / KORAMANGALA HUB</t>
+          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="3" t="n">
-        <v>46600.77</v>
+        <v>14726.31</v>
       </c>
       <c r="F24" s="3" t="n"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-104,653.80 Cr</t>
+          <t>8,115.32 Cr</t>
         </is>
       </c>
     </row>
@@ -1071,22 +1071,22 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>08-05-2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605082353/CR</t>
+          <t>NEFT/INWARD/CITI/GROCERY WHOLESALE REBATE</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n">
-        <v>9357.01</v>
+        <v>15509.68</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-95,296.79 Cr</t>
+          <t>23,625.00 Cr</t>
         </is>
       </c>
     </row>
@@ -1096,22 +1096,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08-05-2026</t>
+          <t>10-05-2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/982301928371/CR/LOCAL VENDOR/ICIC/vendor@icici</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605104157/CR</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="n">
-        <v>3435.21</v>
+        <v>4945.03</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-91,861.58 Cr</t>
+          <t>28,570.03 Cr</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08-05-2026</t>
+          <t>10-05-2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EMPLOYEE FIELD COMMUTE &amp; TRAVEL REIMBURSEMENT</t>
+          <t>AIRTEL CORPORATE BROADBAND &amp; FIBER</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="3" t="n">
-        <v>3957.88</v>
+        <v>1599.8</v>
       </c>
       <c r="F27" s="3" t="n"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-95,819.46 Cr</t>
+          <t>26,970.23 Cr</t>
         </is>
       </c>
     </row>
@@ -1146,22 +1146,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>08-05-2026</t>
+          <t>10-05-2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/800823341214/CR/PITCHIKA/CNRB/ umanag9712@ax</t>
+          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n">
-        <v>2336.55</v>
-      </c>
+      <c r="E28" s="3" t="n">
+        <v>10753.45</v>
+      </c>
+      <c r="F28" s="3" t="n"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-93,482.91 Cr</t>
+          <t>16,216.78 Cr</t>
         </is>
       </c>
     </row>
@@ -1171,22 +1171,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>08-05-2026</t>
+          <t>11-05-2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/554433221100/DR/FLIPKART ONLINE</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605118141/CR</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
-      <c r="E29" s="3" t="n">
-        <v>1611.34</v>
-      </c>
-      <c r="F29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n">
+        <v>8523.200000000001</v>
+      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-95,094.25 Cr</t>
+          <t>24,739.98 Cr</t>
         </is>
       </c>
     </row>
@@ -1196,22 +1196,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>08-05-2026</t>
+          <t>11-05-2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EMPLOYEE FIELD COMMUTE &amp; TRAVEL REIMBURSEMENT</t>
+          <t>UPIAR/026544681447/DR/SHANTIP/YESB/ Q707874078@yb</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="3" t="n">
-        <v>4117.78</v>
+        <v>718.5</v>
       </c>
       <c r="F30" s="3" t="n"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-99,212.03 Cr</t>
+          <t>24,021.48 Cr</t>
         </is>
       </c>
     </row>
@@ -1221,22 +1221,22 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>12-05-2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605092491/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605129242/CR</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n">
-        <v>2416.85</v>
+        <v>4404.61</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-96,795.18 Cr</t>
+          <t>28,426.09 Cr</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>12-05-2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/776655443322/CR/CASHBACK REWARD</t>
+          <t>JNS-PMSBY-25-26-00289608474-301-631272322</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n">
-        <v>123.86</v>
-      </c>
+      <c r="E32" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F32" s="3" t="n"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-96,671.32 Cr</t>
+          <t>28,406.09 Cr</t>
         </is>
       </c>
     </row>
@@ -1271,22 +1271,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>13-05-2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/645455850592/DR/DDhanus/SBIN/ 7396913943@up</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605137034/CR</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
-      <c r="E33" s="3" t="n">
-        <v>110.36</v>
-      </c>
-      <c r="F33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n">
+        <v>2552.79</v>
+      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-96,781.68 Cr</t>
+          <t>30,958.88 Cr</t>
         </is>
       </c>
     </row>
@@ -1296,22 +1296,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>14-05-2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/637338636405/CR/PITCHIKA/SBIN/ 8919861154@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605145636/CR</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n">
-        <v>3606.27</v>
+        <v>5938.72</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-93,175.41 Cr</t>
+          <t>36,897.60 Cr</t>
         </is>
       </c>
     </row>
@@ -1321,22 +1321,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>14-05-2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/455944913251/DR/KEMSARAP/SBIN/ 8977604821@yb</t>
+          <t>UPIAR/140288398543/DR/73374590/PUNB/7337459005@pty</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="3" t="n">
-        <v>147.06</v>
+        <v>100.06</v>
       </c>
       <c r="F35" s="3" t="n"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-93,322.47 Cr</t>
+          <t>36,797.54 Cr</t>
         </is>
       </c>
     </row>
@@ -1346,22 +1346,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>10-05-2026</t>
+          <t>14-05-2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605102312/CR</t>
+          <t>INVENTORY AUDITOR &amp; CA LEGAL RETAINER</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n">
-        <v>3828.16</v>
-      </c>
+      <c r="E36" s="3" t="n">
+        <v>15261.91</v>
+      </c>
+      <c r="F36" s="3" t="n"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-89,494.31 Cr</t>
+          <t>21,535.63 Cr</t>
         </is>
       </c>
     </row>
@@ -1371,22 +1371,22 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>10-05-2026</t>
+          <t>14-05-2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/908931590719/DR/Mr Raju/YESB/ Q249677790@yb</t>
+          <t>UPIAR/140515780706/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="3" t="n">
-        <v>97.95</v>
+        <v>249.18</v>
       </c>
       <c r="F37" s="3" t="n"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-89,592.26 Cr</t>
+          <t>21,286.45 Cr</t>
         </is>
       </c>
     </row>
@@ -1396,22 +1396,22 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>10-05-2026</t>
+          <t>14-05-2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>OFFICE PANTRY &amp; FRESH REFRESHMENTS</t>
+          <t>UPIAB/322671730620/CR/PITCHIKA/SBIN/ 8919861154@ax</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="3" t="n">
-        <v>2450.43</v>
-      </c>
-      <c r="F38" s="3" t="n"/>
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="3" t="n">
+        <v>3643</v>
+      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>-92,042.69 Cr</t>
+          <t>24,929.45 Cr</t>
         </is>
       </c>
     </row>
@@ -1421,22 +1421,22 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>11-05-2026</t>
+          <t>15-05-2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605111290/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605159985/CR</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="n">
-        <v>9607.370000000001</v>
+        <v>4840.76</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-82,435.32 Cr</t>
+          <t>29,770.21 Cr</t>
         </is>
       </c>
     </row>
@@ -1446,22 +1446,22 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>11-05-2026</t>
+          <t>15-05-2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>AIRTEL CORPORATE BROADBAND &amp; FIBER</t>
+          <t>UPIAR/455944913251/DR/KEMSARAP/SBIN/ 8977604821@yb</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="3" t="n">
-        <v>3071.74</v>
+        <v>161.52</v>
       </c>
       <c r="F40" s="3" t="n"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>-85,507.06 Cr</t>
+          <t>29,608.69 Cr</t>
         </is>
       </c>
     </row>
@@ -1471,22 +1471,22 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>12-05-2026</t>
+          <t>15-05-2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605125975/CR</t>
+          <t>SWIGGY INSTAMART FLEET REIMBURSEMENT</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n">
-        <v>6386.75</v>
-      </c>
+      <c r="E41" s="3" t="n">
+        <v>1603.35</v>
+      </c>
+      <c r="F41" s="3" t="n"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-79,120.31 Cr</t>
+          <t>28,005.34 Cr</t>
         </is>
       </c>
     </row>
@@ -1496,22 +1496,22 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12-05-2026</t>
+          <t>16-05-2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>SWIGGY INSTAMART FLEET REIMBURSEMENT</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605168867/CR</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="3" t="n">
-        <v>1456.79</v>
-      </c>
-      <c r="F42" s="3" t="n"/>
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3" t="n">
+        <v>3209.96</v>
+      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>-80,577.10 Cr</t>
+          <t>31,215.30 Cr</t>
         </is>
       </c>
     </row>
@@ -1521,22 +1521,22 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>12-05-2026</t>
+          <t>16-05-2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>EMPLOYEE FIELD COMMUTE &amp; TRAVEL REIMBURSEMENT</t>
+          <t>UPIAR/026544681447/DR/SHANTIP/YESB/ Q707874078@yb</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="3" t="n">
-        <v>3939.67</v>
+        <v>778.35</v>
       </c>
       <c r="F43" s="3" t="n"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-84,516.77 Cr</t>
+          <t>30,436.95 Cr</t>
         </is>
       </c>
     </row>
@@ -1546,22 +1546,22 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>13-05-2026</t>
+          <t>16-05-2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605139045/CR</t>
+          <t>ATM CASH WITHDRAWAL / KORAMANGALA BRANCH</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="3" t="n"/>
-      <c r="F44" s="3" t="n">
-        <v>4646.51</v>
-      </c>
+      <c r="E44" s="3" t="n">
+        <v>6822.28</v>
+      </c>
+      <c r="F44" s="3" t="n"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>-79,870.26 Cr</t>
+          <t>23,614.67 Cr</t>
         </is>
       </c>
     </row>
@@ -1571,22 +1571,22 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>13-05-2026</t>
+          <t>17-05-2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/624556864731/CR/PICHIKA/UBIN/pvasuviswanadh</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605179941/CR</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="n">
-        <v>1567.21</v>
+        <v>4223.49</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-78,303.05 Cr</t>
+          <t>27,838.16 Cr</t>
         </is>
       </c>
     </row>
@@ -1596,22 +1596,22 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>14-05-2026</t>
+          <t>17-05-2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605146115/CR</t>
+          <t>UPIAB/982301928371/CR/LOCAL VENDOR/ICIC/vendor@icici</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="n">
-        <v>2821.71</v>
+        <v>6186.89</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>-75,481.34 Cr</t>
+          <t>34,025.05 Cr</t>
         </is>
       </c>
     </row>
@@ -1621,22 +1621,22 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>14-05-2026</t>
+          <t>17-05-2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/637338636405/CR/PITCHIKA/SBIN/ 8919861154@yb</t>
+          <t>UPIAR/140515780706/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
-      <c r="E47" s="3" t="n"/>
-      <c r="F47" s="3" t="n">
-        <v>2238.73</v>
-      </c>
+      <c r="E47" s="3" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="F47" s="3" t="n"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-73,242.61 Cr</t>
+          <t>33,706.55 Cr</t>
         </is>
       </c>
     </row>
@@ -1646,22 +1646,22 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14-05-2026</t>
+          <t>18-05-2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>NEFT/OUTWARD/HDFC/FARMERS COOP SUPPLY</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605186777/CR</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="3" t="n">
-        <v>18951.27</v>
-      </c>
-      <c r="F48" s="3" t="n"/>
+      <c r="E48" s="3" t="n"/>
+      <c r="F48" s="3" t="n">
+        <v>8272.58</v>
+      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>-92,193.88 Cr</t>
+          <t>41,979.13 Cr</t>
         </is>
       </c>
     </row>
@@ -1671,22 +1671,22 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>15-05-2026</t>
+          <t>19-05-2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605154901/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605192365/CR</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="3" t="n"/>
       <c r="F49" s="3" t="n">
-        <v>4744.68</v>
+        <v>4329.71</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-87,449.20 Cr</t>
+          <t>46,308.84 Cr</t>
         </is>
       </c>
     </row>
@@ -1696,22 +1696,22 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>15-05-2026</t>
+          <t>19-05-2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>PRINTING BARCODE LABELS &amp; BILLING ROLLS</t>
+          <t>UPIAR/140288398543/DR/73374590/PUNB/7337459005@pty</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="3" t="n">
-        <v>2749.33</v>
+        <v>190.41</v>
       </c>
       <c r="F50" s="3" t="n"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>-90,198.53 Cr</t>
+          <t>46,118.43 Cr</t>
         </is>
       </c>
     </row>
@@ -1721,22 +1721,22 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>15-05-2026</t>
+          <t>19-05-2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/637338636405/CR/PITCHIKA/SBIN/ 8919861154@yb</t>
+          <t>GOOGLE WORKSPACE &amp; SLACK CLOUD SUITE</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
-      <c r="E51" s="3" t="n"/>
-      <c r="F51" s="3" t="n">
-        <v>2832.86</v>
-      </c>
+      <c r="E51" s="3" t="n">
+        <v>6526.14</v>
+      </c>
+      <c r="F51" s="3" t="n"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-87,365.67 Cr</t>
+          <t>39,592.29 Cr</t>
         </is>
       </c>
     </row>
@@ -1746,22 +1746,22 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16-05-2026</t>
+          <t>19-05-2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605165632/CR</t>
+          <t>UPIAR/373995020793/DR/LHEMANT/HDFC/hemanth0508@yb</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="3" t="n"/>
-      <c r="F52" s="3" t="n">
-        <v>6015.05</v>
-      </c>
+      <c r="E52" s="3" t="n">
+        <v>1941.18</v>
+      </c>
+      <c r="F52" s="3" t="n"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>-81,350.62 Cr</t>
+          <t>37,651.11 Cr</t>
         </is>
       </c>
     </row>
@@ -1771,22 +1771,22 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16-05-2026</t>
+          <t>19-05-2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>BESCOM POWER UTILITY / BANGALORE WAREHOUSE</t>
+          <t>UPIAB/322671730620/CR/PITCHIKA/SBIN/ 8919861154@ax</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
-      <c r="E53" s="3" t="n">
-        <v>12936.37</v>
-      </c>
-      <c r="F53" s="3" t="n"/>
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n">
+        <v>2790.57</v>
+      </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-94,286.99 Cr</t>
+          <t>40,441.68 Cr</t>
         </is>
       </c>
     </row>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>17-05-2026</t>
+          <t>20-05-2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605177523/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605202357/CR</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="3" t="n"/>
       <c r="F54" s="3" t="n">
-        <v>5169.24</v>
+        <v>2470.78</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>-89,117.75 Cr</t>
+          <t>42,912.46 Cr</t>
         </is>
       </c>
     </row>
@@ -1821,22 +1821,22 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>17-05-2026</t>
+          <t>20-05-2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/512938102938/CR/SUPPLIER CREDIT NOTE</t>
+          <t>UPIAR/312938102938/DR/ZEPTO/YESB/zepto@yb</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
-      <c r="E55" s="3" t="n"/>
-      <c r="F55" s="3" t="n">
-        <v>2534.22</v>
-      </c>
+      <c r="E55" s="3" t="n">
+        <v>351.34</v>
+      </c>
+      <c r="F55" s="3" t="n"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-86,583.53 Cr</t>
+          <t>42,561.12 Cr</t>
         </is>
       </c>
     </row>
@@ -1846,22 +1846,22 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17-05-2026</t>
+          <t>21-05-2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/347067657684/DR/KAJALVI/YESB/paytm.s1w3jr9@</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605213483/CR</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
-      <c r="E56" s="3" t="n">
-        <v>181.44</v>
-      </c>
-      <c r="F56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n">
+        <v>4738.76</v>
+      </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>-86,764.97 Cr</t>
+          <t>47,299.88 Cr</t>
         </is>
       </c>
     </row>
@@ -1871,22 +1871,22 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>18-05-2026</t>
+          <t>21-05-2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605189488/CR</t>
+          <t>UPIAR/140515780706/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
-      <c r="E57" s="3" t="n"/>
-      <c r="F57" s="3" t="n">
-        <v>4498.86</v>
-      </c>
+      <c r="E57" s="3" t="n">
+        <v>298.16</v>
+      </c>
+      <c r="F57" s="3" t="n"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-82,266.11 Cr</t>
+          <t>47,001.72 Cr</t>
         </is>
       </c>
     </row>
@@ -1896,22 +1896,22 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>19-05-2026</t>
+          <t>22-05-2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605191295/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605227560/CR</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="3" t="n"/>
       <c r="F58" s="3" t="n">
-        <v>8178.15</v>
+        <v>9917.110000000001</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>-74,087.96 Cr</t>
+          <t>56,918.83 Cr</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,20 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>19-05-2026</t>
+          <t>23-05-2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/719421374678/DR/NEWKRSN/YESB/paytmqr6a0ixr@</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605232109/CR</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
-      <c r="E59" s="3" t="n">
-        <v>295.34</v>
-      </c>
+      <c r="E59" s="3" t="n"/>
       <c r="F59" s="3" t="n"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-74,383.30 Cr</t>
+          <t>53,817.55 Cr</t>
         </is>
       </c>
     </row>
@@ -1946,22 +1944,22 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19-05-2026</t>
+          <t>23-05-2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/124934775512/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+          <t>UPIAR/758331734676/DR/EKNATHB/YESB/ Q440089343@yb</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="3" t="n">
-        <v>204.47</v>
+        <v>244.28</v>
       </c>
       <c r="F60" s="3" t="n"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>-74,587.77 Cr</t>
+          <t>53,573.27 Cr</t>
         </is>
       </c>
     </row>
@@ -1971,22 +1969,22 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19-05-2026</t>
+          <t>24-05-2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/112938102938/CR/WHOLESALE MILK DEPOSIT</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605247649/CR</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="3" t="n"/>
       <c r="F61" s="3" t="n">
-        <v>8403.860000000001</v>
+        <v>5910.58</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>-66,183.91 Cr</t>
+          <t>59,483.85 Cr</t>
         </is>
       </c>
     </row>
@@ -1996,22 +1994,22 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20-05-2026</t>
+          <t>24-05-2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605206093/CR</t>
+          <t>UPIAR/701074556047/DR/73374590/PUNB/7337459005@pty</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
-      <c r="E62" s="3" t="n"/>
-      <c r="F62" s="3" t="n">
-        <v>6366.98</v>
-      </c>
+      <c r="E62" s="3" t="n">
+        <v>202.25</v>
+      </c>
+      <c r="F62" s="3" t="n"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>-59,816.93 Cr</t>
+          <t>59,281.60 Cr</t>
         </is>
       </c>
     </row>
@@ -2021,22 +2019,22 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>21-05-2026</t>
+          <t>24-05-2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605214649/CR</t>
+          <t>UPIAR/110099887766/DR/OLA CABS</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
-      <c r="E63" s="3" t="n"/>
-      <c r="F63" s="3" t="n">
-        <v>4127.73</v>
-      </c>
+      <c r="E63" s="3" t="n">
+        <v>463.64</v>
+      </c>
+      <c r="F63" s="3" t="n"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-55,689.20 Cr</t>
+          <t>58,817.96 Cr</t>
         </is>
       </c>
     </row>
@@ -2046,22 +2044,22 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>21-05-2026</t>
+          <t>25-05-2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/221100998877/DR/UBER RIDE</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605255922/CR</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="3" t="n">
-        <v>683.02</v>
-      </c>
-      <c r="F64" s="3" t="n"/>
+      <c r="E64" s="3" t="n"/>
+      <c r="F64" s="3" t="n">
+        <v>7802.94</v>
+      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>-56,372.22 Cr</t>
+          <t>66,620.90 Cr</t>
         </is>
       </c>
     </row>
@@ -2071,22 +2069,22 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>21-05-2026</t>
+          <t>25-05-2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/301984712093/DR/SWIGGY/HDFC/swiggy@hdfc</t>
+          <t>UPIAB/776655443322/CR/CASHBACK REWARD</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
-      <c r="E65" s="3" t="n">
-        <v>354.78</v>
-      </c>
-      <c r="F65" s="3" t="n"/>
+      <c r="E65" s="3" t="n"/>
+      <c r="F65" s="3" t="n">
+        <v>118.8</v>
+      </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-56,727.00 Cr</t>
+          <t>66,739.70 Cr</t>
         </is>
       </c>
     </row>
@@ -2096,22 +2094,22 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>21-05-2026</t>
+          <t>25-05-2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>BESCOM POWER UTILITY / BANGALORE WAREHOUSE</t>
+          <t>LIC PREMIUM AUTO DEBIT CLEARING</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="3" t="n">
-        <v>10967.91</v>
+        <v>8673.799999999999</v>
       </c>
       <c r="F66" s="3" t="n"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>-67,694.91 Cr</t>
+          <t>58,065.90 Cr</t>
         </is>
       </c>
     </row>
@@ -2121,22 +2119,22 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>22-05-2026</t>
+          <t>25-05-2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605226247/CR</t>
+          <t>UPIAR/123854061954/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
-      <c r="E67" s="3" t="n"/>
-      <c r="F67" s="3" t="n">
-        <v>3930.89</v>
-      </c>
+      <c r="E67" s="3" t="n">
+        <v>462.96</v>
+      </c>
+      <c r="F67" s="3" t="n"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-63,764.02 Cr</t>
+          <t>57,602.94 Cr</t>
         </is>
       </c>
     </row>
@@ -2146,22 +2144,22 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>22-05-2026</t>
+          <t>25-05-2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/998877665544/DR/PAYTM QR VENDOR</t>
+          <t>UPIAR/077728365159/DR/NAMBURI /YESB/ Q501702001@yb</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="3" t="n">
-        <v>117.66</v>
+        <v>76.34</v>
       </c>
       <c r="F68" s="3" t="n"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>-63,881.68 Cr</t>
+          <t>57,526.60 Cr</t>
         </is>
       </c>
     </row>
@@ -2171,22 +2169,22 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23-05-2026</t>
+          <t>26-05-2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605232837/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605268941/CR</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
       <c r="E69" s="3" t="n"/>
       <c r="F69" s="3" t="n">
-        <v>3861.09</v>
+        <v>774.23</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-60,020.59 Cr</t>
+          <t>58,300.83 Cr</t>
         </is>
       </c>
     </row>
@@ -2196,22 +2194,22 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>23-05-2026</t>
+          <t>26-05-2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/998877665544/DR/PAYTM QR VENDOR</t>
+          <t>UPIAR/221100998877/DR/UBER RIDE</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="3" t="n">
-        <v>170.76</v>
+        <v>235.95</v>
       </c>
       <c r="F70" s="3" t="n"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>-60,191.35 Cr</t>
+          <t>58,064.88 Cr</t>
         </is>
       </c>
     </row>
@@ -2221,22 +2219,22 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>24-05-2026</t>
+          <t>26-05-2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605241075/CR</t>
+          <t>UPIAR/812938102938/DR/PETROL PUMP/HPCL/hpcl@icici</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
-      <c r="E71" s="3" t="n"/>
-      <c r="F71" s="3" t="n">
-        <v>7034.63</v>
-      </c>
+      <c r="E71" s="3" t="n">
+        <v>1831.77</v>
+      </c>
+      <c r="F71" s="3" t="n"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-53,156.72 Cr</t>
+          <t>56,233.11 Cr</t>
         </is>
       </c>
     </row>
@@ -2246,22 +2244,22 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>24-05-2026</t>
+          <t>27-05-2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/140288398543/DR/73374590/PUNB/7337459005@pty</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605276607/CR</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
-      <c r="E72" s="3" t="n">
-        <v>169.45</v>
-      </c>
-      <c r="F72" s="3" t="n"/>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n">
+        <v>11670.09</v>
+      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>-53,326.17 Cr</t>
+          <t>67,903.20 Cr</t>
         </is>
       </c>
     </row>
@@ -2271,22 +2269,22 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>25-05-2026</t>
+          <t>28-05-2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605251628/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605283471/CR</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="3" t="n"/>
       <c r="F73" s="3" t="n">
-        <v>2700.43</v>
+        <v>1440.63</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-50,625.74 Cr</t>
+          <t>69,343.83 Cr</t>
         </is>
       </c>
     </row>
@@ -2296,22 +2294,22 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>25-05-2026</t>
+          <t>29-05-2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/110099887766/DR/OLA CABS</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605298574/CR</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
-      <c r="E74" s="3" t="n">
-        <v>584.5599999999999</v>
-      </c>
-      <c r="F74" s="3" t="n"/>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="3" t="n">
+        <v>4462.87</v>
+      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>-51,210.30 Cr</t>
+          <t>73,806.70 Cr</t>
         </is>
       </c>
     </row>
@@ -2321,22 +2319,22 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>26-05-2026</t>
+          <t>29-05-2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605263985/CR</t>
+          <t>UPIAB/271988123471/CR/THIRUVEE/UBIN/9391652831-2@a</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" s="3" t="n"/>
       <c r="F75" s="3" t="n">
-        <v>4322.51</v>
+        <v>394.54</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-46,887.79 Cr</t>
+          <t>74,201.24 Cr</t>
         </is>
       </c>
     </row>
@@ -2346,22 +2344,22 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>26-05-2026</t>
+          <t>30-05-2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/645455850592/DR/DDhanus/SBIN/ 7396913943@up</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605305010/CR</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
-      <c r="E76" s="3" t="n">
-        <v>256.6</v>
-      </c>
-      <c r="F76" s="3" t="n"/>
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="3" t="n">
+        <v>3107.45</v>
+      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>-47,144.39 Cr</t>
+          <t>77,308.69 Cr</t>
         </is>
       </c>
     </row>
@@ -2371,22 +2369,22 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>27-05-2026</t>
+          <t>30-05-2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605272263/CR</t>
+          <t>UPIAR/665544332211/DR/AMAZON INDIA</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
-      <c r="E77" s="3" t="n"/>
-      <c r="F77" s="3" t="n">
-        <v>5077.32</v>
-      </c>
+      <c r="E77" s="3" t="n">
+        <v>3116.82</v>
+      </c>
+      <c r="F77" s="3" t="n"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-42,067.07 Cr</t>
+          <t>74,191.87 Cr</t>
         </is>
       </c>
     </row>
@@ -2396,22 +2394,22 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>28-05-2026</t>
+          <t>31-05-2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/776655443322/CR/CASHBACK REWARD</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605311710/CR</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="3" t="n"/>
       <c r="F78" s="3" t="n">
-        <v>21.93</v>
+        <v>7783.52</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>-42,045.14 Cr</t>
+          <t>81,975.39 Cr</t>
         </is>
       </c>
     </row>
@@ -2421,22 +2419,22 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>29-05-2026</t>
+          <t>31-05-2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605295449/CR</t>
+          <t>OFFICE PANTRY &amp; FRESH REFRESHMENTS</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
-      <c r="E79" s="3" t="n"/>
-      <c r="F79" s="3" t="n">
-        <v>1465.23</v>
-      </c>
+      <c r="E79" s="3" t="n">
+        <v>1632.7</v>
+      </c>
+      <c r="F79" s="3" t="n"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-40,579.91 Cr</t>
+          <t>80,342.69 Cr</t>
         </is>
       </c>
     </row>
@@ -2446,22 +2444,22 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>29-05-2026</t>
+          <t>31-05-2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/665544332211/DR/AMAZON INDIA</t>
+          <t>GST ADVANCE TAX DEPOSIT / GOVT OF INDIA</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="3" t="n">
-        <v>2021.65</v>
+        <v>22497.72</v>
       </c>
       <c r="F80" s="3" t="n"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>-42,601.56 Cr</t>
+          <t>57,844.97 Cr</t>
         </is>
       </c>
     </row>
@@ -2471,22 +2469,22 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>29-05-2026</t>
+          <t>31-05-2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>LIC PREMIUM AUTO DEBIT CLEARING</t>
+          <t>UPIAB/322671730620/CR/PITCHIKA/SBIN/ 8919861154@ax</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
-      <c r="E81" s="3" t="n">
-        <v>7663.51</v>
-      </c>
-      <c r="F81" s="3" t="n"/>
+      <c r="E81" s="3" t="n"/>
+      <c r="F81" s="3" t="n">
+        <v>2046.8</v>
+      </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-50,265.07 Cr</t>
+          <t>59,891.77 Cr</t>
         </is>
       </c>
     </row>
@@ -2496,22 +2494,22 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>30-05-2026</t>
+          <t>31-05-2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605305620/CR</t>
+          <t>NEFT/OUTWARD/UTI MUTUAL FUND SIP</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
-      <c r="E82" s="3" t="n"/>
-      <c r="F82" s="3" t="n">
-        <v>7865.48</v>
-      </c>
+      <c r="E82" s="3" t="n">
+        <v>2363.2</v>
+      </c>
+      <c r="F82" s="3" t="n"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>-42,399.59 Cr</t>
+          <t>57,528.57 Cr</t>
         </is>
       </c>
     </row>
@@ -2521,22 +2519,22 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>30-05-2026</t>
+          <t>31-05-2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>FIRE SAFETY INSPECTION &amp; EQUIPMENT REFILL</t>
+          <t>UPIAR/645455850592/DR/DDhanus/SBIN/ 7396913943@up</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="3" t="n">
-        <v>3953.87</v>
+        <v>253.23</v>
       </c>
       <c r="F83" s="3" t="n"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-46,353.46 Cr</t>
+          <t>57,275.34 Cr</t>
         </is>
       </c>
     </row>
@@ -2546,22 +2544,22 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31-05-2026</t>
+          <t>01-06-2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605318122/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606018365/CR</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="3" t="n"/>
       <c r="F84" s="3" t="n">
-        <v>2743.79</v>
+        <v>4476.85</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>-43,609.67 Cr</t>
+          <t>61,752.19 Cr</t>
         </is>
       </c>
     </row>
@@ -2571,22 +2569,22 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>31-05-2026</t>
+          <t>01-06-2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>WATER TANKER &amp; SANITATION CHARGES</t>
+          <t>UPIAR/110099887766/DR/OLA CABS</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="3" t="n">
-        <v>2173.36</v>
+        <v>346.51</v>
       </c>
       <c r="F85" s="3" t="n"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-45,783.03 Cr</t>
+          <t>61,405.68 Cr</t>
         </is>
       </c>
     </row>
@@ -2596,22 +2594,22 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>01-06-2026</t>
+          <t>02-06-2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606012908/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606026388/CR</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="3" t="n"/>
       <c r="F86" s="3" t="n">
-        <v>5631.71</v>
+        <v>384.07</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>-40,151.32 Cr</t>
+          <t>61,789.75 Cr</t>
         </is>
       </c>
     </row>
@@ -2621,22 +2619,22 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>01-06-2026</t>
+          <t>03-06-2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>BESCOM POWER UTILITY / BANGALORE WAREHOUSE</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606035395/CR</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
-      <c r="E87" s="3" t="n">
-        <v>16172.63</v>
-      </c>
-      <c r="F87" s="3" t="n"/>
+      <c r="E87" s="3" t="n"/>
+      <c r="F87" s="3" t="n">
+        <v>9622.82</v>
+      </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>-56,323.95 Cr</t>
+          <t>71,412.57 Cr</t>
         </is>
       </c>
     </row>
@@ -2646,22 +2644,22 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>02-06-2026</t>
+          <t>03-06-2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606027181/CR</t>
+          <t>UPIAR/110099887766/DR/OLA CABS</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
-      <c r="E88" s="3" t="n"/>
-      <c r="F88" s="3" t="n">
-        <v>6305.1</v>
-      </c>
+      <c r="E88" s="3" t="n">
+        <v>635.4299999999999</v>
+      </c>
+      <c r="F88" s="3" t="n"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>-50,018.85 Cr</t>
+          <t>70,777.14 Cr</t>
         </is>
       </c>
     </row>
@@ -2671,22 +2669,22 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>02-06-2026</t>
+          <t>03-06-2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/443322110099/CR/PROMO DISCOUNT CREDIT</t>
+          <t>SWIGGY INSTAMART FLEET REIMBURSEMENT</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
-      <c r="E89" s="3" t="n"/>
-      <c r="F89" s="3" t="n">
-        <v>123.63</v>
-      </c>
+      <c r="E89" s="3" t="n">
+        <v>593.4299999999999</v>
+      </c>
+      <c r="F89" s="3" t="n"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>-49,895.22 Cr</t>
+          <t>70,183.71 Cr</t>
         </is>
       </c>
     </row>
@@ -2696,22 +2694,22 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>02-06-2026</t>
+          <t>04-06-2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/637338636405/CR/PITCHIKA/SBIN/ 8919861154@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606044675/CR</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="3" t="n"/>
       <c r="F90" s="3" t="n">
-        <v>1958.06</v>
+        <v>3283.87</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>-47,937.16 Cr</t>
+          <t>73,467.58 Cr</t>
         </is>
       </c>
     </row>
@@ -2721,22 +2719,22 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>02-06-2026</t>
+          <t>04-06-2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>SERVICE CHARGE / MINIMUM BALANCE FEE</t>
+          <t>UPIAR/204208208508/DR/Zomato87/AIRP/Zomato8759546.</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
       <c r="E91" s="3" t="n">
-        <v>181.53</v>
+        <v>197.25</v>
       </c>
       <c r="F91" s="3" t="n"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>-48,118.69 Cr</t>
+          <t>73,270.33 Cr</t>
         </is>
       </c>
     </row>
@@ -2746,22 +2744,22 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>02-06-2026</t>
+          <t>05-06-2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>DELIVERY ELECTRIC VAN MAINTENANCE &amp; AMC</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606056512/CR</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
-      <c r="E92" s="3" t="n">
-        <v>3837.15</v>
-      </c>
-      <c r="F92" s="3" t="n"/>
+      <c r="E92" s="3" t="n"/>
+      <c r="F92" s="3" t="n">
+        <v>7581.62</v>
+      </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>-51,955.84 Cr</t>
+          <t>80,851.95 Cr</t>
         </is>
       </c>
     </row>
@@ -2771,22 +2769,22 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03-06-2026</t>
+          <t>05-06-2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606033544/CR</t>
+          <t>UPIAB/712626244599/CR/PICHIKA/BARB/ 8985068499@ax</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" s="3" t="n"/>
       <c r="F93" s="3" t="n">
-        <v>7288.22</v>
+        <v>921.42</v>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>-44,667.62 Cr</t>
+          <t>81,773.37 Cr</t>
         </is>
       </c>
     </row>
@@ -2796,22 +2794,22 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>03-06-2026</t>
+          <t>06-06-2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/443322110099/CR/PROMO DISCOUNT CREDIT</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606064611/CR</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
       <c r="E94" s="3" t="n"/>
       <c r="F94" s="3" t="n">
-        <v>195.95</v>
+        <v>8957.559999999999</v>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>-44,471.67 Cr</t>
+          <t>90,730.93 Cr</t>
         </is>
       </c>
     </row>
@@ -2821,22 +2819,22 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04-06-2026</t>
+          <t>07-06-2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606045096/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606074332/CR</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="3" t="n"/>
       <c r="F95" s="3" t="n">
-        <v>7571.24</v>
+        <v>4138.93</v>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>-36,900.43 Cr</t>
+          <t>94,869.86 Cr</t>
         </is>
       </c>
     </row>
@@ -2846,22 +2844,22 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>04-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>WATER TANKER &amp; SANITATION CHARGES</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606084204/CR</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
-      <c r="E96" s="3" t="n">
-        <v>2428.33</v>
-      </c>
-      <c r="F96" s="3" t="n"/>
+      <c r="E96" s="3" t="n"/>
+      <c r="F96" s="3" t="n">
+        <v>471.17</v>
+      </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>-39,328.76 Cr</t>
+          <t>95,341.03 Cr</t>
         </is>
       </c>
     </row>
@@ -2871,22 +2869,22 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>04-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/022447403071/CR/THIRUVEE/UBIN/9391652831-2@a</t>
+          <t>UPIAR/124934775512/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
-      <c r="E97" s="3" t="n"/>
-      <c r="F97" s="3" t="n">
-        <v>752.12</v>
-      </c>
+      <c r="E97" s="3" t="n">
+        <v>726.35</v>
+      </c>
+      <c r="F97" s="3" t="n"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-38,576.64 Cr</t>
+          <t>94,614.68 Cr</t>
         </is>
       </c>
     </row>
@@ -2896,22 +2894,22 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>05-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606053262/CR</t>
+          <t>ATM CASH WITHDRAWAL / KORAMANGALA BRANCH</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
-      <c r="E98" s="3" t="n"/>
-      <c r="F98" s="3" t="n">
-        <v>4379.83</v>
-      </c>
+      <c r="E98" s="3" t="n">
+        <v>2634.15</v>
+      </c>
+      <c r="F98" s="3" t="n"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>-34,196.81 Cr</t>
+          <t>91,980.53 Cr</t>
         </is>
       </c>
     </row>
@@ -2921,22 +2919,22 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>05-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/554433221100/DR/FLIPKART ONLINE</t>
+          <t>UPIAR/908931590719/DR/Mr Raju/YESB/ Q249677790@yb</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="3" t="n">
-        <v>3535.6</v>
+        <v>120.42</v>
       </c>
       <c r="F99" s="3" t="n"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>-37,732.41 Cr</t>
+          <t>91,860.11 Cr</t>
         </is>
       </c>
     </row>
@@ -2946,22 +2944,22 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>05-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/645455850592/DR/DDhanus/SBIN/ 7396913943@up</t>
+          <t>UPIAR/347067657684/DR/KAJALVI/YESB/paytm.s1w3jr9@</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="3" t="n">
-        <v>270.65</v>
+        <v>68.92</v>
       </c>
       <c r="F100" s="3" t="n"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>-38,003.06 Cr</t>
+          <t>91,791.19 Cr</t>
         </is>
       </c>
     </row>
@@ -2971,22 +2969,22 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>06-06-2026</t>
+          <t>10-06-2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606067588/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606108542/CR</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr"/>
       <c r="E101" s="3" t="n"/>
       <c r="F101" s="3" t="n">
-        <v>5315.95</v>
+        <v>3080.97</v>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>-32,687.11 Cr</t>
+          <t>94,872.16 Cr</t>
         </is>
       </c>
     </row>
@@ -2996,22 +2994,22 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06-06-2026</t>
+          <t>10-06-2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/665544332211/DR/AMAZON INDIA</t>
+          <t>PRINTING BARCODE LABELS &amp; BILLING ROLLS</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="3" t="n">
-        <v>1266.84</v>
+        <v>4232.32</v>
       </c>
       <c r="F102" s="3" t="n"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>-33,953.95 Cr</t>
+          <t>90,639.84 Cr</t>
         </is>
       </c>
     </row>
@@ -3021,22 +3019,22 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>07-06-2026</t>
+          <t>10-06-2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606073974/CR</t>
+          <t>DELIVERY FLEET FUEL &amp; DIESEL RECHARGE</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr"/>
-      <c r="E103" s="3" t="n"/>
-      <c r="F103" s="3" t="n">
-        <v>4031.17</v>
-      </c>
+      <c r="E103" s="3" t="n">
+        <v>5300.48</v>
+      </c>
+      <c r="F103" s="3" t="n"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>-29,922.78 Cr</t>
+          <t>85,339.36 Cr</t>
         </is>
       </c>
     </row>
@@ -3046,22 +3044,22 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>10-06-2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606088690/CR</t>
+          <t>UPIAR/645455850592/DR/DDhanus/SBIN/ 7396913943@up</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr"/>
-      <c r="E104" s="3" t="n"/>
-      <c r="F104" s="3" t="n">
-        <v>6109.48</v>
-      </c>
+      <c r="E104" s="3" t="n">
+        <v>248.98</v>
+      </c>
+      <c r="F104" s="3" t="n"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>-23,813.30 Cr</t>
+          <t>85,090.38 Cr</t>
         </is>
       </c>
     </row>
@@ -3071,22 +3069,22 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>10-06-2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/172136536211/DR/ZOMATO L/YESB/zomato-order@p</t>
+          <t>UPIAR/123854061954/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr"/>
       <c r="E105" s="3" t="n">
-        <v>507.82</v>
+        <v>174.19</v>
       </c>
       <c r="F105" s="3" t="n"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>-24,321.12 Cr</t>
+          <t>84,916.19 Cr</t>
         </is>
       </c>
     </row>
@@ -3096,22 +3094,22 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>INTEREST CREDIT / SBI SAVINGS &amp; CURRENT BAL</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606118435/CR</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr"/>
       <c r="E106" s="3" t="n"/>
       <c r="F106" s="3" t="n">
-        <v>1440.37</v>
+        <v>6596.46</v>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>-22,880.75 Cr</t>
+          <t>91,512.65 Cr</t>
         </is>
       </c>
     </row>
@@ -3121,22 +3119,22 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>09-06-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606092277/CR</t>
+          <t>UPIAR/554433221100/DR/FLIPKART ONLINE</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
-      <c r="E107" s="3" t="n"/>
-      <c r="F107" s="3" t="n">
-        <v>1996.2</v>
-      </c>
+      <c r="E107" s="3" t="n">
+        <v>3640.96</v>
+      </c>
+      <c r="F107" s="3" t="n"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>-20,884.55 Cr</t>
+          <t>87,871.69 Cr</t>
         </is>
       </c>
     </row>
@@ -3146,22 +3144,22 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>09-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/347067657684/DR/KAJALVI/YESB/paytm.s1w3jr9@</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606125240/CR</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr"/>
-      <c r="E108" s="3" t="n">
-        <v>64.75</v>
-      </c>
-      <c r="F108" s="3" t="n"/>
+      <c r="E108" s="3" t="n"/>
+      <c r="F108" s="3" t="n">
+        <v>7142.71</v>
+      </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>-20,949.30 Cr</t>
+          <t>95,014.40 Cr</t>
         </is>
       </c>
     </row>
@@ -3171,22 +3169,22 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>GST ADVANCE TAX DEPOSIT / GOVT OF INDIA</t>
+          <t>BBMP MUNICIPAL TRADE LICENSE &amp; PROPERTY TAX</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr"/>
       <c r="E109" s="3" t="n">
-        <v>21504.87</v>
+        <v>5323.5</v>
       </c>
       <c r="F109" s="3" t="n"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>-42,454.17 Cr</t>
+          <t>89,690.90 Cr</t>
         </is>
       </c>
     </row>
@@ -3196,22 +3194,22 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>10-06-2026</t>
+          <t>13-06-2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606103051/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606136588/CR</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr"/>
       <c r="E110" s="3" t="n"/>
       <c r="F110" s="3" t="n">
-        <v>3352.57</v>
+        <v>748.6</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>-39,101.60 Cr</t>
+          <t>90,439.50 Cr</t>
         </is>
       </c>
     </row>
@@ -3221,22 +3219,22 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>10-06-2026</t>
+          <t>13-06-2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>AIRTEL CORPORATE BROADBAND &amp; FIBER</t>
+          <t>SERVICE CHARGE / MINIMUM BALANCE FEE</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr"/>
       <c r="E111" s="3" t="n">
-        <v>2105.8</v>
+        <v>260.85</v>
       </c>
       <c r="F111" s="3" t="n"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>-41,207.40 Cr</t>
+          <t>90,178.65 Cr</t>
         </is>
       </c>
     </row>
@@ -3246,22 +3244,22 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>10-06-2026</t>
+          <t>13-06-2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/455944913251/DR/KEMSARAP/SBIN/ 8977604821@yb</t>
+          <t>UPIAR/204208208508/DR/Zomato87/AIRP/Zomato8759546.</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr"/>
       <c r="E112" s="3" t="n">
-        <v>229.43</v>
+        <v>234.12</v>
       </c>
       <c r="F112" s="3" t="n"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>-41,436.83 Cr</t>
+          <t>89,944.53 Cr</t>
         </is>
       </c>
     </row>
@@ -3271,22 +3269,22 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>10-06-2026</t>
+          <t>14-06-2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/789123891023/CR/CUSTOMER REFUND REVERSAL</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606141302/CR</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr"/>
       <c r="E113" s="3" t="n"/>
       <c r="F113" s="3" t="n">
-        <v>419.56</v>
+        <v>9085.58</v>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>-41,017.27 Cr</t>
+          <t>99,030.11 Cr</t>
         </is>
       </c>
     </row>
@@ -3296,22 +3294,22 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>14-06-2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606117331/CR</t>
+          <t>UPIAB/020074062699/CR/THIRUVEE/UBIN/9391652831-2@a</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr"/>
       <c r="E114" s="3" t="n"/>
       <c r="F114" s="3" t="n">
-        <v>8814</v>
+        <v>1095.12</v>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>-32,203.27 Cr</t>
+          <t>100,125.23 Cr</t>
         </is>
       </c>
     </row>
@@ -3321,22 +3319,22 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>14-06-2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/539631629714/CR/TAIESWA/PPIW/6302476334.wal</t>
+          <t>UPIAR/412938102938/DR/BIGBASKET/ICIC/bb@icici</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr"/>
-      <c r="E115" s="3" t="n"/>
-      <c r="F115" s="3" t="n">
-        <v>431.17</v>
-      </c>
+      <c r="E115" s="3" t="n">
+        <v>2036.21</v>
+      </c>
+      <c r="F115" s="3" t="n"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>-31,772.10 Cr</t>
+          <t>98,089.02 Cr</t>
         </is>
       </c>
     </row>
@@ -3346,22 +3344,22 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>15-06-2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/908931590719/DR/Mr Raju/YESB/ Q249677790@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606158515/CR</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr"/>
-      <c r="E116" s="3" t="n">
-        <v>107.09</v>
-      </c>
-      <c r="F116" s="3" t="n"/>
+      <c r="E116" s="3" t="n"/>
+      <c r="F116" s="3" t="n">
+        <v>5998.75</v>
+      </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>-31,879.19 Cr</t>
+          <t>104,087.77 Cr</t>
         </is>
       </c>
     </row>
@@ -3371,22 +3369,22 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>15-06-2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606126882/CR</t>
+          <t>UPIAR/278079065373/DR/LHEMANT/HDFC/hemanth0508@yb</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr"/>
-      <c r="E117" s="3" t="n"/>
-      <c r="F117" s="3" t="n">
-        <v>6513.41</v>
-      </c>
+      <c r="E117" s="3" t="n">
+        <v>200.16</v>
+      </c>
+      <c r="F117" s="3" t="n"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>-25,365.78 Cr</t>
+          <t>103,887.61 Cr</t>
         </is>
       </c>
     </row>
@@ -3396,22 +3394,22 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>15-06-2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>AWS CLOUD SERVER HOSTING &amp; INFRASTRUCTURE</t>
+          <t>SECURITY GUARD SERVICES &amp; CCTV MONITORING</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr"/>
       <c r="E118" s="3" t="n">
-        <v>5200.17</v>
+        <v>7867.35</v>
       </c>
       <c r="F118" s="3" t="n"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>-30,565.95 Cr</t>
+          <t>96,020.26 Cr</t>
         </is>
       </c>
     </row>
@@ -3421,22 +3419,22 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>15-06-2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>PACKAGING SUPPLIES / ECO CORRUGATED BOXES</t>
+          <t>UPIAR/143302589531/DR/Zomato87/AIRP/Zomato8759546.</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr"/>
       <c r="E119" s="3" t="n">
-        <v>14452.77</v>
+        <v>250.75</v>
       </c>
       <c r="F119" s="3" t="n"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>-45,018.72 Cr</t>
+          <t>95,769.51 Cr</t>
         </is>
       </c>
     </row>
@@ -3446,22 +3444,22 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>15-06-2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/204208208508/DR/Zomato87/AIRP/Zomato8759546.</t>
+          <t>UPIAR/026544681447/DR/SHANTIP/YESB/ Q707874078@yb</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr"/>
       <c r="E120" s="3" t="n">
-        <v>235.26</v>
+        <v>627.08</v>
       </c>
       <c r="F120" s="3" t="n"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>-45,253.98 Cr</t>
+          <t>95,142.43 Cr</t>
         </is>
       </c>
     </row>
@@ -3471,22 +3469,22 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>13-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606137807/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606162585/CR</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr"/>
       <c r="E121" s="3" t="n"/>
       <c r="F121" s="3" t="n">
-        <v>6801.31</v>
+        <v>2304.69</v>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>-38,452.67 Cr</t>
+          <t>97,447.12 Cr</t>
         </is>
       </c>
     </row>
@@ -3496,22 +3494,22 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>13-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/077728365159/DR/NAMBURI /YESB/ Q501702001@yb</t>
+          <t>GOOGLE WORKSPACE &amp; SLACK CLOUD SUITE</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr"/>
       <c r="E122" s="3" t="n">
-        <v>75.64</v>
+        <v>5686.01</v>
       </c>
       <c r="F122" s="3" t="n"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>-38,528.31 Cr</t>
+          <t>91,761.11 Cr</t>
         </is>
       </c>
     </row>
@@ -3521,22 +3519,22 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>13-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/020074062699/CR/THIRUVEE/UBIN/9391652831-2@a</t>
+          <t>UPIAR/908931590719/DR/Mr Raju/YESB/ Q249677790@yb</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr"/>
-      <c r="E123" s="3" t="n"/>
-      <c r="F123" s="3" t="n">
-        <v>1229.9</v>
-      </c>
+      <c r="E123" s="3" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="F123" s="3" t="n"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>-37,298.41 Cr</t>
+          <t>91,711.20 Cr</t>
         </is>
       </c>
     </row>
@@ -3546,22 +3544,22 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>13-06-2026</t>
+          <t>17-06-2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/982301928371/CR/LOCAL VENDOR/ICIC/vendor@icici</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606171651/CR</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr"/>
       <c r="E124" s="3" t="n"/>
       <c r="F124" s="3" t="n">
-        <v>6316.3</v>
+        <v>3698.07</v>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>-30,982.11 Cr</t>
+          <t>95,409.27 Cr</t>
         </is>
       </c>
     </row>
@@ -3571,22 +3569,22 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>14-06-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606146460/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606189046/CR</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr"/>
       <c r="E125" s="3" t="n"/>
       <c r="F125" s="3" t="n">
-        <v>7437.04</v>
+        <v>9182.98</v>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>-23,545.07 Cr</t>
+          <t>104,592.25 Cr</t>
         </is>
       </c>
     </row>
@@ -3596,22 +3594,22 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>14-06-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/312938102938/DR/ZEPTO/YESB/zepto@yb</t>
+          <t>UPIAB/020074062699/CR/THIRUVEE/UBIN/9391652831-2@a</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr"/>
-      <c r="E126" s="3" t="n">
-        <v>561.24</v>
-      </c>
-      <c r="F126" s="3" t="n"/>
+      <c r="E126" s="3" t="n"/>
+      <c r="F126" s="3" t="n">
+        <v>225.35</v>
+      </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>-24,106.31 Cr</t>
+          <t>104,817.60 Cr</t>
         </is>
       </c>
     </row>
@@ -3621,22 +3619,22 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>14-06-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/312938102938/DR/ZEPTO/YESB/zepto@yb</t>
+          <t>UPIAR/758331734676/DR/EKNATHB/YESB/ Q440089343@yb</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr"/>
       <c r="E127" s="3" t="n">
-        <v>400.23</v>
+        <v>201.29</v>
       </c>
       <c r="F127" s="3" t="n"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>-24,506.54 Cr</t>
+          <t>104,616.31 Cr</t>
         </is>
       </c>
     </row>
@@ -3646,22 +3644,22 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>14-06-2026</t>
+          <t>19-06-2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/026544681447/DR/SHANTIP/YESB/ Q707874078@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606192715/CR</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr"/>
-      <c r="E128" s="3" t="n">
-        <v>386.44</v>
-      </c>
-      <c r="F128" s="3" t="n"/>
+      <c r="E128" s="3" t="n"/>
+      <c r="F128" s="3" t="n">
+        <v>3594.44</v>
+      </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>-24,892.98 Cr</t>
+          <t>108,210.75 Cr</t>
         </is>
       </c>
     </row>
@@ -3671,22 +3669,22 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>15-06-2026</t>
+          <t>19-06-2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606155668/CR</t>
+          <t>ATM CASH WITHDRAWAL / KORAMANGALA BRANCH</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr"/>
-      <c r="E129" s="3" t="n"/>
-      <c r="F129" s="3" t="n">
-        <v>2757</v>
-      </c>
+      <c r="E129" s="3" t="n">
+        <v>7945.32</v>
+      </c>
+      <c r="F129" s="3" t="n"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>-22,135.98 Cr</t>
+          <t>100,265.43 Cr</t>
         </is>
       </c>
     </row>
@@ -3696,22 +3694,22 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>20-06-2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606165005/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606202967/CR</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr"/>
       <c r="E130" s="3" t="n"/>
       <c r="F130" s="3" t="n">
-        <v>3857.39</v>
+        <v>7416.69</v>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>-18,278.59 Cr</t>
+          <t>107,682.12 Cr</t>
         </is>
       </c>
     </row>
@@ -3721,22 +3719,22 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>20-06-2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>PACKAGING SUPPLIES / ECO CORRUGATED BOXES</t>
+          <t>UPIAR/332211009988/DR/BOOKMYSHOW TICKET</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr"/>
       <c r="E131" s="3" t="n">
-        <v>10686.26</v>
+        <v>628.84</v>
       </c>
       <c r="F131" s="3" t="n"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>-28,964.85 Cr</t>
+          <t>107,053.28 Cr</t>
         </is>
       </c>
     </row>
@@ -3746,22 +3744,22 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>17-06-2026</t>
+          <t>20-06-2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606178072/CR</t>
+          <t>UPIAR/373995020793/DR/LHEMANT/HDFC/hemanth0508@yb</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr"/>
-      <c r="E132" s="3" t="n"/>
-      <c r="F132" s="3" t="n">
-        <v>6720.32</v>
-      </c>
+      <c r="E132" s="3" t="n">
+        <v>2603.42</v>
+      </c>
+      <c r="F132" s="3" t="n"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>-22,244.53 Cr</t>
+          <t>104,449.86 Cr</t>
         </is>
       </c>
     </row>
@@ -3771,22 +3769,22 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>17-06-2026</t>
+          <t>20-06-2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/271988123471/CR/THIRUVEE/UBIN/9391652831-2@a</t>
+          <t>UPIAR/717134959917/DR/AoapAmr/AIRP/AoapAmrita.pay</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr"/>
-      <c r="E133" s="3" t="n"/>
-      <c r="F133" s="3" t="n">
-        <v>509.26</v>
-      </c>
+      <c r="E133" s="3" t="n">
+        <v>4592.03</v>
+      </c>
+      <c r="F133" s="3" t="n"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>-21,735.27 Cr</t>
+          <t>99,857.83 Cr</t>
         </is>
       </c>
     </row>
@@ -3796,22 +3794,22 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>17-06-2026</t>
+          <t>21-06-2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/712626244599/CR/PICHIKA/BARB/ 8985068499@ax</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606219077/CR</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr"/>
       <c r="E134" s="3" t="n"/>
       <c r="F134" s="3" t="n">
-        <v>249.76</v>
+        <v>7005.52</v>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>-21,485.51 Cr</t>
+          <t>106,863.35 Cr</t>
         </is>
       </c>
     </row>
@@ -3821,22 +3819,22 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>17-06-2026</t>
+          <t>21-06-2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>OFFICE PANTRY &amp; FRESH REFRESHMENTS</t>
+          <t>UPIAR/554433221100/DR/FLIPKART ONLINE</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr"/>
       <c r="E135" s="3" t="n">
-        <v>1043.63</v>
+        <v>1437.98</v>
       </c>
       <c r="F135" s="3" t="n"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>-22,529.14 Cr</t>
+          <t>105,425.37 Cr</t>
         </is>
       </c>
     </row>
@@ -3846,22 +3844,22 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606182653/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606224772/CR</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr"/>
       <c r="E136" s="3" t="n"/>
       <c r="F136" s="3" t="n">
-        <v>8910.01</v>
+        <v>4275.26</v>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>-13,619.13 Cr</t>
+          <t>109,700.63 Cr</t>
         </is>
       </c>
     </row>
@@ -3871,22 +3869,22 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606193446/CR</t>
+          <t>UPIAR/221100998877/DR/UBER RIDE</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr"/>
-      <c r="E137" s="3" t="n"/>
-      <c r="F137" s="3" t="n">
-        <v>1898.71</v>
-      </c>
+      <c r="E137" s="3" t="n">
+        <v>656.28</v>
+      </c>
+      <c r="F137" s="3" t="n"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>-11,720.42 Cr</t>
+          <t>109,044.35 Cr</t>
         </is>
       </c>
     </row>
@@ -3896,22 +3894,22 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>EMPLOYEE FIELD COMMUTE &amp; TRAVEL REIMBURSEMENT</t>
+          <t>UPIAR/645455850592/DR/DDhanus/SBIN/ 7396913943@up</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr"/>
       <c r="E138" s="3" t="n">
-        <v>5919.96</v>
+        <v>234.09</v>
       </c>
       <c r="F138" s="3" t="n"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>-17,640.38 Cr</t>
+          <t>108,810.26 Cr</t>
         </is>
       </c>
     </row>
@@ -3921,22 +3919,22 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/235911221570/DR/LHEMANT/HDFC/hemanth0508@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606235070/CR</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr"/>
-      <c r="E139" s="3" t="n">
-        <v>42.78</v>
-      </c>
-      <c r="F139" s="3" t="n"/>
+      <c r="E139" s="3" t="n"/>
+      <c r="F139" s="3" t="n">
+        <v>6476.52</v>
+      </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>-17,683.16 Cr</t>
+          <t>115,286.78 Cr</t>
         </is>
       </c>
     </row>
@@ -3946,22 +3944,22 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/443322110099/CR/PROMO DISCOUNT CREDIT</t>
+          <t>UPIAR/123854061954/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr"/>
-      <c r="E140" s="3" t="n"/>
-      <c r="F140" s="3" t="n">
-        <v>77.58</v>
-      </c>
+      <c r="E140" s="3" t="n">
+        <v>423.32</v>
+      </c>
+      <c r="F140" s="3" t="n"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>-17,605.58 Cr</t>
+          <t>114,863.46 Cr</t>
         </is>
       </c>
     </row>
@@ -3971,22 +3969,22 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>20-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606202980/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606242607/CR</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr"/>
       <c r="E141" s="3" t="n"/>
       <c r="F141" s="3" t="n">
-        <v>8363.01</v>
+        <v>7702.5</v>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>-9,242.57 Cr</t>
+          <t>122,565.96 Cr</t>
         </is>
       </c>
     </row>
@@ -3996,22 +3994,22 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>20-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/301984712093/DR/SWIGGY/HDFC/swiggy@hdfc</t>
+          <t>UPIAB/271988123471/CR/THIRUVEE/UBIN/9391652831-2@a</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr"/>
-      <c r="E142" s="3" t="n">
-        <v>577.59</v>
-      </c>
-      <c r="F142" s="3" t="n"/>
+      <c r="E142" s="3" t="n"/>
+      <c r="F142" s="3" t="n">
+        <v>180.74</v>
+      </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>-9,820.16 Cr</t>
+          <t>122,746.70 Cr</t>
         </is>
       </c>
     </row>
@@ -4021,22 +4019,22 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606214056/CR</t>
+          <t>IMPS/INWARD/SBIN/DISTRIBUTOR SETTLEMENT</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr"/>
       <c r="E143" s="3" t="n"/>
       <c r="F143" s="3" t="n">
-        <v>3009.13</v>
+        <v>21187.4</v>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>-6,811.03 Cr</t>
+          <t>143,934.10 Cr</t>
         </is>
       </c>
     </row>
@@ -4046,22 +4044,22 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>BANK SMS ALERTS &amp; ANNUAL MAINT CHARGES</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606254871/CR</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr"/>
-      <c r="E144" s="3" t="n">
-        <v>93.23</v>
-      </c>
-      <c r="F144" s="3" t="n"/>
+      <c r="E144" s="3" t="n"/>
+      <c r="F144" s="3" t="n">
+        <v>4380.76</v>
+      </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>-6,904.26 Cr</t>
+          <t>148,314.86 Cr</t>
         </is>
       </c>
     </row>
@@ -4071,22 +4069,22 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606227744/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606261529/CR</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr"/>
       <c r="E145" s="3" t="n"/>
       <c r="F145" s="3" t="n">
-        <v>5357.8</v>
+        <v>7823.91</v>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>-1,546.46 Cr</t>
+          <t>156,138.77 Cr</t>
         </is>
       </c>
     </row>
@@ -4096,22 +4094,22 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>JNS-PMSBY-25-26-00289608474-301-631272322</t>
+          <t>SWIGGY INSTAMART FLEET REIMBURSEMENT</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr"/>
       <c r="E146" s="3" t="n">
-        <v>20</v>
+        <v>1034.73</v>
       </c>
       <c r="F146" s="3" t="n"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>-1,566.46 Cr</t>
+          <t>155,104.04 Cr</t>
         </is>
       </c>
     </row>
@@ -4121,22 +4119,22 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606231322/CR</t>
+          <t>UPIAR/758331734676/DR/EKNATHB/YESB/ Q440089343@yb</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr"/>
-      <c r="E147" s="3" t="n"/>
-      <c r="F147" s="3" t="n">
-        <v>9841.469999999999</v>
-      </c>
+      <c r="E147" s="3" t="n">
+        <v>162.53</v>
+      </c>
+      <c r="F147" s="3" t="n"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>8,275.01 Cr</t>
+          <t>154,941.51 Cr</t>
         </is>
       </c>
     </row>
@@ -4146,22 +4144,20 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>DELIVERY ELECTRIC VAN MAINTENANCE &amp; AMC</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606277226/CR</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr"/>
-      <c r="E148" s="3" t="n">
-        <v>4574.61</v>
-      </c>
+      <c r="E148" s="3" t="n"/>
       <c r="F148" s="3" t="n"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>3,700.40 Cr</t>
+          <t>153,351.02 Cr</t>
         </is>
       </c>
     </row>
@@ -4171,22 +4167,22 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606242706/CR</t>
+          <t>UPIAR/347067657684/DR/KAJALVI/YESB/paytm.s1w3jr9@</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr"/>
-      <c r="E149" s="3" t="n"/>
-      <c r="F149" s="3" t="n">
-        <v>2545.62</v>
-      </c>
+      <c r="E149" s="3" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="F149" s="3" t="n"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>6,246.02 Cr</t>
+          <t>153,289.28 Cr</t>
         </is>
       </c>
     </row>
@@ -4196,22 +4192,22 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>28-06-2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>CHQ PAID / CLEARING NO 004812</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606288329/CR</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr"/>
-      <c r="E150" s="3" t="n">
-        <v>12450.18</v>
-      </c>
-      <c r="F150" s="3" t="n"/>
+      <c r="E150" s="3" t="n"/>
+      <c r="F150" s="3" t="n">
+        <v>5000.41</v>
+      </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>-6,204.16 Cr</t>
+          <t>158,289.69 Cr</t>
         </is>
       </c>
     </row>
@@ -4221,22 +4217,22 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>28-06-2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/982301928371/CR/LOCAL VENDOR/ICIC/vendor@icici</t>
+          <t>GOOGLE WORKSPACE &amp; SLACK CLOUD SUITE</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr"/>
-      <c r="E151" s="3" t="n"/>
-      <c r="F151" s="3" t="n">
-        <v>4278.93</v>
-      </c>
+      <c r="E151" s="3" t="n">
+        <v>4218.49</v>
+      </c>
+      <c r="F151" s="3" t="n"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>-1,925.23 Cr</t>
+          <t>154,071.20 Cr</t>
         </is>
       </c>
     </row>
@@ -4246,22 +4242,22 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>28-06-2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606254407/CR</t>
+          <t>UPIAR/373995020793/DR/LHEMANT/HDFC/hemanth0508@yb</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr"/>
-      <c r="E152" s="3" t="n"/>
-      <c r="F152" s="3" t="n">
-        <v>7364.36</v>
-      </c>
+      <c r="E152" s="3" t="n">
+        <v>2167.01</v>
+      </c>
+      <c r="F152" s="3" t="n"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>5,439.13 Cr</t>
+          <t>151,904.19 Cr</t>
         </is>
       </c>
     </row>
@@ -4271,22 +4267,22 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>28-06-2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/412938102938/DR/BIGBASKET/ICIC/bb@icici</t>
+          <t>SERVICE CHARGE / MINIMUM BALANCE FEE</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr"/>
       <c r="E153" s="3" t="n">
-        <v>1093.01</v>
+        <v>153.13</v>
       </c>
       <c r="F153" s="3" t="n"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>4,346.12 Cr</t>
+          <t>151,751.06 Cr</t>
         </is>
       </c>
     </row>
@@ -4296,22 +4292,22 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/701074556047/DR/73374590/PUNB/7337459005@pty</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606299512/CR</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr"/>
-      <c r="E154" s="3" t="n">
-        <v>153.47</v>
-      </c>
-      <c r="F154" s="3" t="n"/>
+      <c r="E154" s="3" t="n"/>
+      <c r="F154" s="3" t="n">
+        <v>4009.72</v>
+      </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>4,192.65 Cr</t>
+          <t>155,760.78 Cr</t>
         </is>
       </c>
     </row>
@@ -4321,22 +4317,22 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606268473/CR</t>
+          <t>UPIAR/908931590719/DR/Mr Raju/YESB/ Q249677790@yb</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr"/>
-      <c r="E155" s="3" t="n"/>
-      <c r="F155" s="3" t="n">
-        <v>3173.05</v>
-      </c>
+      <c r="E155" s="3" t="n">
+        <v>113.14</v>
+      </c>
+      <c r="F155" s="3" t="n"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>7,365.70 Cr</t>
+          <t>155,647.64 Cr</t>
         </is>
       </c>
     </row>
@@ -4346,22 +4342,22 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>SHADOWFAX / DUNZO LAST MILE LOGISTICS FLEET</t>
+          <t>UPIAB/637338636405/CR/PITCHIKA/SBIN/ 8919861154@yb</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr"/>
-      <c r="E156" s="3" t="n">
-        <v>12217.36</v>
-      </c>
-      <c r="F156" s="3" t="n"/>
+      <c r="E156" s="3" t="n"/>
+      <c r="F156" s="3" t="n">
+        <v>1959.56</v>
+      </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>-4,851.66 Cr</t>
+          <t>157,607.20 Cr</t>
         </is>
       </c>
     </row>
@@ -4371,22 +4367,22 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606273957/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606306893/CR</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr"/>
       <c r="E157" s="3" t="n"/>
       <c r="F157" s="3" t="n">
-        <v>10202.06</v>
+        <v>8134.11</v>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>5,350.40 Cr</t>
+          <t>165,741.31 Cr</t>
         </is>
       </c>
     </row>
@@ -4396,22 +4392,22 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>COMMERCIAL WAREHOUSE RENT / KORAMANGALA HUB</t>
+          <t>UPIAR/123854061954/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr"/>
       <c r="E158" s="3" t="n">
-        <v>44344.23</v>
+        <v>295.25</v>
       </c>
       <c r="F158" s="3" t="n"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>-38,993.83 Cr</t>
+          <t>165,446.06 Cr</t>
         </is>
       </c>
     </row>
@@ -4421,22 +4417,22 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>28-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606285235/CR</t>
+          <t>UPIAR/373995020793/DR/LHEMANT/HDFC/hemanth0508@yb</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr"/>
-      <c r="E159" s="3" t="n"/>
-      <c r="F159" s="3" t="n">
-        <v>2674.8</v>
-      </c>
+      <c r="E159" s="3" t="n">
+        <v>2834.85</v>
+      </c>
+      <c r="F159" s="3" t="n"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>-36,319.03 Cr</t>
+          <t>162,611.21 Cr</t>
         </is>
       </c>
     </row>
@@ -4446,22 +4442,22 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>28-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>CHQ PAID / CLEARING NO 004812</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607017875/CR</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr"/>
-      <c r="E160" s="3" t="n">
-        <v>12749.7</v>
-      </c>
-      <c r="F160" s="3" t="n"/>
+      <c r="E160" s="3" t="n"/>
+      <c r="F160" s="3" t="n">
+        <v>8161.3</v>
+      </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>-49,068.73 Cr</t>
+          <t>170,772.51 Cr</t>
         </is>
       </c>
     </row>
@@ -4471,22 +4467,22 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>28-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>AWS CLOUD SERVER HOSTING &amp; INFRASTRUCTURE</t>
+          <t>UPIAR/312938102938/DR/ZEPTO/YESB/zepto@yb</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr"/>
       <c r="E161" s="3" t="n">
-        <v>7931.75</v>
+        <v>630.08</v>
       </c>
       <c r="F161" s="3" t="n"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>-57,000.48 Cr</t>
+          <t>170,142.43 Cr</t>
         </is>
       </c>
     </row>
@@ -4496,22 +4492,22 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606293722/CR</t>
+          <t>UPIAR/908129381023/DR/BILLDESK/SBIN/billdesk@sbi</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr"/>
-      <c r="E162" s="3" t="n"/>
-      <c r="F162" s="3" t="n">
-        <v>6531.87</v>
-      </c>
+      <c r="E162" s="3" t="n">
+        <v>829.48</v>
+      </c>
+      <c r="F162" s="3" t="n"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>-50,468.61 Cr</t>
+          <t>169,312.95 Cr</t>
         </is>
       </c>
     </row>
@@ -4521,22 +4517,22 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/789123891023/CR/CUSTOMER REFUND REVERSAL</t>
+          <t>UPIAB/322671730620/CR/PITCHIKA/SBIN/ 8919861154@ax</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr"/>
       <c r="E163" s="3" t="n"/>
       <c r="F163" s="3" t="n">
-        <v>702.25</v>
+        <v>2103.83</v>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>-49,766.36 Cr</t>
+          <t>171,416.78 Cr</t>
         </is>
       </c>
     </row>
@@ -4546,22 +4542,22 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/455944913251/DR/KEMSARAP/SBIN/ 8977604821@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607028117/CR</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr"/>
-      <c r="E164" s="3" t="n">
-        <v>104.26</v>
-      </c>
-      <c r="F164" s="3" t="n"/>
+      <c r="E164" s="3" t="n"/>
+      <c r="F164" s="3" t="n">
+        <v>4971.4</v>
+      </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>-49,870.62 Cr</t>
+          <t>176,388.18 Cr</t>
         </is>
       </c>
     </row>
@@ -4571,22 +4567,22 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202606306927/CR</t>
+          <t>UPIAR/717134959917/DR/AoapAmr/AIRP/AoapAmrita.pay</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr"/>
-      <c r="E165" s="3" t="n"/>
-      <c r="F165" s="3" t="n">
-        <v>6062.44</v>
-      </c>
+      <c r="E165" s="3" t="n">
+        <v>4998.38</v>
+      </c>
+      <c r="F165" s="3" t="n"/>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>-43,808.18 Cr</t>
+          <t>171,389.80 Cr</t>
         </is>
       </c>
     </row>
@@ -4596,22 +4592,22 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607016477/CR</t>
+          <t>ATM CASH WITHDRAWAL / KORAMANGALA BRANCH</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr"/>
-      <c r="E166" s="3" t="n"/>
-      <c r="F166" s="3" t="n">
-        <v>4067.15</v>
-      </c>
+      <c r="E166" s="3" t="n">
+        <v>2448.4</v>
+      </c>
+      <c r="F166" s="3" t="n"/>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>-39,741.03 Cr</t>
+          <t>168,941.40 Cr</t>
         </is>
       </c>
     </row>
@@ -4626,17 +4622,17 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607022682/CR</t>
+          <t>AIRTEL CORPORATE BROADBAND &amp; FIBER</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr"/>
-      <c r="E167" s="3" t="n"/>
-      <c r="F167" s="3" t="n">
-        <v>7380.75</v>
-      </c>
+      <c r="E167" s="3" t="n">
+        <v>1526.87</v>
+      </c>
+      <c r="F167" s="3" t="n"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>-32,360.28 Cr</t>
+          <t>167,414.53 Cr</t>
         </is>
       </c>
     </row>
@@ -4646,22 +4642,22 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/857830578859/DR/GAURAV S/YESB/ Q815875629@yb</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607031793/CR</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr"/>
-      <c r="E168" s="3" t="n">
-        <v>203.27</v>
-      </c>
-      <c r="F168" s="3" t="n"/>
+      <c r="E168" s="3" t="n"/>
+      <c r="F168" s="3" t="n">
+        <v>4571.44</v>
+      </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>-32,563.55 Cr</t>
+          <t>171,985.97 Cr</t>
         </is>
       </c>
     </row>
@@ -4671,22 +4667,22 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/347067657684/DR/KAJALVI/YESB/paytm.s1w3jr9@</t>
+          <t>UPIAR/235911221570/DR/LHEMANT/HDFC/hemanth0508@yb</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr"/>
       <c r="E169" s="3" t="n">
-        <v>114.5</v>
+        <v>43.95</v>
       </c>
       <c r="F169" s="3" t="n"/>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>-32,678.05 Cr</t>
+          <t>171,942.02 Cr</t>
         </is>
       </c>
     </row>
@@ -4696,22 +4692,22 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/776655443322/CR/CASHBACK REWARD</t>
+          <t>CHQ PAID / CLEARING NO 004812</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr"/>
-      <c r="E170" s="3" t="n"/>
-      <c r="F170" s="3" t="n">
-        <v>51.7</v>
-      </c>
+      <c r="E170" s="3" t="n">
+        <v>11370.82</v>
+      </c>
+      <c r="F170" s="3" t="n"/>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>-32,626.35 Cr</t>
+          <t>160,571.20 Cr</t>
         </is>
       </c>
     </row>
@@ -4726,17 +4722,17 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607036464/CR</t>
+          <t>UPIAR/140515780706/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr"/>
-      <c r="E171" s="3" t="n"/>
-      <c r="F171" s="3" t="n">
-        <v>3663.3</v>
-      </c>
+      <c r="E171" s="3" t="n">
+        <v>236.35</v>
+      </c>
+      <c r="F171" s="3" t="n"/>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>-28,963.05 Cr</t>
+          <t>160,334.85 Cr</t>
         </is>
       </c>
     </row>
@@ -4751,17 +4747,17 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607047215/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607044815/CR</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr"/>
       <c r="E172" s="3" t="n"/>
       <c r="F172" s="3" t="n">
-        <v>3411.62</v>
+        <v>6287.78</v>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>-25,551.43 Cr</t>
+          <t>166,622.63 Cr</t>
         </is>
       </c>
     </row>
@@ -4776,17 +4772,17 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/412938102938/DR/BIGBASKET/ICIC/bb@icici</t>
+          <t>UPIAB/271988123471/CR/THIRUVEE/UBIN/9391652831-2@a</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr"/>
-      <c r="E173" s="3" t="n">
-        <v>1797.16</v>
-      </c>
-      <c r="F173" s="3" t="n"/>
+      <c r="E173" s="3" t="n"/>
+      <c r="F173" s="3" t="n">
+        <v>322.2</v>
+      </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>-27,348.59 Cr</t>
+          <t>166,944.83 Cr</t>
         </is>
       </c>
     </row>
@@ -4796,22 +4792,22 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>05-07-2026</t>
+          <t>04-07-2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607058720/CR</t>
+          <t>UPIAR/857830578859/DR/GAURAV S/YESB/ Q815875629@yb</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr"/>
-      <c r="E174" s="3" t="n"/>
-      <c r="F174" s="3" t="n">
-        <v>4789.83</v>
-      </c>
+      <c r="E174" s="3" t="n">
+        <v>139.17</v>
+      </c>
+      <c r="F174" s="3" t="n"/>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>-22,558.76 Cr</t>
+          <t>166,805.66 Cr</t>
         </is>
       </c>
     </row>
@@ -4826,17 +4822,17 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>AWS CLOUD SERVER HOSTING &amp; INFRASTRUCTURE</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607055168/CR</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr"/>
-      <c r="E175" s="3" t="n">
-        <v>7462.98</v>
-      </c>
-      <c r="F175" s="3" t="n"/>
+      <c r="E175" s="3" t="n"/>
+      <c r="F175" s="3" t="n">
+        <v>1000.61</v>
+      </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>-30,021.74 Cr</t>
+          <t>167,806.27 Cr</t>
         </is>
       </c>
     </row>
@@ -4851,17 +4847,17 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/022447403071/CR/THIRUVEE/UBIN/9391652831-2@a</t>
+          <t>UPIAR/373995020793/DR/LHEMANT/HDFC/hemanth0508@yb</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr"/>
-      <c r="E176" s="3" t="n"/>
-      <c r="F176" s="3" t="n">
-        <v>752.0700000000001</v>
-      </c>
+      <c r="E176" s="3" t="n">
+        <v>3580.83</v>
+      </c>
+      <c r="F176" s="3" t="n"/>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>-29,269.67 Cr</t>
+          <t>164,225.44 Cr</t>
         </is>
       </c>
     </row>
@@ -4876,17 +4872,17 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607067745/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607062885/CR</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr"/>
       <c r="E177" s="3" t="n"/>
       <c r="F177" s="3" t="n">
-        <v>2290.54</v>
+        <v>7669.66</v>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>-26,979.13 Cr</t>
+          <t>171,895.10 Cr</t>
         </is>
       </c>
     </row>
@@ -4901,17 +4897,17 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/857830578859/DR/GAURAV S/YESB/ Q815875629@yb</t>
+          <t>WATER TANKER &amp; SANITATION CHARGES</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr"/>
       <c r="E178" s="3" t="n">
-        <v>182.64</v>
+        <v>1995.44</v>
       </c>
       <c r="F178" s="3" t="n"/>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>-27,161.77 Cr</t>
+          <t>169,899.66 Cr</t>
         </is>
       </c>
     </row>
@@ -4926,17 +4922,17 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/172136536211/DR/ZOMATO L/YESB/zomato-order@p</t>
+          <t>FIRE SAFETY INSPECTION &amp; EQUIPMENT REFILL</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr"/>
       <c r="E179" s="3" t="n">
-        <v>408.5</v>
+        <v>3543.41</v>
       </c>
       <c r="F179" s="3" t="n"/>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>-27,570.27 Cr</t>
+          <t>166,356.25 Cr</t>
         </is>
       </c>
     </row>
@@ -4951,17 +4947,17 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/908129381023/DR/BILLDESK/SBIN/billdesk@sbi</t>
+          <t>UPIAB/800823341214/CR/PITCHIKA/CNRB/ umanag9712@ax</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr"/>
-      <c r="E180" s="3" t="n">
-        <v>1040.42</v>
-      </c>
-      <c r="F180" s="3" t="n"/>
+      <c r="E180" s="3" t="n"/>
+      <c r="F180" s="3" t="n">
+        <v>3225.43</v>
+      </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>-28,610.69 Cr</t>
+          <t>169,581.68 Cr</t>
         </is>
       </c>
     </row>
@@ -4976,17 +4972,17 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607077969/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607077244/CR</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr"/>
       <c r="E181" s="3" t="n"/>
       <c r="F181" s="3" t="n">
-        <v>3591.45</v>
+        <v>5487.01</v>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>-25,019.24 Cr</t>
+          <t>175,068.69 Cr</t>
         </is>
       </c>
     </row>
@@ -5001,17 +4997,17 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/077728365159/DR/NAMBURI /YESB/ Q501702001@yb</t>
+          <t>UPIAB/009988776655/CR/DIVIDEND PAYOUT</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr"/>
-      <c r="E182" s="3" t="n">
-        <v>66.48</v>
-      </c>
-      <c r="F182" s="3" t="n"/>
+      <c r="E182" s="3" t="n"/>
+      <c r="F182" s="3" t="n">
+        <v>261.59</v>
+      </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>-25,085.72 Cr</t>
+          <t>175,330.28 Cr</t>
         </is>
       </c>
     </row>
@@ -5021,20 +5017,22 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>08-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202605282597/CR</t>
+          <t>UPIAR/140288398543/DR/73374590/PUNB/7337459005@pty</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr"/>
-      <c r="E183" s="3" t="n"/>
+      <c r="E183" s="3" t="n">
+        <v>76.8</v>
+      </c>
       <c r="F183" s="3" t="n"/>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>-52,822.51 Cr</t>
+          <t>175,253.48 Cr</t>
         </is>
       </c>
     </row>
@@ -5044,22 +5042,22 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>08-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607081320/CR</t>
+          <t>UPIAB/112938102938/CR/WHOLESALE MILK DEPOSIT</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr"/>
       <c r="E184" s="3" t="n"/>
       <c r="F184" s="3" t="n">
-        <v>7372.48</v>
+        <v>4398.44</v>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>-45,450.03 Cr</t>
+          <t>179,651.92 Cr</t>
         </is>
       </c>
     </row>
@@ -5074,17 +5072,17 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/719421374678/DR/NEWKRSN/YESB/paytmqr6a0ixr@</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607082627/CR</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr"/>
-      <c r="E185" s="3" t="n">
-        <v>102.2</v>
-      </c>
-      <c r="F185" s="3" t="n"/>
+      <c r="E185" s="3" t="n"/>
+      <c r="F185" s="3" t="n">
+        <v>1236.02</v>
+      </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>-45,552.23 Cr</t>
+          <t>180,887.94 Cr</t>
         </is>
       </c>
     </row>
@@ -5099,17 +5097,17 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>WAREHOUSE STAFF WAGES &amp; PACKING CREW</t>
+          <t>JNS-PMSBY-25-26-00289608474-301-631272322</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr"/>
       <c r="E186" s="3" t="n">
-        <v>36763.2</v>
+        <v>20</v>
       </c>
       <c r="F186" s="3" t="n"/>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>-82,315.43 Cr</t>
+          <t>180,867.94 Cr</t>
         </is>
       </c>
     </row>
@@ -5124,17 +5122,17 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/554433221100/DR/FLIPKART ONLINE</t>
+          <t>BBMP MUNICIPAL TRADE LICENSE &amp; PROPERTY TAX</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr"/>
       <c r="E187" s="3" t="n">
-        <v>3876.83</v>
+        <v>4758.27</v>
       </c>
       <c r="F187" s="3" t="n"/>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>-86,192.26 Cr</t>
+          <t>176,109.67 Cr</t>
         </is>
       </c>
     </row>
@@ -5149,17 +5147,17 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/455944913251/DR/KEMSARAP/SBIN/ 8977604821@yb</t>
+          <t>UPIAR/554433221100/DR/FLIPKART ONLINE</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr"/>
       <c r="E188" s="3" t="n">
-        <v>63.06</v>
+        <v>3570.56</v>
       </c>
       <c r="F188" s="3" t="n"/>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>-86,255.32 Cr</t>
+          <t>172,539.11 Cr</t>
         </is>
       </c>
     </row>
@@ -5174,17 +5172,17 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607092736/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607094176/CR</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr"/>
       <c r="E189" s="3" t="n"/>
       <c r="F189" s="3" t="n">
-        <v>7946.47</v>
+        <v>3133.06</v>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>-78,308.85 Cr</t>
+          <t>175,672.17 Cr</t>
         </is>
       </c>
     </row>
@@ -5199,17 +5197,17 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>UPIAB/271988123471/CR/THIRUVEE/UBIN/9391652831-2@a</t>
+          <t>IMPS/INWARD/SBIN/DISTRIBUTOR SETTLEMENT</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr"/>
       <c r="E190" s="3" t="n"/>
       <c r="F190" s="3" t="n">
-        <v>207.62</v>
+        <v>19227.52</v>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>-78,101.23 Cr</t>
+          <t>194,899.69 Cr</t>
         </is>
       </c>
     </row>
@@ -5224,17 +5222,17 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>GOOGLE WORKSPACE &amp; SLACK CLOUD SUITE</t>
+          <t>UPIAR/455944913251/DR/KEMSARAP/SBIN/ 8977604821@yb</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr"/>
       <c r="E191" s="3" t="n">
-        <v>6501.68</v>
+        <v>257.45</v>
       </c>
       <c r="F191" s="3" t="n"/>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>-84,602.91 Cr</t>
+          <t>194,642.24 Cr</t>
         </is>
       </c>
     </row>
@@ -5244,22 +5242,22 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>10-07-2026</t>
+          <t>09-07-2026</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607103466/CR</t>
+          <t>FIRE SAFETY INSPECTION &amp; EQUIPMENT REFILL</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr"/>
-      <c r="E192" s="3" t="n"/>
-      <c r="F192" s="3" t="n">
-        <v>5328.15</v>
-      </c>
+      <c r="E192" s="3" t="n">
+        <v>2662.29</v>
+      </c>
+      <c r="F192" s="3" t="n"/>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>-79,274.76 Cr</t>
+          <t>191,979.95 Cr</t>
         </is>
       </c>
     </row>
@@ -5274,17 +5272,17 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>CHQ PAID / CLEARING NO 004812</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607103418/CR</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr"/>
-      <c r="E193" s="3" t="n">
-        <v>13092.28</v>
-      </c>
-      <c r="F193" s="3" t="n"/>
+      <c r="E193" s="3" t="n"/>
+      <c r="F193" s="3" t="n">
+        <v>9020.92</v>
+      </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>-92,367.04 Cr</t>
+          <t>201,000.87 Cr</t>
         </is>
       </c>
     </row>
@@ -5294,22 +5292,22 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>11-07-2026</t>
+          <t>10-07-2026</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607112876/CR</t>
+          <t>UPIAB/009988776655/CR/DIVIDEND PAYOUT</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr"/>
       <c r="E194" s="3" t="n"/>
       <c r="F194" s="3" t="n">
-        <v>5179.4</v>
+        <v>1742.07</v>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>-87,187.64 Cr</t>
+          <t>202,742.94 Cr</t>
         </is>
       </c>
     </row>
@@ -5319,22 +5317,22 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>11-07-2026</t>
+          <t>10-07-2026</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/123854061954/DR/ZOMATO/HDFC/payzomato@hdfc</t>
+          <t>UPIAB/982301928371/CR/LOCAL VENDOR/ICIC/vendor@icici</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr"/>
-      <c r="E195" s="3" t="n">
-        <v>203.06</v>
-      </c>
-      <c r="F195" s="3" t="n"/>
+      <c r="E195" s="3" t="n"/>
+      <c r="F195" s="3" t="n">
+        <v>7514.09</v>
+      </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>-87,390.70 Cr</t>
+          <t>210,257.03 Cr</t>
         </is>
       </c>
     </row>
@@ -5349,17 +5347,17 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/221100998877/DR/UBER RIDE</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607119177/CR</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr"/>
-      <c r="E196" s="3" t="n">
-        <v>740.91</v>
-      </c>
-      <c r="F196" s="3" t="n"/>
+      <c r="E196" s="3" t="n"/>
+      <c r="F196" s="3" t="n">
+        <v>8525.1</v>
+      </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>-88,131.61 Cr</t>
+          <t>218,782.13 Cr</t>
         </is>
       </c>
     </row>
@@ -5369,22 +5367,22 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>12-07-2026</t>
+          <t>11-07-2026</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607129486/CR</t>
+          <t>UPIAB/112938102938/CR/WHOLESALE MILK DEPOSIT</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr"/>
       <c r="E197" s="3" t="n"/>
       <c r="F197" s="3" t="n">
-        <v>3021.33</v>
+        <v>9599.25</v>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>-85,110.28 Cr</t>
+          <t>228,381.38 Cr</t>
         </is>
       </c>
     </row>
@@ -5394,22 +5392,22 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>12-07-2026</t>
+          <t>11-07-2026</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/908931590719/DR/Mr Raju/YESB/ Q249677790@yb</t>
+          <t>UPIAR/347067657684/DR/KAJALVI/YESB/paytm.s1w3jr9@</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr"/>
       <c r="E198" s="3" t="n">
-        <v>64.56999999999999</v>
+        <v>188.85</v>
       </c>
       <c r="F198" s="3" t="n"/>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>-85,174.85 Cr</t>
+          <t>228,192.53 Cr</t>
         </is>
       </c>
     </row>
@@ -5419,22 +5417,22 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>13-07-2026</t>
+          <t>11-07-2026</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607135659/CR</t>
+          <t>BESCOM POWER UTILITY / BANGALORE WAREHOUSE</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr"/>
-      <c r="E199" s="3" t="n"/>
-      <c r="F199" s="3" t="n">
-        <v>4498.75</v>
-      </c>
+      <c r="E199" s="3" t="n">
+        <v>13022.01</v>
+      </c>
+      <c r="F199" s="3" t="n"/>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>-80,676.10 Cr</t>
+          <t>215,170.52 Cr</t>
         </is>
       </c>
     </row>
@@ -5444,22 +5442,22 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>13-07-2026</t>
+          <t>11-07-2026</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/812938102938/DR/PETROL PUMP/HPCL/hpcl@icici</t>
+          <t>UPIAB/800823341214/CR/PITCHIKA/CNRB/ umanag9712@ax</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr"/>
-      <c r="E200" s="3" t="n">
-        <v>1292.6</v>
-      </c>
-      <c r="F200" s="3" t="n"/>
+      <c r="E200" s="3" t="n"/>
+      <c r="F200" s="3" t="n">
+        <v>2148.54</v>
+      </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>-81,968.70 Cr</t>
+          <t>217,319.06 Cr</t>
         </is>
       </c>
     </row>
@@ -5469,22 +5467,22 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>13-07-2026</t>
+          <t>12-07-2026</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>JNS-PMSBY-25-26-00289608474-301-631272322</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607122253/CR</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr"/>
-      <c r="E201" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F201" s="3" t="n"/>
+      <c r="E201" s="3" t="n"/>
+      <c r="F201" s="3" t="n">
+        <v>5843.72</v>
+      </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>-81,988.70 Cr</t>
+          <t>223,162.78 Cr</t>
         </is>
       </c>
     </row>
@@ -5494,22 +5492,22 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>14-07-2026</t>
+          <t>12-07-2026</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607144495/CR</t>
+          <t>UPIAR/124934775512/DR/ZOMATO/HDFC/payzomato@hdfc</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr"/>
-      <c r="E202" s="3" t="n"/>
-      <c r="F202" s="3" t="n">
-        <v>1782.85</v>
-      </c>
+      <c r="E202" s="3" t="n">
+        <v>284.18</v>
+      </c>
+      <c r="F202" s="3" t="n"/>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>-80,205.85 Cr</t>
+          <t>222,878.60 Cr</t>
         </is>
       </c>
     </row>
@@ -5519,22 +5517,22 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>14-07-2026</t>
+          <t>13-07-2026</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>POINT OF SALE (POS) HARDWARE RENTAL</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607132949/CR</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr"/>
-      <c r="E203" s="3" t="n">
-        <v>2705.12</v>
-      </c>
-      <c r="F203" s="3" t="n"/>
+      <c r="E203" s="3" t="n"/>
+      <c r="F203" s="3" t="n">
+        <v>4129.59</v>
+      </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>-82,910.97 Cr</t>
+          <t>227,008.19 Cr</t>
         </is>
       </c>
     </row>
@@ -5544,22 +5542,22 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>14-07-2026</t>
+          <t>13-07-2026</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>NEFT/INWARD/CITI/GROCERY WHOLESALE REBATE</t>
+          <t>UPIAR/278079065373/DR/LHEMANT/HDFC/hemanth0508@yb</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr"/>
-      <c r="E204" s="3" t="n"/>
-      <c r="F204" s="3" t="n">
-        <v>17024.04</v>
-      </c>
+      <c r="E204" s="3" t="n">
+        <v>483.42</v>
+      </c>
+      <c r="F204" s="3" t="n"/>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>-65,886.93 Cr</t>
+          <t>226,524.77 Cr</t>
         </is>
       </c>
     </row>
@@ -5569,22 +5567,22 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>15-07-2026</t>
+          <t>14-07-2026</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607155953/CR</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607143428/CR</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr"/>
       <c r="E205" s="3" t="n"/>
       <c r="F205" s="3" t="n">
-        <v>1771.87</v>
+        <v>797.92</v>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>-64,115.06 Cr</t>
+          <t>227,322.69 Cr</t>
         </is>
       </c>
     </row>
@@ -5594,22 +5592,22 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>15-07-2026</t>
+          <t>14-07-2026</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/719421374678/DR/NEWKRSN/YESB/paytmqr6a0ixr@</t>
+          <t>UPIAR/347067657684/DR/KAJALVI/YESB/paytm.s1w3jr9@</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr"/>
       <c r="E206" s="3" t="n">
-        <v>234.32</v>
+        <v>36.7</v>
       </c>
       <c r="F206" s="3" t="n"/>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>-64,349.38 Cr</t>
+          <t>227,285.99 Cr</t>
         </is>
       </c>
     </row>
@@ -5624,17 +5622,17 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/332211009988/DR/BOOKMYSHOW TICKET</t>
+          <t>CMS/RAZORPAY/BATCH_SETL/CMS202607152952/CR</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr"/>
-      <c r="E207" s="3" t="n">
-        <v>834.78</v>
-      </c>
-      <c r="F207" s="3" t="n"/>
+      <c r="E207" s="3" t="n"/>
+      <c r="F207" s="3" t="n">
+        <v>1166.7</v>
+      </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>-65,184.16 Cr</t>
+          <t>228,452.69 Cr</t>
         </is>
       </c>
     </row>
@@ -5649,42 +5647,17 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>UPIAR/301984712093/DR/SWIGGY/HDFC/swiggy@hdfc</t>
+          <t>INVENTORY AUDITOR &amp; CA LEGAL RETAINER</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr"/>
       <c r="E208" s="3" t="n">
-        <v>604.8</v>
+        <v>17949.45</v>
       </c>
       <c r="F208" s="3" t="n"/>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>-65,788.96 Cr</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="2" t="n">
-        <v>208</v>
-      </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>15-07-2026</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>SECURITY GUARD SERVICES &amp; CCTV MONITORING</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr"/>
-      <c r="E209" s="3" t="n">
-        <v>7566.12</v>
-      </c>
-      <c r="F209" s="3" t="n"/>
-      <c r="G209" s="2" t="inlineStr">
-        <is>
-          <t>-73,355.08 Cr</t>
+          <t>210,503.24 Cr</t>
         </is>
       </c>
     </row>
